--- a/level_design/level_map.xlsx
+++ b/level_design/level_map.xlsx
@@ -18,7 +18,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="15">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -111,8 +111,14 @@
       <name val="Arial"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Consolas"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="13">
+  <fills count="14">
     <fill>
       <patternFill/>
     </fill>
@@ -174,6 +180,11 @@
         <fgColor rgb="00FFD966"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002E6B34"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -202,7 +213,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -248,6 +259,9 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -714,7 +728,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B66"/>
+  <dimension ref="A1:B72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -1009,325 +1023,397 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="6" t="inlineStr">
+      <c r="A37" s="21" t="inlineStr">
+        <is>
+          <t>TC2</t>
+        </is>
+      </c>
+      <c r="B37" s="20" t="inlineStr">
+        <is>
+          <t>CommonTree_2</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="21" t="inlineStr">
+        <is>
+          <t>TC4</t>
+        </is>
+      </c>
+      <c r="B38" s="20" t="inlineStr">
+        <is>
+          <t>CommonTree_4</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="21" t="inlineStr">
+        <is>
+          <t>TP1</t>
+        </is>
+      </c>
+      <c r="B39" s="20" t="inlineStr">
+        <is>
+          <t>Pine_1 (evergreen, dark, pointed)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="21" t="inlineStr">
+        <is>
+          <t>TP2</t>
+        </is>
+      </c>
+      <c r="B40" s="20" t="inlineStr">
+        <is>
+          <t>Pine_2 (evergreen)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="21" t="inlineStr">
+        <is>
+          <t>TP5</t>
+        </is>
+      </c>
+      <c r="B41" s="20" t="inlineStr">
+        <is>
+          <t>Pine_5 (evergreen, light)</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="21" t="inlineStr">
+        <is>
+          <t>TT5</t>
+        </is>
+      </c>
+      <c r="B42" s="20" t="inlineStr">
+        <is>
+          <t>TwistedTree_5 (compact twisted)</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
         <is>
           <t>T</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>Any tree - Claude picks a model that fits</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Any tree - Claude picks a model that fits. Leaf colours are chosen per tree by the build.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
         <is>
           <t>Rocks</t>
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="7" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="7" t="inlineStr">
         <is>
           <t>RM1</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
         <is>
           <t>Rock_Medium_1</t>
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="7" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="7" t="inlineStr">
         <is>
           <t>R</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
         <is>
           <t>Any rock - Claude picks</t>
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="5" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="5" t="inlineStr">
         <is>
           <t>Bushes &amp; plants</t>
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="8" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="8" t="inlineStr">
         <is>
           <t>BCO</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
         <is>
           <t>Bush_Common</t>
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="8" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="8" t="inlineStr">
         <is>
           <t>BCF</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
         <is>
           <t>Bush_Common_Flowers</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="8" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="8" t="inlineStr">
         <is>
           <t>BFE</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
         <is>
           <t>Fern_1</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="8" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="8" t="inlineStr">
         <is>
           <t>BFL</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
         <is>
           <t>Flower_3_Group</t>
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
         <is>
           <t>Walls &amp; ruins</t>
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="9" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="9" t="inlineStr">
         <is>
           <t>WUB</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
         <is>
           <t>Wall_UnevenBrick_Straight (ancient ruin wall)</t>
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="5" t="inlineStr">
         <is>
           <t>Vines</t>
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="10" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="10" t="inlineStr">
         <is>
           <t>VN1</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
         <is>
           <t>Prop_Vine1</t>
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="10" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="10" t="inlineStr">
         <is>
           <t>VN2</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
         <is>
           <t>Prop_Vine2</t>
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="5" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="5" t="inlineStr">
         <is>
           <t>Structures</t>
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="11" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="11" t="inlineStr">
         <is>
           <t>SHO</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
         <is>
           <t>House (1Story)</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="11" t="inlineStr">
-        <is>
-          <t>SCH</t>
-        </is>
-      </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>Charging station</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="11" t="inlineStr">
-        <is>
-          <t>SPS</t>
-        </is>
-      </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>Path stone</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="11" t="inlineStr">
-        <is>
-          <t>SC1</t>
-        </is>
-      </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>City building, small</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="11" t="inlineStr">
-        <is>
-          <t>SC2</t>
-        </is>
-      </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>City building, medium</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="11" t="inlineStr">
-        <is>
-          <t>SC3</t>
-        </is>
-      </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>City building, large</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="5" t="inlineStr">
-        <is>
-          <t>Markers</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="11" t="inlineStr">
         <is>
+          <t>SCH</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Charging station</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="11" t="inlineStr">
+        <is>
+          <t>SPS</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Path stone</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="11" t="inlineStr">
+        <is>
+          <t>SC1</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>City building, small</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="11" t="inlineStr">
+        <is>
+          <t>SC2</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>City building, medium</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="11" t="inlineStr">
+        <is>
+          <t>SC3</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>City building, large</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="5" t="inlineStr">
+        <is>
+          <t>Markers</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="11" t="inlineStr">
+        <is>
           <t>SPN</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
         <is>
           <t>Player spawn</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="12" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="12" t="inlineStr">
         <is>
           <t>P</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
         <is>
           <t>Path - keep clear, must stay drivable</t>
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="13" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="13" t="inlineStr">
         <is>
           <t>X</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
         <is>
           <t>Occupied by a large object - leave empty</t>
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="18" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="18" t="inlineStr">
         <is>
           <t>Collectibles</t>
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="19" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="19" t="inlineStr">
         <is>
           <t>CP1</t>
         </is>
       </c>
-      <c r="B63" s="20" t="inlineStr">
+      <c r="B69" s="20" t="inlineStr">
         <is>
           <t>Collectible part: Servo motor (placeholder)</t>
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="19" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="19" t="inlineStr">
         <is>
           <t>CP2</t>
         </is>
       </c>
-      <c r="B64" s="20" t="inlineStr">
+      <c r="B70" s="20" t="inlineStr">
         <is>
           <t>Collectible part: Optic lens (placeholder)</t>
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="19" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="19" t="inlineStr">
         <is>
           <t>CP3</t>
         </is>
       </c>
-      <c r="B65" s="20" t="inlineStr">
+      <c r="B71" s="20" t="inlineStr">
         <is>
           <t>Collectible part: Power cell (placeholder)</t>
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="19" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="19" t="inlineStr">
         <is>
           <t>CP4</t>
         </is>
       </c>
-      <c r="B66" s="20" t="inlineStr">
+      <c r="B72" s="20" t="inlineStr">
         <is>
           <t>Collectible part: Circuit board (placeholder)</t>
         </is>
@@ -1509,7 +1595,7 @@
       <c r="B2" s="17" t="n"/>
       <c r="C2" s="17" t="inlineStr">
         <is>
-          <t>TT2@30</t>
+          <t>TC4@30</t>
         </is>
       </c>
       <c r="D2" s="17" t="n"/>
@@ -1521,7 +1607,7 @@
       <c r="F2" s="17" t="n"/>
       <c r="G2" s="17" t="inlineStr">
         <is>
-          <t>TC3@60</t>
+          <t>TP2@60</t>
         </is>
       </c>
       <c r="H2" s="17" t="n"/>
@@ -1533,19 +1619,19 @@
       <c r="J2" s="17" t="n"/>
       <c r="K2" s="17" t="inlineStr">
         <is>
-          <t>TC5@75</t>
+          <t>TC2@75</t>
         </is>
       </c>
       <c r="L2" s="17" t="n"/>
       <c r="M2" s="17" t="inlineStr">
         <is>
-          <t>TD1@120</t>
+          <t>TC2@120</t>
         </is>
       </c>
       <c r="N2" s="17" t="n"/>
       <c r="O2" s="17" t="inlineStr">
         <is>
-          <t>TC5@90</t>
+          <t>TP1@90</t>
         </is>
       </c>
       <c r="P2" s="17" t="n"/>
@@ -1575,31 +1661,31 @@
       <c r="AN2" s="17" t="n"/>
       <c r="AO2" s="17" t="inlineStr">
         <is>
-          <t>TD1@150</t>
+          <t>TC1@150</t>
         </is>
       </c>
       <c r="AP2" s="17" t="n"/>
       <c r="AQ2" s="17" t="inlineStr">
         <is>
-          <t>TC3@105</t>
+          <t>TP5@105</t>
         </is>
       </c>
       <c r="AR2" s="17" t="n"/>
       <c r="AS2" s="17" t="inlineStr">
         <is>
-          <t>TC5@285</t>
+          <t>TC2@285</t>
         </is>
       </c>
       <c r="AT2" s="17" t="n"/>
       <c r="AU2" s="17" t="inlineStr">
         <is>
-          <t>TC1@105</t>
+          <t>TP2@105</t>
         </is>
       </c>
       <c r="AV2" s="17" t="n"/>
       <c r="AW2" s="17" t="inlineStr">
         <is>
-          <t>TT4@75</t>
+          <t>TP2@75</t>
         </is>
       </c>
     </row>
@@ -1609,31 +1695,31 @@
       </c>
       <c r="B3" s="17" t="inlineStr">
         <is>
-          <t>TC3@315</t>
+          <t>TC4@315</t>
         </is>
       </c>
       <c r="C3" s="17" t="n"/>
       <c r="D3" s="17" t="inlineStr">
         <is>
-          <t>TD1@240</t>
+          <t>TP2@240</t>
         </is>
       </c>
       <c r="E3" s="17" t="n"/>
       <c r="F3" s="17" t="inlineStr">
         <is>
-          <t>TT2@330</t>
+          <t>TP1@330</t>
         </is>
       </c>
       <c r="G3" s="17" t="n"/>
       <c r="H3" s="17" t="inlineStr">
         <is>
-          <t>TT4@15</t>
+          <t>TC3@15</t>
         </is>
       </c>
       <c r="I3" s="17" t="n"/>
       <c r="J3" s="17" t="inlineStr">
         <is>
-          <t>TT4@195</t>
+          <t>TC1@195</t>
         </is>
       </c>
       <c r="K3" s="17" t="n"/>
@@ -1645,13 +1731,13 @@
       <c r="M3" s="17" t="n"/>
       <c r="N3" s="17" t="inlineStr">
         <is>
-          <t>TC5@150</t>
+          <t>TP5@150</t>
         </is>
       </c>
       <c r="O3" s="17" t="n"/>
       <c r="P3" s="17" t="inlineStr">
         <is>
-          <t>TT4@195</t>
+          <t>TC1@195</t>
         </is>
       </c>
       <c r="Q3" s="17" t="n"/>
@@ -1679,13 +1765,13 @@
       <c r="AM3" s="17" t="n"/>
       <c r="AN3" s="17" t="inlineStr">
         <is>
-          <t>TT2@105</t>
+          <t>TP2@105</t>
         </is>
       </c>
       <c r="AO3" s="17" t="n"/>
       <c r="AP3" s="17" t="inlineStr">
         <is>
-          <t>TT2@210</t>
+          <t>TC1@210</t>
         </is>
       </c>
       <c r="AQ3" s="17" t="n"/>
@@ -1697,13 +1783,13 @@
       <c r="AS3" s="17" t="n"/>
       <c r="AT3" s="17" t="inlineStr">
         <is>
-          <t>TD1@300</t>
+          <t>TP1@300</t>
         </is>
       </c>
       <c r="AU3" s="17" t="n"/>
       <c r="AV3" s="17" t="inlineStr">
         <is>
-          <t>TD1@330</t>
+          <t>TC1@330</t>
         </is>
       </c>
       <c r="AW3" s="17" t="n"/>
@@ -1715,25 +1801,25 @@
       <c r="B4" s="17" t="n"/>
       <c r="C4" s="17" t="inlineStr">
         <is>
-          <t>TT2@150</t>
+          <t>TT4@150</t>
         </is>
       </c>
       <c r="D4" s="17" t="n"/>
       <c r="E4" s="17" t="inlineStr">
         <is>
-          <t>TT4@345</t>
+          <t>TT2@345</t>
         </is>
       </c>
       <c r="F4" s="17" t="n"/>
       <c r="G4" s="17" t="inlineStr">
         <is>
-          <t>TC3@15</t>
+          <t>TP2@15</t>
         </is>
       </c>
       <c r="H4" s="17" t="n"/>
       <c r="I4" s="17" t="inlineStr">
         <is>
-          <t>TC1@135</t>
+          <t>TC3@135</t>
         </is>
       </c>
       <c r="J4" s="17" t="n"/>
@@ -1745,13 +1831,13 @@
       <c r="L4" s="17" t="n"/>
       <c r="M4" s="17" t="inlineStr">
         <is>
-          <t>TC3@105</t>
+          <t>TP2@105</t>
         </is>
       </c>
       <c r="N4" s="17" t="n"/>
       <c r="O4" s="17" t="inlineStr">
         <is>
-          <t>TT2@75</t>
+          <t>TC5@75</t>
         </is>
       </c>
       <c r="P4" s="17" t="n"/>
@@ -1781,31 +1867,31 @@
       <c r="AN4" s="17" t="n"/>
       <c r="AO4" s="17" t="inlineStr">
         <is>
-          <t>TT2@135</t>
+          <t>TD1@135</t>
         </is>
       </c>
       <c r="AP4" s="17" t="n"/>
       <c r="AQ4" s="17" t="inlineStr">
         <is>
-          <t>TC5@225</t>
+          <t>TC3@225</t>
         </is>
       </c>
       <c r="AR4" s="17" t="n"/>
       <c r="AS4" s="17" t="inlineStr">
         <is>
-          <t>TC1@270</t>
+          <t>TP2@270</t>
         </is>
       </c>
       <c r="AT4" s="17" t="n"/>
       <c r="AU4" s="17" t="inlineStr">
         <is>
-          <t>TT2@15</t>
+          <t>TC3@15</t>
         </is>
       </c>
       <c r="AV4" s="17" t="n"/>
       <c r="AW4" s="17" t="inlineStr">
         <is>
-          <t>TC1@255</t>
+          <t>TC3@255</t>
         </is>
       </c>
     </row>
@@ -1815,49 +1901,49 @@
       </c>
       <c r="B5" s="17" t="inlineStr">
         <is>
-          <t>TC5@270</t>
+          <t>TT4@270</t>
         </is>
       </c>
       <c r="C5" s="17" t="n"/>
       <c r="D5" s="17" t="inlineStr">
         <is>
-          <t>TT4@195</t>
+          <t>TC2@195</t>
         </is>
       </c>
       <c r="E5" s="17" t="n"/>
       <c r="F5" s="17" t="inlineStr">
         <is>
-          <t>TD1@150</t>
+          <t>TC1@150</t>
         </is>
       </c>
       <c r="G5" s="17" t="n"/>
       <c r="H5" s="17" t="inlineStr">
         <is>
-          <t>TT2</t>
+          <t>TP2</t>
         </is>
       </c>
       <c r="I5" s="17" t="n"/>
       <c r="J5" s="17" t="inlineStr">
         <is>
-          <t>TC5@210</t>
+          <t>TC3@210</t>
         </is>
       </c>
       <c r="K5" s="17" t="n"/>
       <c r="L5" s="17" t="inlineStr">
         <is>
-          <t>TT4@240</t>
+          <t>TP2@240</t>
         </is>
       </c>
       <c r="M5" s="17" t="n"/>
       <c r="N5" s="17" t="inlineStr">
         <is>
-          <t>TC5@45</t>
+          <t>TP1@45</t>
         </is>
       </c>
       <c r="O5" s="17" t="n"/>
       <c r="P5" s="17" t="inlineStr">
         <is>
-          <t>TT4@105</t>
+          <t>TC2@105</t>
         </is>
       </c>
       <c r="Q5" s="17" t="n"/>
@@ -1885,31 +1971,31 @@
       <c r="AM5" s="17" t="n"/>
       <c r="AN5" s="17" t="inlineStr">
         <is>
-          <t>TT2@330</t>
+          <t>TP5@330</t>
         </is>
       </c>
       <c r="AO5" s="17" t="n"/>
       <c r="AP5" s="17" t="inlineStr">
         <is>
-          <t>TC5@105</t>
+          <t>TP1@105</t>
         </is>
       </c>
       <c r="AQ5" s="17" t="n"/>
       <c r="AR5" s="17" t="inlineStr">
         <is>
-          <t>TC5@330</t>
+          <t>TP2@330</t>
         </is>
       </c>
       <c r="AS5" s="17" t="n"/>
       <c r="AT5" s="17" t="inlineStr">
         <is>
-          <t>TT4@105</t>
+          <t>TC3@105</t>
         </is>
       </c>
       <c r="AU5" s="17" t="n"/>
       <c r="AV5" s="17" t="inlineStr">
         <is>
-          <t>TD1@180</t>
+          <t>TC5@180</t>
         </is>
       </c>
       <c r="AW5" s="17" t="n"/>
@@ -1921,13 +2007,13 @@
       <c r="B6" s="17" t="n"/>
       <c r="C6" s="17" t="inlineStr">
         <is>
-          <t>TD1@60</t>
+          <t>TC3@60</t>
         </is>
       </c>
       <c r="D6" s="17" t="n"/>
       <c r="E6" s="17" t="inlineStr">
         <is>
-          <t>TC5@120</t>
+          <t>TC1@120</t>
         </is>
       </c>
       <c r="F6" s="17" t="n"/>
@@ -1973,13 +2059,13 @@
       <c r="AT6" s="17" t="n"/>
       <c r="AU6" s="17" t="inlineStr">
         <is>
-          <t>TC3@105</t>
+          <t>TP2@105</t>
         </is>
       </c>
       <c r="AV6" s="17" t="n"/>
       <c r="AW6" s="17" t="inlineStr">
         <is>
-          <t>TC3@105</t>
+          <t>TC4@105</t>
         </is>
       </c>
     </row>
@@ -1989,13 +2075,13 @@
       </c>
       <c r="B7" s="17" t="inlineStr">
         <is>
-          <t>TT2@240</t>
+          <t>TC3@240</t>
         </is>
       </c>
       <c r="C7" s="17" t="n"/>
       <c r="D7" s="17" t="inlineStr">
         <is>
-          <t>TD1@105</t>
+          <t>TP2@105</t>
         </is>
       </c>
       <c r="E7" s="17" t="n"/>
@@ -2045,13 +2131,13 @@
       <c r="AS7" s="17" t="n"/>
       <c r="AT7" s="17" t="inlineStr">
         <is>
-          <t>TD1@285</t>
+          <t>TC4@285</t>
         </is>
       </c>
       <c r="AU7" s="17" t="n"/>
       <c r="AV7" s="17" t="inlineStr">
         <is>
-          <t>TC1@345</t>
+          <t>TP2@345</t>
         </is>
       </c>
       <c r="AW7" s="17" t="n"/>
@@ -2063,13 +2149,13 @@
       <c r="B8" s="17" t="n"/>
       <c r="C8" s="17" t="inlineStr">
         <is>
-          <t>TC3@195</t>
+          <t>TP1@195</t>
         </is>
       </c>
       <c r="D8" s="17" t="n"/>
       <c r="E8" s="17" t="inlineStr">
         <is>
-          <t>TT4@90</t>
+          <t>TP2@90</t>
         </is>
       </c>
       <c r="F8" s="17" t="n"/>
@@ -2115,13 +2201,13 @@
       <c r="AT8" s="17" t="n"/>
       <c r="AU8" s="17" t="inlineStr">
         <is>
-          <t>TC3@15</t>
+          <t>TC1@15</t>
         </is>
       </c>
       <c r="AV8" s="17" t="n"/>
       <c r="AW8" s="17" t="inlineStr">
         <is>
-          <t>TC1@270</t>
+          <t>TC2@270</t>
         </is>
       </c>
     </row>
@@ -2131,13 +2217,13 @@
       </c>
       <c r="B9" s="17" t="inlineStr">
         <is>
-          <t>TT4@120</t>
+          <t>TC1@120</t>
         </is>
       </c>
       <c r="C9" s="17" t="n"/>
       <c r="D9" s="17" t="inlineStr">
         <is>
-          <t>TC3@90</t>
+          <t>TD1@90</t>
         </is>
       </c>
       <c r="E9" s="17" t="n"/>
@@ -2183,13 +2269,13 @@
       <c r="AS9" s="17" t="n"/>
       <c r="AT9" s="17" t="inlineStr">
         <is>
-          <t>TC3@30</t>
+          <t>TP2@30</t>
         </is>
       </c>
       <c r="AU9" s="17" t="n"/>
       <c r="AV9" s="17" t="inlineStr">
         <is>
-          <t>TD1@165</t>
+          <t>TC3@165</t>
         </is>
       </c>
       <c r="AW9" s="17" t="n"/>
@@ -2201,7 +2287,7 @@
       <c r="B10" s="17" t="n"/>
       <c r="C10" s="17" t="inlineStr">
         <is>
-          <t>TD1@345</t>
+          <t>TP1@345</t>
         </is>
       </c>
       <c r="D10" s="17" t="n"/>
@@ -2253,13 +2339,13 @@
       <c r="AT10" s="17" t="n"/>
       <c r="AU10" s="17" t="inlineStr">
         <is>
-          <t>TD1@15</t>
+          <t>TT5@15</t>
         </is>
       </c>
       <c r="AV10" s="17" t="n"/>
       <c r="AW10" s="17" t="inlineStr">
         <is>
-          <t>TT4@240</t>
+          <t>TC4@240</t>
         </is>
       </c>
     </row>
@@ -2275,7 +2361,7 @@
       <c r="C11" s="17" t="n"/>
       <c r="D11" s="17" t="inlineStr">
         <is>
-          <t>TT2@60</t>
+          <t>TC5@60</t>
         </is>
       </c>
       <c r="E11" s="17" t="n"/>
@@ -2321,13 +2407,13 @@
       <c r="AS11" s="17" t="n"/>
       <c r="AT11" s="17" t="inlineStr">
         <is>
-          <t>TC3@150</t>
+          <t>TT2@150</t>
         </is>
       </c>
       <c r="AU11" s="17" t="n"/>
       <c r="AV11" s="17" t="inlineStr">
         <is>
-          <t>TC3@45</t>
+          <t>TP5@45</t>
         </is>
       </c>
       <c r="AW11" s="17" t="n"/>
@@ -2339,13 +2425,13 @@
       <c r="B12" s="17" t="n"/>
       <c r="C12" s="17" t="inlineStr">
         <is>
-          <t>TT2@255</t>
+          <t>TC3@255</t>
         </is>
       </c>
       <c r="D12" s="17" t="n"/>
       <c r="E12" s="17" t="inlineStr">
         <is>
-          <t>TT2@30</t>
+          <t>TP5@30</t>
         </is>
       </c>
       <c r="F12" s="17" t="n"/>
@@ -2391,13 +2477,13 @@
       <c r="AT12" s="17" t="n"/>
       <c r="AU12" s="17" t="inlineStr">
         <is>
-          <t>TT4@195</t>
+          <t>TP5@195</t>
         </is>
       </c>
       <c r="AV12" s="17" t="n"/>
       <c r="AW12" s="17" t="inlineStr">
         <is>
-          <t>TC3@225</t>
+          <t>TT2@225</t>
         </is>
       </c>
     </row>
@@ -2407,13 +2493,13 @@
       </c>
       <c r="B13" s="17" t="inlineStr">
         <is>
-          <t>TC1@240</t>
+          <t>TC2@240</t>
         </is>
       </c>
       <c r="C13" s="17" t="n"/>
       <c r="D13" s="17" t="inlineStr">
         <is>
-          <t>TT4@210</t>
+          <t>TC2@210</t>
         </is>
       </c>
       <c r="E13" s="17" t="n"/>
@@ -2459,13 +2545,13 @@
       <c r="AS13" s="17" t="n"/>
       <c r="AT13" s="17" t="inlineStr">
         <is>
-          <t>TT4@120</t>
+          <t>TP2@120</t>
         </is>
       </c>
       <c r="AU13" s="17" t="n"/>
       <c r="AV13" s="17" t="inlineStr">
         <is>
-          <t>TC1@285</t>
+          <t>TP2@285</t>
         </is>
       </c>
       <c r="AW13" s="17" t="n"/>
@@ -2477,13 +2563,13 @@
       <c r="B14" s="17" t="n"/>
       <c r="C14" s="17" t="inlineStr">
         <is>
-          <t>TT2@225</t>
+          <t>TC3@225</t>
         </is>
       </c>
       <c r="D14" s="17" t="n"/>
       <c r="E14" s="17" t="inlineStr">
         <is>
-          <t>TC3@60</t>
+          <t>TC2@60</t>
         </is>
       </c>
       <c r="F14" s="17" t="n"/>
@@ -2529,13 +2615,13 @@
       <c r="AT14" s="17" t="n"/>
       <c r="AU14" s="17" t="inlineStr">
         <is>
-          <t>TC5@285</t>
+          <t>TP5@285</t>
         </is>
       </c>
       <c r="AV14" s="17" t="n"/>
       <c r="AW14" s="17" t="inlineStr">
         <is>
-          <t>TC3@240</t>
+          <t>TC5@240</t>
         </is>
       </c>
     </row>
@@ -2545,13 +2631,13 @@
       </c>
       <c r="B15" s="17" t="inlineStr">
         <is>
-          <t>TC5@105</t>
+          <t>TC3@105</t>
         </is>
       </c>
       <c r="C15" s="17" t="n"/>
       <c r="D15" s="17" t="inlineStr">
         <is>
-          <t>TC3@210</t>
+          <t>TP2@210</t>
         </is>
       </c>
       <c r="E15" s="17" t="n"/>
@@ -2597,13 +2683,13 @@
       <c r="AS15" s="17" t="n"/>
       <c r="AT15" s="17" t="inlineStr">
         <is>
-          <t>TD1@60</t>
+          <t>TC5@60</t>
         </is>
       </c>
       <c r="AU15" s="17" t="n"/>
       <c r="AV15" s="17" t="inlineStr">
         <is>
-          <t>TD1@255</t>
+          <t>TC5@255</t>
         </is>
       </c>
       <c r="AW15" s="17" t="n"/>
@@ -2615,13 +2701,13 @@
       <c r="B16" s="17" t="n"/>
       <c r="C16" s="17" t="inlineStr">
         <is>
-          <t>TT4@30</t>
+          <t>TT5@30</t>
         </is>
       </c>
       <c r="D16" s="17" t="n"/>
       <c r="E16" s="17" t="inlineStr">
         <is>
-          <t>TT2@210</t>
+          <t>TC5@210</t>
         </is>
       </c>
       <c r="F16" s="17" t="n"/>
@@ -2667,13 +2753,13 @@
       <c r="AT16" s="17" t="n"/>
       <c r="AU16" s="17" t="inlineStr">
         <is>
-          <t>TT4@15</t>
+          <t>TT2@15</t>
         </is>
       </c>
       <c r="AV16" s="17" t="n"/>
       <c r="AW16" s="17" t="inlineStr">
         <is>
-          <t>TT2@135</t>
+          <t>TC5@135</t>
         </is>
       </c>
     </row>
@@ -2689,7 +2775,7 @@
       <c r="C17" s="17" t="n"/>
       <c r="D17" s="17" t="inlineStr">
         <is>
-          <t>TC3@30</t>
+          <t>TC5@30</t>
         </is>
       </c>
       <c r="E17" s="17" t="n"/>
@@ -2735,7 +2821,7 @@
       <c r="AS17" s="17" t="n"/>
       <c r="AT17" s="17" t="inlineStr">
         <is>
-          <t>TT2@225</t>
+          <t>TC1@225</t>
         </is>
       </c>
       <c r="AU17" s="17" t="n"/>
@@ -2753,13 +2839,13 @@
       <c r="B18" s="17" t="n"/>
       <c r="C18" s="17" t="inlineStr">
         <is>
-          <t>TC5@165</t>
+          <t>TC4@165</t>
         </is>
       </c>
       <c r="D18" s="17" t="n"/>
       <c r="E18" s="17" t="inlineStr">
         <is>
-          <t>TT4@75</t>
+          <t>TC5@75</t>
         </is>
       </c>
       <c r="F18" s="17" t="n"/>
@@ -2805,13 +2891,13 @@
       <c r="AT18" s="17" t="n"/>
       <c r="AU18" s="17" t="inlineStr">
         <is>
-          <t>TD1@45</t>
+          <t>TC2@45</t>
         </is>
       </c>
       <c r="AV18" s="17" t="n"/>
       <c r="AW18" s="17" t="inlineStr">
         <is>
-          <t>TT2@300</t>
+          <t>TP5@300</t>
         </is>
       </c>
     </row>
@@ -2821,13 +2907,13 @@
       </c>
       <c r="B19" s="17" t="inlineStr">
         <is>
-          <t>TD1@240</t>
+          <t>TC2@240</t>
         </is>
       </c>
       <c r="C19" s="17" t="n"/>
       <c r="D19" s="17" t="inlineStr">
         <is>
-          <t>TC3@315</t>
+          <t>TC2@315</t>
         </is>
       </c>
       <c r="E19" s="17" t="n"/>
@@ -2873,13 +2959,13 @@
       <c r="AS19" s="17" t="n"/>
       <c r="AT19" s="17" t="inlineStr">
         <is>
-          <t>TT4@135</t>
+          <t>TP1@135</t>
         </is>
       </c>
       <c r="AU19" s="17" t="n"/>
       <c r="AV19" s="17" t="inlineStr">
         <is>
-          <t>TD1@255</t>
+          <t>TC4@255</t>
         </is>
       </c>
       <c r="AW19" s="17" t="n"/>
@@ -2891,13 +2977,13 @@
       <c r="B20" s="17" t="n"/>
       <c r="C20" s="17" t="inlineStr">
         <is>
-          <t>TC5@240</t>
+          <t>TC1@240</t>
         </is>
       </c>
       <c r="D20" s="17" t="n"/>
       <c r="E20" s="17" t="inlineStr">
         <is>
-          <t>TT4@255</t>
+          <t>TT5@255</t>
         </is>
       </c>
       <c r="F20" s="17" t="n"/>
@@ -2943,13 +3029,13 @@
       <c r="AT20" s="17" t="n"/>
       <c r="AU20" s="17" t="inlineStr">
         <is>
-          <t>TT2@150</t>
+          <t>TC2@150</t>
         </is>
       </c>
       <c r="AV20" s="17" t="n"/>
       <c r="AW20" s="17" t="inlineStr">
         <is>
-          <t>TT2@120</t>
+          <t>TC3@120</t>
         </is>
       </c>
     </row>
@@ -2959,13 +3045,13 @@
       </c>
       <c r="B21" s="17" t="inlineStr">
         <is>
-          <t>TT4@345</t>
+          <t>TC2@345</t>
         </is>
       </c>
       <c r="C21" s="17" t="n"/>
       <c r="D21" s="17" t="inlineStr">
         <is>
-          <t>TT2@240</t>
+          <t>TC4@240</t>
         </is>
       </c>
       <c r="E21" s="17" t="n"/>
@@ -3015,13 +3101,13 @@
       <c r="AS21" s="17" t="n"/>
       <c r="AT21" s="17" t="inlineStr">
         <is>
-          <t>TC5@15</t>
+          <t>TP2@15</t>
         </is>
       </c>
       <c r="AU21" s="17" t="n"/>
       <c r="AV21" s="17" t="inlineStr">
         <is>
-          <t>TT4</t>
+          <t>TC1</t>
         </is>
       </c>
       <c r="AW21" s="17" t="n"/>
@@ -3033,13 +3119,13 @@
       <c r="B22" s="17" t="n"/>
       <c r="C22" s="17" t="inlineStr">
         <is>
-          <t>TT4@315</t>
+          <t>TC2@315</t>
         </is>
       </c>
       <c r="D22" s="17" t="n"/>
       <c r="E22" s="17" t="inlineStr">
         <is>
-          <t>TT2@345</t>
+          <t>TC1@345</t>
         </is>
       </c>
       <c r="F22" s="17" t="n"/>
@@ -3085,13 +3171,13 @@
       <c r="AT22" s="17" t="n"/>
       <c r="AU22" s="17" t="inlineStr">
         <is>
-          <t>TD1@60</t>
+          <t>TC5@60</t>
         </is>
       </c>
       <c r="AV22" s="17" t="n"/>
       <c r="AW22" s="17" t="inlineStr">
         <is>
-          <t>TC1@330</t>
+          <t>TC3@330</t>
         </is>
       </c>
     </row>
@@ -3101,13 +3187,13 @@
       </c>
       <c r="B23" s="17" t="inlineStr">
         <is>
-          <t>TT4@270</t>
+          <t>TC2@270</t>
         </is>
       </c>
       <c r="C23" s="17" t="n"/>
       <c r="D23" s="17" t="inlineStr">
         <is>
-          <t>TT4@180</t>
+          <t>TP5@180</t>
         </is>
       </c>
       <c r="E23" s="17" t="n"/>
@@ -3153,13 +3239,13 @@
       <c r="AS23" s="17" t="n"/>
       <c r="AT23" s="17" t="inlineStr">
         <is>
-          <t>TT4@45</t>
+          <t>TP2@45</t>
         </is>
       </c>
       <c r="AU23" s="17" t="n"/>
       <c r="AV23" s="17" t="inlineStr">
         <is>
-          <t>TD1@45</t>
+          <t>TC4@45</t>
         </is>
       </c>
       <c r="AW23" s="17" t="n"/>
@@ -3171,13 +3257,13 @@
       <c r="B24" s="17" t="n"/>
       <c r="C24" s="17" t="inlineStr">
         <is>
-          <t>TT2@135</t>
+          <t>TP1@135</t>
         </is>
       </c>
       <c r="D24" s="17" t="n"/>
       <c r="E24" s="17" t="inlineStr">
         <is>
-          <t>TD1@240</t>
+          <t>TC4@240</t>
         </is>
       </c>
       <c r="F24" s="17" t="n"/>
@@ -3227,7 +3313,7 @@
       <c r="AT24" s="17" t="n"/>
       <c r="AU24" s="17" t="inlineStr">
         <is>
-          <t>TT4@45</t>
+          <t>TC2@45</t>
         </is>
       </c>
       <c r="AV24" s="17" t="n"/>
@@ -3243,13 +3329,13 @@
       </c>
       <c r="B25" s="17" t="inlineStr">
         <is>
-          <t>TT2@120</t>
+          <t>TP5@120</t>
         </is>
       </c>
       <c r="C25" s="17" t="n"/>
       <c r="D25" s="17" t="inlineStr">
         <is>
-          <t>TC5@60</t>
+          <t>TD1@60</t>
         </is>
       </c>
       <c r="E25" s="17" t="n"/>
@@ -3295,7 +3381,7 @@
       <c r="AS25" s="17" t="n"/>
       <c r="AT25" s="17" t="inlineStr">
         <is>
-          <t>TT4@330</t>
+          <t>TC4@330</t>
         </is>
       </c>
       <c r="AU25" s="17" t="n"/>
@@ -3313,13 +3399,13 @@
       <c r="B26" s="17" t="n"/>
       <c r="C26" s="17" t="inlineStr">
         <is>
-          <t>TC5@45</t>
+          <t>TT5@45</t>
         </is>
       </c>
       <c r="D26" s="17" t="n"/>
       <c r="E26" s="17" t="inlineStr">
         <is>
-          <t>TC3@330</t>
+          <t>TT5@330</t>
         </is>
       </c>
       <c r="F26" s="17" t="n"/>
@@ -3365,13 +3451,13 @@
       <c r="AT26" s="17" t="n"/>
       <c r="AU26" s="17" t="inlineStr">
         <is>
-          <t>TC5@90</t>
+          <t>TP5@90</t>
         </is>
       </c>
       <c r="AV26" s="17" t="n"/>
       <c r="AW26" s="17" t="inlineStr">
         <is>
-          <t>TT4@195</t>
+          <t>TP2@195</t>
         </is>
       </c>
     </row>
@@ -3381,13 +3467,13 @@
       </c>
       <c r="B27" s="17" t="inlineStr">
         <is>
-          <t>TC5@150</t>
+          <t>TP2@150</t>
         </is>
       </c>
       <c r="C27" s="17" t="n"/>
       <c r="D27" s="17" t="inlineStr">
         <is>
-          <t>TC3@210</t>
+          <t>TP1@210</t>
         </is>
       </c>
       <c r="E27" s="17" t="n"/>
@@ -3433,13 +3519,13 @@
       <c r="AS27" s="17" t="n"/>
       <c r="AT27" s="17" t="inlineStr">
         <is>
-          <t>TC3@30</t>
+          <t>TC2@30</t>
         </is>
       </c>
       <c r="AU27" s="17" t="n"/>
       <c r="AV27" s="17" t="inlineStr">
         <is>
-          <t>TT2@135</t>
+          <t>TP1@135</t>
         </is>
       </c>
       <c r="AW27" s="17" t="n"/>
@@ -3451,13 +3537,13 @@
       <c r="B28" s="17" t="n"/>
       <c r="C28" s="17" t="inlineStr">
         <is>
-          <t>TC5@135</t>
+          <t>TC3@135</t>
         </is>
       </c>
       <c r="D28" s="17" t="n"/>
       <c r="E28" s="17" t="inlineStr">
         <is>
-          <t>TC3@30</t>
+          <t>TC1@30</t>
         </is>
       </c>
       <c r="F28" s="17" t="n"/>
@@ -3509,7 +3595,7 @@
       <c r="AV28" s="17" t="n"/>
       <c r="AW28" s="17" t="inlineStr">
         <is>
-          <t>TC1@90</t>
+          <t>TP2@90</t>
         </is>
       </c>
     </row>
@@ -3519,13 +3605,13 @@
       </c>
       <c r="B29" s="17" t="inlineStr">
         <is>
-          <t>TD1@210</t>
+          <t>TP1@210</t>
         </is>
       </c>
       <c r="C29" s="17" t="n"/>
       <c r="D29" s="17" t="inlineStr">
         <is>
-          <t>TC5@165</t>
+          <t>TT2@165</t>
         </is>
       </c>
       <c r="E29" s="17" t="n"/>
@@ -3571,13 +3657,13 @@
       <c r="AS29" s="17" t="n"/>
       <c r="AT29" s="17" t="inlineStr">
         <is>
-          <t>TD1@300</t>
+          <t>TC3@300</t>
         </is>
       </c>
       <c r="AU29" s="17" t="n"/>
       <c r="AV29" s="17" t="inlineStr">
         <is>
-          <t>TC5@330</t>
+          <t>TP5@330</t>
         </is>
       </c>
       <c r="AW29" s="17" t="n"/>
@@ -3589,13 +3675,13 @@
       <c r="B30" s="17" t="n"/>
       <c r="C30" s="17" t="inlineStr">
         <is>
-          <t>TC3@225</t>
+          <t>TP1@225</t>
         </is>
       </c>
       <c r="D30" s="17" t="n"/>
       <c r="E30" s="17" t="inlineStr">
         <is>
-          <t>TT4@195</t>
+          <t>TC5@195</t>
         </is>
       </c>
       <c r="F30" s="17" t="n"/>
@@ -3641,13 +3727,13 @@
       <c r="AT30" s="17" t="n"/>
       <c r="AU30" s="17" t="inlineStr">
         <is>
-          <t>TD1@150</t>
+          <t>TC4@150</t>
         </is>
       </c>
       <c r="AV30" s="17" t="n"/>
       <c r="AW30" s="17" t="inlineStr">
         <is>
-          <t>TT4@120</t>
+          <t>TC3@120</t>
         </is>
       </c>
     </row>
@@ -3657,13 +3743,13 @@
       </c>
       <c r="B31" s="17" t="inlineStr">
         <is>
-          <t>TD1@30</t>
+          <t>TC5@30</t>
         </is>
       </c>
       <c r="C31" s="17" t="n"/>
       <c r="D31" s="17" t="inlineStr">
         <is>
-          <t>TC5@255</t>
+          <t>TP1@255</t>
         </is>
       </c>
       <c r="E31" s="17" t="n"/>
@@ -3709,13 +3795,13 @@
       <c r="AS31" s="17" t="n"/>
       <c r="AT31" s="17" t="inlineStr">
         <is>
-          <t>TC5@30</t>
+          <t>TD1@30</t>
         </is>
       </c>
       <c r="AU31" s="17" t="n"/>
       <c r="AV31" s="17" t="inlineStr">
         <is>
-          <t>TT2@75</t>
+          <t>TP2@75</t>
         </is>
       </c>
       <c r="AW31" s="17" t="n"/>
@@ -3727,13 +3813,13 @@
       <c r="B32" s="17" t="n"/>
       <c r="C32" s="17" t="inlineStr">
         <is>
-          <t>TD1@150</t>
+          <t>TP1@150</t>
         </is>
       </c>
       <c r="D32" s="17" t="n"/>
       <c r="E32" s="17" t="inlineStr">
         <is>
-          <t>TD1@315</t>
+          <t>TT2@315</t>
         </is>
       </c>
       <c r="F32" s="17" t="n"/>
@@ -3779,13 +3865,13 @@
       <c r="AT32" s="17" t="n"/>
       <c r="AU32" s="17" t="inlineStr">
         <is>
-          <t>TT2@225</t>
+          <t>TC3@225</t>
         </is>
       </c>
       <c r="AV32" s="17" t="n"/>
       <c r="AW32" s="17" t="inlineStr">
         <is>
-          <t>TT4@135</t>
+          <t>TC4@135</t>
         </is>
       </c>
     </row>
@@ -3795,13 +3881,13 @@
       </c>
       <c r="B33" s="17" t="inlineStr">
         <is>
-          <t>TC3@285</t>
+          <t>TC5@285</t>
         </is>
       </c>
       <c r="C33" s="17" t="n"/>
       <c r="D33" s="17" t="inlineStr">
         <is>
-          <t>TT2@255</t>
+          <t>TP1@255</t>
         </is>
       </c>
       <c r="E33" s="17" t="n"/>
@@ -3853,7 +3939,7 @@
       <c r="AU33" s="17" t="n"/>
       <c r="AV33" s="17" t="inlineStr">
         <is>
-          <t>TC5@45</t>
+          <t>TD1@45</t>
         </is>
       </c>
       <c r="AW33" s="17" t="n"/>
@@ -3865,13 +3951,13 @@
       <c r="B34" s="17" t="n"/>
       <c r="C34" s="17" t="inlineStr">
         <is>
-          <t>TD1@150</t>
+          <t>TP1@150</t>
         </is>
       </c>
       <c r="D34" s="17" t="n"/>
       <c r="E34" s="17" t="inlineStr">
         <is>
-          <t>TC3@90</t>
+          <t>TT4@90</t>
         </is>
       </c>
       <c r="F34" s="17" t="n"/>
@@ -3917,13 +4003,13 @@
       <c r="AT34" s="17" t="n"/>
       <c r="AU34" s="17" t="inlineStr">
         <is>
-          <t>TC1@90</t>
+          <t>TP5@90</t>
         </is>
       </c>
       <c r="AV34" s="17" t="n"/>
       <c r="AW34" s="17" t="inlineStr">
         <is>
-          <t>TT4@270</t>
+          <t>TP5@270</t>
         </is>
       </c>
     </row>
@@ -3933,13 +4019,13 @@
       </c>
       <c r="B35" s="17" t="inlineStr">
         <is>
-          <t>TT2@120</t>
+          <t>TC4@120</t>
         </is>
       </c>
       <c r="C35" s="17" t="n"/>
       <c r="D35" s="17" t="inlineStr">
         <is>
-          <t>TT4@315</t>
+          <t>TC1@315</t>
         </is>
       </c>
       <c r="E35" s="17" t="n"/>
@@ -3985,13 +4071,13 @@
       <c r="AS35" s="17" t="n"/>
       <c r="AT35" s="17" t="inlineStr">
         <is>
-          <t>TC3@150</t>
+          <t>TP2@150</t>
         </is>
       </c>
       <c r="AU35" s="17" t="n"/>
       <c r="AV35" s="17" t="inlineStr">
         <is>
-          <t>TD1@255</t>
+          <t>TP5@255</t>
         </is>
       </c>
       <c r="AW35" s="17" t="n"/>
@@ -4003,13 +4089,13 @@
       <c r="B36" s="17" t="n"/>
       <c r="C36" s="17" t="inlineStr">
         <is>
-          <t>TD1@75</t>
+          <t>TP5@75</t>
         </is>
       </c>
       <c r="D36" s="17" t="n"/>
       <c r="E36" s="17" t="inlineStr">
         <is>
-          <t>TD1@225</t>
+          <t>TT5@225</t>
         </is>
       </c>
       <c r="F36" s="17" t="n"/>
@@ -4055,13 +4141,13 @@
       <c r="AT36" s="17" t="n"/>
       <c r="AU36" s="17" t="inlineStr">
         <is>
-          <t>TT4</t>
+          <t>TC4</t>
         </is>
       </c>
       <c r="AV36" s="17" t="n"/>
       <c r="AW36" s="17" t="inlineStr">
         <is>
-          <t>TT4@165</t>
+          <t>TC2@165</t>
         </is>
       </c>
     </row>
@@ -4071,13 +4157,13 @@
       </c>
       <c r="B37" s="17" t="inlineStr">
         <is>
-          <t>TD1@210</t>
+          <t>TC2@210</t>
         </is>
       </c>
       <c r="C37" s="17" t="n"/>
       <c r="D37" s="17" t="inlineStr">
         <is>
-          <t>TC3@270</t>
+          <t>TC2@270</t>
         </is>
       </c>
       <c r="E37" s="17" t="n"/>
@@ -4123,13 +4209,13 @@
       <c r="AS37" s="17" t="n"/>
       <c r="AT37" s="17" t="inlineStr">
         <is>
-          <t>TC3@165</t>
+          <t>TP5@165</t>
         </is>
       </c>
       <c r="AU37" s="17" t="n"/>
       <c r="AV37" s="17" t="inlineStr">
         <is>
-          <t>TD1@330</t>
+          <t>TC2@330</t>
         </is>
       </c>
       <c r="AW37" s="17" t="n"/>
@@ -4141,13 +4227,13 @@
       <c r="B38" s="17" t="n"/>
       <c r="C38" s="17" t="inlineStr">
         <is>
-          <t>TD1@180</t>
+          <t>TC1@180</t>
         </is>
       </c>
       <c r="D38" s="17" t="n"/>
       <c r="E38" s="17" t="inlineStr">
         <is>
-          <t>TC3@105</t>
+          <t>TP2@105</t>
         </is>
       </c>
       <c r="F38" s="17" t="n"/>
@@ -4193,13 +4279,13 @@
       <c r="AT38" s="17" t="n"/>
       <c r="AU38" s="17" t="inlineStr">
         <is>
-          <t>TT2@195</t>
+          <t>TP5@195</t>
         </is>
       </c>
       <c r="AV38" s="17" t="n"/>
       <c r="AW38" s="17" t="inlineStr">
         <is>
-          <t>TT2@300</t>
+          <t>TD1@300</t>
         </is>
       </c>
     </row>
@@ -4209,13 +4295,13 @@
       </c>
       <c r="B39" s="17" t="inlineStr">
         <is>
-          <t>TT2@195</t>
+          <t>TC1@195</t>
         </is>
       </c>
       <c r="C39" s="17" t="n"/>
       <c r="D39" s="17" t="inlineStr">
         <is>
-          <t>TT4@315</t>
+          <t>TP2@315</t>
         </is>
       </c>
       <c r="E39" s="17" t="n"/>
@@ -4261,13 +4347,13 @@
       <c r="AS39" s="17" t="n"/>
       <c r="AT39" s="17" t="inlineStr">
         <is>
-          <t>TT4@30</t>
+          <t>TC5@30</t>
         </is>
       </c>
       <c r="AU39" s="17" t="n"/>
       <c r="AV39" s="17" t="inlineStr">
         <is>
-          <t>TD1@15</t>
+          <t>TT2@15</t>
         </is>
       </c>
       <c r="AW39" s="17" t="n"/>
@@ -4279,13 +4365,13 @@
       <c r="B40" s="17" t="n"/>
       <c r="C40" s="17" t="inlineStr">
         <is>
-          <t>TC1@255</t>
+          <t>TC5@255</t>
         </is>
       </c>
       <c r="D40" s="17" t="n"/>
       <c r="E40" s="17" t="inlineStr">
         <is>
-          <t>TC1@195</t>
+          <t>TP1@195</t>
         </is>
       </c>
       <c r="F40" s="17" t="n"/>
@@ -4331,13 +4417,13 @@
       <c r="AT40" s="17" t="n"/>
       <c r="AU40" s="17" t="inlineStr">
         <is>
-          <t>TC5@210</t>
+          <t>TT4@210</t>
         </is>
       </c>
       <c r="AV40" s="17" t="n"/>
       <c r="AW40" s="17" t="inlineStr">
         <is>
-          <t>TC5@225</t>
+          <t>TT5@225</t>
         </is>
       </c>
     </row>
@@ -4347,13 +4433,13 @@
       </c>
       <c r="B41" s="17" t="inlineStr">
         <is>
-          <t>TT4@255</t>
+          <t>TD1@255</t>
         </is>
       </c>
       <c r="C41" s="17" t="n"/>
       <c r="D41" s="17" t="inlineStr">
         <is>
-          <t>TC3@60</t>
+          <t>TP2@60</t>
         </is>
       </c>
       <c r="E41" s="17" t="n"/>
@@ -4399,13 +4485,13 @@
       <c r="AS41" s="17" t="n"/>
       <c r="AT41" s="17" t="inlineStr">
         <is>
-          <t>TC5@180</t>
+          <t>TC3@180</t>
         </is>
       </c>
       <c r="AU41" s="17" t="n"/>
       <c r="AV41" s="17" t="inlineStr">
         <is>
-          <t>TT4@300</t>
+          <t>TC5@300</t>
         </is>
       </c>
       <c r="AW41" s="17" t="n"/>
@@ -4417,13 +4503,13 @@
       <c r="B42" s="17" t="n"/>
       <c r="C42" s="17" t="inlineStr">
         <is>
-          <t>TT4@15</t>
+          <t>TC3@15</t>
         </is>
       </c>
       <c r="D42" s="17" t="n"/>
       <c r="E42" s="17" t="inlineStr">
         <is>
-          <t>TT4@105</t>
+          <t>TT5@105</t>
         </is>
       </c>
       <c r="F42" s="17" t="n"/>
@@ -4469,13 +4555,13 @@
       <c r="AT42" s="17" t="n"/>
       <c r="AU42" s="17" t="inlineStr">
         <is>
-          <t>TC1@75</t>
+          <t>TP5@75</t>
         </is>
       </c>
       <c r="AV42" s="17" t="n"/>
       <c r="AW42" s="17" t="inlineStr">
         <is>
-          <t>TC3@150</t>
+          <t>TC5@150</t>
         </is>
       </c>
     </row>
@@ -4485,13 +4571,13 @@
       </c>
       <c r="B43" s="17" t="inlineStr">
         <is>
-          <t>TT4@75</t>
+          <t>TC2@75</t>
         </is>
       </c>
       <c r="C43" s="17" t="n"/>
       <c r="D43" s="17" t="inlineStr">
         <is>
-          <t>TD1@270</t>
+          <t>TP5@270</t>
         </is>
       </c>
       <c r="E43" s="17" t="n"/>
@@ -4537,13 +4623,13 @@
       <c r="AS43" s="17" t="n"/>
       <c r="AT43" s="17" t="inlineStr">
         <is>
-          <t>TC5@195</t>
+          <t>TT2@195</t>
         </is>
       </c>
       <c r="AU43" s="17" t="n"/>
       <c r="AV43" s="17" t="inlineStr">
         <is>
-          <t>TC5@315</t>
+          <t>TC4@315</t>
         </is>
       </c>
       <c r="AW43" s="17" t="n"/>
@@ -4555,13 +4641,13 @@
       <c r="B44" s="17" t="n"/>
       <c r="C44" s="17" t="inlineStr">
         <is>
-          <t>TC5@225</t>
+          <t>TC1@225</t>
         </is>
       </c>
       <c r="D44" s="17" t="n"/>
       <c r="E44" s="17" t="inlineStr">
         <is>
-          <t>TC5@195</t>
+          <t>TC1@195</t>
         </is>
       </c>
       <c r="F44" s="17" t="n"/>
@@ -4607,13 +4693,13 @@
       <c r="AT44" s="17" t="n"/>
       <c r="AU44" s="17" t="inlineStr">
         <is>
-          <t>TC3@210</t>
+          <t>TP2@210</t>
         </is>
       </c>
       <c r="AV44" s="17" t="n"/>
       <c r="AW44" s="17" t="inlineStr">
         <is>
-          <t>TC5@180</t>
+          <t>TC3@180</t>
         </is>
       </c>
     </row>
@@ -4629,7 +4715,7 @@
       <c r="C45" s="17" t="n"/>
       <c r="D45" s="17" t="inlineStr">
         <is>
-          <t>TT4@60</t>
+          <t>TP2@60</t>
         </is>
       </c>
       <c r="E45" s="17" t="n"/>
@@ -4675,13 +4761,13 @@
       <c r="AS45" s="17" t="n"/>
       <c r="AT45" s="17" t="inlineStr">
         <is>
-          <t>TC5@345</t>
+          <t>TP2@345</t>
         </is>
       </c>
       <c r="AU45" s="17" t="n"/>
       <c r="AV45" s="17" t="inlineStr">
         <is>
-          <t>TC5@180</t>
+          <t>TC2@180</t>
         </is>
       </c>
       <c r="AW45" s="17" t="n"/>
@@ -4693,13 +4779,13 @@
       <c r="B46" s="17" t="n"/>
       <c r="C46" s="17" t="inlineStr">
         <is>
-          <t>TT2@15</t>
+          <t>TP5@15</t>
         </is>
       </c>
       <c r="D46" s="17" t="n"/>
       <c r="E46" s="17" t="inlineStr">
         <is>
-          <t>TC1@60</t>
+          <t>TC3@60</t>
         </is>
       </c>
       <c r="F46" s="17" t="n"/>
@@ -4759,7 +4845,7 @@
       <c r="AV46" s="17" t="n"/>
       <c r="AW46" s="17" t="inlineStr">
         <is>
-          <t>TC3@330</t>
+          <t>TC4@330</t>
         </is>
       </c>
     </row>
@@ -4769,43 +4855,43 @@
       </c>
       <c r="B47" s="17" t="inlineStr">
         <is>
-          <t>TC3@285</t>
+          <t>TD1@285</t>
         </is>
       </c>
       <c r="C47" s="17" t="n"/>
       <c r="D47" s="17" t="inlineStr">
         <is>
-          <t>TC3@75</t>
+          <t>TP2@75</t>
         </is>
       </c>
       <c r="E47" s="17" t="n"/>
       <c r="F47" s="17" t="inlineStr">
         <is>
-          <t>TC3@330</t>
+          <t>TC5@330</t>
         </is>
       </c>
       <c r="G47" s="17" t="n"/>
       <c r="H47" s="17" t="inlineStr">
         <is>
-          <t>TT4@120</t>
+          <t>TC2@120</t>
         </is>
       </c>
       <c r="I47" s="17" t="n"/>
       <c r="J47" s="17" t="inlineStr">
         <is>
-          <t>TC3@90</t>
+          <t>TC2@90</t>
         </is>
       </c>
       <c r="K47" s="17" t="n"/>
       <c r="L47" s="17" t="inlineStr">
         <is>
-          <t>TC3@195</t>
+          <t>TP5@195</t>
         </is>
       </c>
       <c r="M47" s="17" t="n"/>
       <c r="N47" s="17" t="inlineStr">
         <is>
-          <t>TC1@135</t>
+          <t>TC3@135</t>
         </is>
       </c>
       <c r="O47" s="17" t="n"/>
@@ -4823,79 +4909,79 @@
       <c r="W47" s="17" t="n"/>
       <c r="X47" s="17" t="inlineStr">
         <is>
-          <t>TD1@255</t>
+          <t>TC3@255</t>
         </is>
       </c>
       <c r="Y47" s="17" t="n"/>
       <c r="Z47" s="17" t="inlineStr">
         <is>
-          <t>TC5@300</t>
+          <t>TT5@300</t>
         </is>
       </c>
       <c r="AA47" s="17" t="n"/>
       <c r="AB47" s="17" t="inlineStr">
         <is>
-          <t>TT4@285</t>
+          <t>TP1@285</t>
         </is>
       </c>
       <c r="AC47" s="17" t="n"/>
       <c r="AD47" s="17" t="inlineStr">
         <is>
-          <t>TC3@300</t>
+          <t>TC5@300</t>
         </is>
       </c>
       <c r="AE47" s="17" t="n"/>
       <c r="AF47" s="17" t="inlineStr">
         <is>
-          <t>TC5@180</t>
+          <t>TP2@180</t>
         </is>
       </c>
       <c r="AG47" s="17" t="n"/>
       <c r="AH47" s="17" t="inlineStr">
         <is>
-          <t>TT4@135</t>
+          <t>TC1@135</t>
         </is>
       </c>
       <c r="AI47" s="17" t="n"/>
       <c r="AJ47" s="17" t="inlineStr">
         <is>
-          <t>TT4@315</t>
+          <t>TC4@315</t>
         </is>
       </c>
       <c r="AK47" s="17" t="n"/>
       <c r="AL47" s="17" t="inlineStr">
         <is>
-          <t>TD1@225</t>
+          <t>TC3@225</t>
         </is>
       </c>
       <c r="AM47" s="17" t="n"/>
       <c r="AN47" s="17" t="inlineStr">
         <is>
-          <t>TD1@135</t>
+          <t>TC1@135</t>
         </is>
       </c>
       <c r="AO47" s="17" t="n"/>
       <c r="AP47" s="17" t="inlineStr">
         <is>
-          <t>TT2@210</t>
+          <t>TP1@210</t>
         </is>
       </c>
       <c r="AQ47" s="17" t="n"/>
       <c r="AR47" s="17" t="inlineStr">
         <is>
-          <t>TC3@330</t>
+          <t>TC2@330</t>
         </is>
       </c>
       <c r="AS47" s="17" t="n"/>
       <c r="AT47" s="17" t="inlineStr">
         <is>
-          <t>TC5@210</t>
+          <t>TP5@210</t>
         </is>
       </c>
       <c r="AU47" s="17" t="n"/>
       <c r="AV47" s="17" t="inlineStr">
         <is>
-          <t>TD1@225</t>
+          <t>TP1@225</t>
         </is>
       </c>
       <c r="AW47" s="17" t="n"/>
@@ -4907,37 +4993,37 @@
       <c r="B48" s="17" t="n"/>
       <c r="C48" s="17" t="inlineStr">
         <is>
-          <t>TC5</t>
+          <t>TP2</t>
         </is>
       </c>
       <c r="D48" s="17" t="n"/>
       <c r="E48" s="17" t="inlineStr">
         <is>
-          <t>TD1@60</t>
+          <t>TC5@60</t>
         </is>
       </c>
       <c r="F48" s="17" t="n"/>
       <c r="G48" s="17" t="inlineStr">
         <is>
-          <t>TT4</t>
+          <t>TP2</t>
         </is>
       </c>
       <c r="H48" s="17" t="n"/>
       <c r="I48" s="17" t="inlineStr">
         <is>
-          <t>TD1@120</t>
+          <t>TP2@120</t>
         </is>
       </c>
       <c r="J48" s="17" t="n"/>
       <c r="K48" s="17" t="inlineStr">
         <is>
-          <t>TT4@300</t>
+          <t>TC4@300</t>
         </is>
       </c>
       <c r="L48" s="17" t="n"/>
       <c r="M48" s="17" t="inlineStr">
         <is>
-          <t>TC1@330</t>
+          <t>TP2@330</t>
         </is>
       </c>
       <c r="N48" s="17" t="n"/>
@@ -4953,25 +5039,25 @@
       <c r="T48" s="17" t="n"/>
       <c r="U48" s="17" t="inlineStr">
         <is>
-          <t>TC3@105</t>
+          <t>TC2@105</t>
         </is>
       </c>
       <c r="V48" s="17" t="n"/>
       <c r="W48" s="17" t="inlineStr">
         <is>
-          <t>TT2@240</t>
+          <t>TD1@240</t>
         </is>
       </c>
       <c r="X48" s="17" t="n"/>
       <c r="Y48" s="17" t="inlineStr">
         <is>
-          <t>TT4@120</t>
+          <t>TC2@120</t>
         </is>
       </c>
       <c r="Z48" s="17" t="n"/>
       <c r="AA48" s="17" t="inlineStr">
         <is>
-          <t>TC3@225</t>
+          <t>TP2@225</t>
         </is>
       </c>
       <c r="AB48" s="17" t="n"/>
@@ -4983,49 +5069,49 @@
       <c r="AD48" s="17" t="n"/>
       <c r="AE48" s="17" t="inlineStr">
         <is>
-          <t>TC5@240</t>
+          <t>TP2@240</t>
         </is>
       </c>
       <c r="AF48" s="17" t="n"/>
       <c r="AG48" s="17" t="inlineStr">
         <is>
-          <t>TC3@105</t>
+          <t>TC1@105</t>
         </is>
       </c>
       <c r="AH48" s="17" t="n"/>
       <c r="AI48" s="17" t="inlineStr">
         <is>
-          <t>TD1@330</t>
+          <t>TC1@330</t>
         </is>
       </c>
       <c r="AJ48" s="17" t="n"/>
       <c r="AK48" s="17" t="inlineStr">
         <is>
-          <t>TT4@330</t>
+          <t>TC1@330</t>
         </is>
       </c>
       <c r="AL48" s="17" t="n"/>
       <c r="AM48" s="17" t="inlineStr">
         <is>
-          <t>TT4@195</t>
+          <t>TC5@195</t>
         </is>
       </c>
       <c r="AN48" s="17" t="n"/>
       <c r="AO48" s="17" t="inlineStr">
         <is>
-          <t>TT2@285</t>
+          <t>TP2@285</t>
         </is>
       </c>
       <c r="AP48" s="17" t="n"/>
       <c r="AQ48" s="17" t="inlineStr">
         <is>
-          <t>TT2@45</t>
+          <t>TC4@45</t>
         </is>
       </c>
       <c r="AR48" s="17" t="n"/>
       <c r="AS48" s="17" t="inlineStr">
         <is>
-          <t>TC5@345</t>
+          <t>TC1@345</t>
         </is>
       </c>
       <c r="AT48" s="17" t="n"/>
@@ -5047,7 +5133,7 @@
       </c>
       <c r="B49" s="17" t="inlineStr">
         <is>
-          <t>TT2@315</t>
+          <t>TC1@315</t>
         </is>
       </c>
       <c r="C49" s="17" t="n"/>
@@ -5059,31 +5145,31 @@
       <c r="E49" s="17" t="n"/>
       <c r="F49" s="17" t="inlineStr">
         <is>
-          <t>TT4@285</t>
+          <t>TC4@285</t>
         </is>
       </c>
       <c r="G49" s="17" t="n"/>
       <c r="H49" s="17" t="inlineStr">
         <is>
-          <t>TT4@345</t>
+          <t>TC3@345</t>
         </is>
       </c>
       <c r="I49" s="17" t="n"/>
       <c r="J49" s="17" t="inlineStr">
         <is>
-          <t>TT2@15</t>
+          <t>TP1@15</t>
         </is>
       </c>
       <c r="K49" s="17" t="n"/>
       <c r="L49" s="17" t="inlineStr">
         <is>
-          <t>TD1@180</t>
+          <t>TC4@180</t>
         </is>
       </c>
       <c r="M49" s="17" t="n"/>
       <c r="N49" s="17" t="inlineStr">
         <is>
-          <t>TC1@165</t>
+          <t>TC2@165</t>
         </is>
       </c>
       <c r="O49" s="17" t="n"/>
@@ -5101,19 +5187,19 @@
       <c r="S49" s="17" t="n"/>
       <c r="T49" s="17" t="inlineStr">
         <is>
-          <t>TD1@135</t>
+          <t>TC5@135</t>
         </is>
       </c>
       <c r="U49" s="17" t="n"/>
       <c r="V49" s="17" t="inlineStr">
         <is>
-          <t>TC3@225</t>
+          <t>TC2@225</t>
         </is>
       </c>
       <c r="W49" s="17" t="n"/>
       <c r="X49" s="17" t="inlineStr">
         <is>
-          <t>TT4@180</t>
+          <t>TP5@180</t>
         </is>
       </c>
       <c r="Y49" s="17" t="n"/>
@@ -5125,19 +5211,19 @@
       <c r="AA49" s="17" t="n"/>
       <c r="AB49" s="17" t="inlineStr">
         <is>
-          <t>TC3@30</t>
+          <t>TC5@30</t>
         </is>
       </c>
       <c r="AC49" s="17" t="n"/>
       <c r="AD49" s="17" t="inlineStr">
         <is>
-          <t>TC5@300</t>
+          <t>TC2@300</t>
         </is>
       </c>
       <c r="AE49" s="17" t="n"/>
       <c r="AF49" s="17" t="inlineStr">
         <is>
-          <t>TT2@240</t>
+          <t>TC4@240</t>
         </is>
       </c>
       <c r="AG49" s="17" t="n"/>
@@ -5149,43 +5235,43 @@
       <c r="AI49" s="17" t="n"/>
       <c r="AJ49" s="17" t="inlineStr">
         <is>
-          <t>TC5@60</t>
+          <t>TP5@60</t>
         </is>
       </c>
       <c r="AK49" s="17" t="n"/>
       <c r="AL49" s="17" t="inlineStr">
         <is>
-          <t>TT2@285</t>
+          <t>TP5@285</t>
         </is>
       </c>
       <c r="AM49" s="17" t="n"/>
       <c r="AN49" s="17" t="inlineStr">
         <is>
-          <t>TC1@300</t>
+          <t>TC3@300</t>
         </is>
       </c>
       <c r="AO49" s="17" t="n"/>
       <c r="AP49" s="17" t="inlineStr">
         <is>
-          <t>TC3@105</t>
+          <t>TC2@105</t>
         </is>
       </c>
       <c r="AQ49" s="17" t="n"/>
       <c r="AR49" s="17" t="inlineStr">
         <is>
-          <t>TT2@75</t>
+          <t>TC4@75</t>
         </is>
       </c>
       <c r="AS49" s="17" t="n"/>
       <c r="AT49" s="17" t="inlineStr">
         <is>
-          <t>TT2@180</t>
+          <t>TC1@180</t>
         </is>
       </c>
       <c r="AU49" s="17" t="n"/>
       <c r="AV49" s="17" t="inlineStr">
         <is>
-          <t>TT4@30</t>
+          <t>TC1@30</t>
         </is>
       </c>
       <c r="AW49" s="17" t="n"/>
@@ -5197,37 +5283,37 @@
       <c r="B50" s="17" t="n"/>
       <c r="C50" s="17" t="inlineStr">
         <is>
-          <t>TC1@120</t>
+          <t>TP2@120</t>
         </is>
       </c>
       <c r="D50" s="17" t="n"/>
       <c r="E50" s="17" t="inlineStr">
         <is>
-          <t>TT4@195</t>
+          <t>TC1@195</t>
         </is>
       </c>
       <c r="F50" s="17" t="n"/>
       <c r="G50" s="17" t="inlineStr">
         <is>
-          <t>TT4</t>
+          <t>TD1</t>
         </is>
       </c>
       <c r="H50" s="17" t="n"/>
       <c r="I50" s="17" t="inlineStr">
         <is>
-          <t>TT2@300</t>
+          <t>TP2@300</t>
         </is>
       </c>
       <c r="J50" s="17" t="n"/>
       <c r="K50" s="17" t="inlineStr">
         <is>
-          <t>TD1@30</t>
+          <t>TP5@30</t>
         </is>
       </c>
       <c r="L50" s="17" t="n"/>
       <c r="M50" s="17" t="inlineStr">
         <is>
-          <t>TC5@195</t>
+          <t>TC3@195</t>
         </is>
       </c>
       <c r="N50" s="17" t="n"/>
@@ -5243,13 +5329,13 @@
       <c r="T50" s="17" t="n"/>
       <c r="U50" s="17" t="inlineStr">
         <is>
-          <t>TC3@315</t>
+          <t>TT4@315</t>
         </is>
       </c>
       <c r="V50" s="17" t="n"/>
       <c r="W50" s="17" t="inlineStr">
         <is>
-          <t>TC5@105</t>
+          <t>TC1@105</t>
         </is>
       </c>
       <c r="X50" s="17" t="n"/>
@@ -5261,73 +5347,73 @@
       <c r="Z50" s="17" t="n"/>
       <c r="AA50" s="17" t="inlineStr">
         <is>
-          <t>TC5@120</t>
+          <t>TC2@120</t>
         </is>
       </c>
       <c r="AB50" s="17" t="n"/>
       <c r="AC50" s="17" t="inlineStr">
         <is>
-          <t>TT2@240</t>
+          <t>TP5@240</t>
         </is>
       </c>
       <c r="AD50" s="17" t="n"/>
       <c r="AE50" s="17" t="inlineStr">
         <is>
-          <t>TC5@270</t>
+          <t>TC3@270</t>
         </is>
       </c>
       <c r="AF50" s="17" t="n"/>
       <c r="AG50" s="17" t="inlineStr">
         <is>
-          <t>TT4@45</t>
+          <t>TC2@45</t>
         </is>
       </c>
       <c r="AH50" s="17" t="n"/>
       <c r="AI50" s="17" t="inlineStr">
         <is>
-          <t>TC1@15</t>
+          <t>TC5@15</t>
         </is>
       </c>
       <c r="AJ50" s="17" t="n"/>
       <c r="AK50" s="17" t="inlineStr">
         <is>
-          <t>TD1@225</t>
+          <t>TC3@225</t>
         </is>
       </c>
       <c r="AL50" s="17" t="n"/>
       <c r="AM50" s="17" t="inlineStr">
         <is>
-          <t>TT2@90</t>
+          <t>TD1@90</t>
         </is>
       </c>
       <c r="AN50" s="17" t="n"/>
       <c r="AO50" s="17" t="inlineStr">
         <is>
-          <t>TT2@270</t>
+          <t>TC5@270</t>
         </is>
       </c>
       <c r="AP50" s="17" t="n"/>
       <c r="AQ50" s="17" t="inlineStr">
         <is>
-          <t>TC3@285</t>
+          <t>TP1@285</t>
         </is>
       </c>
       <c r="AR50" s="17" t="n"/>
       <c r="AS50" s="17" t="inlineStr">
         <is>
-          <t>TC1@285</t>
+          <t>TT5@285</t>
         </is>
       </c>
       <c r="AT50" s="17" t="n"/>
       <c r="AU50" s="17" t="inlineStr">
         <is>
-          <t>TT2@105</t>
+          <t>TP1@105</t>
         </is>
       </c>
       <c r="AV50" s="17" t="n"/>
       <c r="AW50" s="17" t="inlineStr">
         <is>
-          <t>TT4@345</t>
+          <t>TP5@345</t>
         </is>
       </c>
     </row>
@@ -5337,31 +5423,31 @@
       </c>
       <c r="B51" s="17" t="inlineStr">
         <is>
-          <t>TT2@90</t>
+          <t>TP5@90</t>
         </is>
       </c>
       <c r="C51" s="17" t="n"/>
       <c r="D51" s="17" t="inlineStr">
         <is>
-          <t>TD1@30</t>
+          <t>TP1@30</t>
         </is>
       </c>
       <c r="E51" s="17" t="n"/>
       <c r="F51" s="17" t="inlineStr">
         <is>
-          <t>TD1@345</t>
+          <t>TP5@345</t>
         </is>
       </c>
       <c r="G51" s="17" t="n"/>
       <c r="H51" s="17" t="inlineStr">
         <is>
-          <t>TC1@45</t>
+          <t>TP1@45</t>
         </is>
       </c>
       <c r="I51" s="17" t="n"/>
       <c r="J51" s="17" t="inlineStr">
         <is>
-          <t>TT4@315</t>
+          <t>TT2@315</t>
         </is>
       </c>
       <c r="K51" s="17" t="n"/>
@@ -5381,97 +5467,97 @@
       <c r="Q51" s="17" t="n"/>
       <c r="R51" s="17" t="inlineStr">
         <is>
-          <t>TC3@150</t>
+          <t>TC5@150</t>
         </is>
       </c>
       <c r="S51" s="17" t="n"/>
       <c r="T51" s="17" t="inlineStr">
         <is>
-          <t>TT4@105</t>
+          <t>TC5@105</t>
         </is>
       </c>
       <c r="U51" s="17" t="n"/>
       <c r="V51" s="17" t="inlineStr">
         <is>
-          <t>TC5@60</t>
+          <t>TP2@60</t>
         </is>
       </c>
       <c r="W51" s="17" t="n"/>
       <c r="X51" s="17" t="inlineStr">
         <is>
-          <t>TT4@45</t>
+          <t>TD1@45</t>
         </is>
       </c>
       <c r="Y51" s="17" t="n"/>
       <c r="Z51" s="17" t="inlineStr">
         <is>
-          <t>TC1@45</t>
+          <t>TC5@45</t>
         </is>
       </c>
       <c r="AA51" s="17" t="n"/>
       <c r="AB51" s="17" t="inlineStr">
         <is>
-          <t>TC3@210</t>
+          <t>TP1@210</t>
         </is>
       </c>
       <c r="AC51" s="17" t="n"/>
       <c r="AD51" s="17" t="inlineStr">
         <is>
-          <t>TC3@210</t>
+          <t>TP2@210</t>
         </is>
       </c>
       <c r="AE51" s="17" t="n"/>
       <c r="AF51" s="17" t="inlineStr">
         <is>
-          <t>TT2@105</t>
+          <t>TC1@105</t>
         </is>
       </c>
       <c r="AG51" s="17" t="n"/>
       <c r="AH51" s="17" t="inlineStr">
         <is>
-          <t>TT4@225</t>
+          <t>TC1@225</t>
         </is>
       </c>
       <c r="AI51" s="17" t="n"/>
       <c r="AJ51" s="17" t="inlineStr">
         <is>
-          <t>TC5@165</t>
+          <t>TC2@165</t>
         </is>
       </c>
       <c r="AK51" s="17" t="n"/>
       <c r="AL51" s="17" t="inlineStr">
         <is>
-          <t>TD1@30</t>
+          <t>TC3@30</t>
         </is>
       </c>
       <c r="AM51" s="17" t="n"/>
       <c r="AN51" s="17" t="inlineStr">
         <is>
-          <t>TC3@195</t>
+          <t>TP1@195</t>
         </is>
       </c>
       <c r="AO51" s="17" t="n"/>
       <c r="AP51" s="17" t="inlineStr">
         <is>
-          <t>TT4@330</t>
+          <t>TT2@330</t>
         </is>
       </c>
       <c r="AQ51" s="17" t="n"/>
       <c r="AR51" s="17" t="inlineStr">
         <is>
-          <t>TT4@45</t>
+          <t>TC1@45</t>
         </is>
       </c>
       <c r="AS51" s="17" t="n"/>
       <c r="AT51" s="17" t="inlineStr">
         <is>
-          <t>TT2@270</t>
+          <t>TP2@270</t>
         </is>
       </c>
       <c r="AU51" s="17" t="n"/>
       <c r="AV51" s="17" t="inlineStr">
         <is>
-          <t>TC1@90</t>
+          <t>TP2@90</t>
         </is>
       </c>
       <c r="AW51" s="17" t="n"/>
@@ -5483,31 +5569,31 @@
       <c r="B52" s="17" t="n"/>
       <c r="C52" s="17" t="inlineStr">
         <is>
-          <t>TT2@15</t>
+          <t>TC1@15</t>
         </is>
       </c>
       <c r="D52" s="17" t="n"/>
       <c r="E52" s="17" t="inlineStr">
         <is>
-          <t>TT4@225</t>
+          <t>TC3@225</t>
         </is>
       </c>
       <c r="F52" s="17" t="n"/>
       <c r="G52" s="17" t="inlineStr">
         <is>
-          <t>TC1@45</t>
+          <t>TC3@45</t>
         </is>
       </c>
       <c r="H52" s="17" t="n"/>
       <c r="I52" s="17" t="inlineStr">
         <is>
-          <t>TT2@150</t>
+          <t>TC3@150</t>
         </is>
       </c>
       <c r="J52" s="17" t="n"/>
       <c r="K52" s="17" t="inlineStr">
         <is>
-          <t>TC1@315</t>
+          <t>TC2@315</t>
         </is>
       </c>
       <c r="L52" s="17" t="n"/>
@@ -5523,13 +5609,13 @@
       <c r="R52" s="17" t="n"/>
       <c r="S52" s="17" t="inlineStr">
         <is>
-          <t>TC1@315</t>
+          <t>TP2@315</t>
         </is>
       </c>
       <c r="T52" s="17" t="n"/>
       <c r="U52" s="17" t="inlineStr">
         <is>
-          <t>TD1@225</t>
+          <t>TC4@225</t>
         </is>
       </c>
       <c r="V52" s="17" t="n"/>
@@ -5541,79 +5627,79 @@
       <c r="X52" s="17" t="n"/>
       <c r="Y52" s="17" t="inlineStr">
         <is>
-          <t>TC5@135</t>
+          <t>TC3@135</t>
         </is>
       </c>
       <c r="Z52" s="17" t="n"/>
       <c r="AA52" s="17" t="inlineStr">
         <is>
-          <t>TD1@330</t>
+          <t>TC1@330</t>
         </is>
       </c>
       <c r="AB52" s="17" t="n"/>
       <c r="AC52" s="17" t="inlineStr">
         <is>
-          <t>TD1@120</t>
+          <t>TT2@120</t>
         </is>
       </c>
       <c r="AD52" s="17" t="n"/>
       <c r="AE52" s="17" t="inlineStr">
         <is>
-          <t>TT4@120</t>
+          <t>TP1@120</t>
         </is>
       </c>
       <c r="AF52" s="17" t="n"/>
       <c r="AG52" s="17" t="inlineStr">
         <is>
-          <t>TC3@165</t>
+          <t>TP2@165</t>
         </is>
       </c>
       <c r="AH52" s="17" t="n"/>
       <c r="AI52" s="17" t="inlineStr">
         <is>
-          <t>TC1@105</t>
+          <t>TC4@105</t>
         </is>
       </c>
       <c r="AJ52" s="17" t="n"/>
       <c r="AK52" s="17" t="inlineStr">
         <is>
-          <t>TT4@105</t>
+          <t>TC3@105</t>
         </is>
       </c>
       <c r="AL52" s="17" t="n"/>
       <c r="AM52" s="17" t="inlineStr">
         <is>
-          <t>TT4@135</t>
+          <t>TD1@135</t>
         </is>
       </c>
       <c r="AN52" s="17" t="n"/>
       <c r="AO52" s="17" t="inlineStr">
         <is>
-          <t>TC5@165</t>
+          <t>TC4@165</t>
         </is>
       </c>
       <c r="AP52" s="17" t="n"/>
       <c r="AQ52" s="17" t="inlineStr">
         <is>
-          <t>TC3@195</t>
+          <t>TT2@195</t>
         </is>
       </c>
       <c r="AR52" s="17" t="n"/>
       <c r="AS52" s="17" t="inlineStr">
         <is>
-          <t>TC3</t>
+          <t>TP2</t>
         </is>
       </c>
       <c r="AT52" s="17" t="n"/>
       <c r="AU52" s="17" t="inlineStr">
         <is>
-          <t>TC1@180</t>
+          <t>TC2@180</t>
         </is>
       </c>
       <c r="AV52" s="17" t="n"/>
       <c r="AW52" s="17" t="inlineStr">
         <is>
-          <t>TC3@270</t>
+          <t>TC5@270</t>
         </is>
       </c>
     </row>
@@ -5623,37 +5709,37 @@
       </c>
       <c r="B53" s="17" t="inlineStr">
         <is>
-          <t>TT2@345</t>
+          <t>TT4@345</t>
         </is>
       </c>
       <c r="C53" s="17" t="n"/>
       <c r="D53" s="17" t="inlineStr">
         <is>
-          <t>TT4@30</t>
+          <t>TC2@30</t>
         </is>
       </c>
       <c r="E53" s="17" t="n"/>
       <c r="F53" s="17" t="inlineStr">
         <is>
-          <t>TD1@90</t>
+          <t>TC2@90</t>
         </is>
       </c>
       <c r="G53" s="17" t="n"/>
       <c r="H53" s="17" t="inlineStr">
         <is>
-          <t>TD1@180</t>
+          <t>TP2@180</t>
         </is>
       </c>
       <c r="I53" s="17" t="n"/>
       <c r="J53" s="17" t="inlineStr">
         <is>
-          <t>TT2@30</t>
+          <t>TP1@30</t>
         </is>
       </c>
       <c r="K53" s="17" t="n"/>
       <c r="L53" s="17" t="inlineStr">
         <is>
-          <t>TC3@180</t>
+          <t>TC1@180</t>
         </is>
       </c>
       <c r="M53" s="17" t="n"/>
@@ -5667,73 +5753,73 @@
       <c r="Q53" s="17" t="n"/>
       <c r="R53" s="17" t="inlineStr">
         <is>
-          <t>TD1@75</t>
+          <t>TC3@75</t>
         </is>
       </c>
       <c r="S53" s="17" t="n"/>
       <c r="T53" s="17" t="inlineStr">
         <is>
-          <t>TT2@345</t>
+          <t>TC2@345</t>
         </is>
       </c>
       <c r="U53" s="17" t="n"/>
       <c r="V53" s="17" t="inlineStr">
         <is>
-          <t>TC3@75</t>
+          <t>TT2@75</t>
         </is>
       </c>
       <c r="W53" s="17" t="n"/>
       <c r="X53" s="17" t="inlineStr">
         <is>
-          <t>TC5@15</t>
+          <t>TC2@15</t>
         </is>
       </c>
       <c r="Y53" s="17" t="n"/>
       <c r="Z53" s="17" t="inlineStr">
         <is>
-          <t>TT2@255</t>
+          <t>TT5@255</t>
         </is>
       </c>
       <c r="AA53" s="17" t="n"/>
       <c r="AB53" s="17" t="inlineStr">
         <is>
-          <t>TT4@315</t>
+          <t>TC5@315</t>
         </is>
       </c>
       <c r="AC53" s="17" t="n"/>
       <c r="AD53" s="17" t="inlineStr">
         <is>
-          <t>TC3@300</t>
+          <t>TP1@300</t>
         </is>
       </c>
       <c r="AE53" s="17" t="n"/>
       <c r="AF53" s="17" t="inlineStr">
         <is>
-          <t>TC1@315</t>
+          <t>TC4@315</t>
         </is>
       </c>
       <c r="AG53" s="17" t="n"/>
       <c r="AH53" s="17" t="inlineStr">
         <is>
-          <t>TT4@105</t>
+          <t>TP5@105</t>
         </is>
       </c>
       <c r="AI53" s="17" t="n"/>
       <c r="AJ53" s="17" t="inlineStr">
         <is>
-          <t>TT2@60</t>
+          <t>TC1@60</t>
         </is>
       </c>
       <c r="AK53" s="17" t="n"/>
       <c r="AL53" s="17" t="inlineStr">
         <is>
-          <t>TD1@255</t>
+          <t>TC4@255</t>
         </is>
       </c>
       <c r="AM53" s="17" t="n"/>
       <c r="AN53" s="17" t="inlineStr">
         <is>
-          <t>TT4@315</t>
+          <t>TT5@315</t>
         </is>
       </c>
       <c r="AO53" s="17" t="n"/>
@@ -5745,13 +5831,13 @@
       <c r="AQ53" s="17" t="n"/>
       <c r="AR53" s="17" t="inlineStr">
         <is>
-          <t>TC5@315</t>
+          <t>TC3@315</t>
         </is>
       </c>
       <c r="AS53" s="17" t="n"/>
       <c r="AT53" s="17" t="inlineStr">
         <is>
-          <t>TC1@300</t>
+          <t>TC5@300</t>
         </is>
       </c>
       <c r="AU53" s="17" t="n"/>
@@ -5773,19 +5859,19 @@
       <c r="F54" s="17" t="n"/>
       <c r="G54" s="17" t="inlineStr">
         <is>
-          <t>TD1@165</t>
+          <t>TP1@165</t>
         </is>
       </c>
       <c r="H54" s="17" t="n"/>
       <c r="I54" s="17" t="inlineStr">
         <is>
-          <t>TC1@165</t>
+          <t>TP2@165</t>
         </is>
       </c>
       <c r="J54" s="17" t="n"/>
       <c r="K54" s="17" t="inlineStr">
         <is>
-          <t>TT2@315</t>
+          <t>TP1@315</t>
         </is>
       </c>
       <c r="L54" s="17" t="n"/>
@@ -5811,7 +5897,7 @@
       <c r="X54" s="17" t="n"/>
       <c r="Y54" s="17" t="inlineStr">
         <is>
-          <t>TC5@300</t>
+          <t>TC2@300</t>
         </is>
       </c>
       <c r="Z54" s="17" t="n"/>
@@ -5845,43 +5931,43 @@
       </c>
       <c r="B55" s="17" t="inlineStr">
         <is>
-          <t>TT2@150</t>
+          <t>TC1@150</t>
         </is>
       </c>
       <c r="C55" s="17" t="n"/>
       <c r="D55" s="17" t="inlineStr">
         <is>
-          <t>TC3@45</t>
+          <t>TC2@45</t>
         </is>
       </c>
       <c r="E55" s="17" t="n"/>
       <c r="F55" s="17" t="inlineStr">
         <is>
-          <t>TC1@15</t>
+          <t>TD1@15</t>
         </is>
       </c>
       <c r="G55" s="17" t="n"/>
       <c r="H55" s="17" t="inlineStr">
         <is>
-          <t>TD1@120</t>
+          <t>TC4@120</t>
         </is>
       </c>
       <c r="I55" s="17" t="n"/>
       <c r="J55" s="17" t="inlineStr">
         <is>
-          <t>TT2@75</t>
+          <t>TC1@75</t>
         </is>
       </c>
       <c r="K55" s="17" t="n"/>
       <c r="L55" s="17" t="inlineStr">
         <is>
-          <t>TT2@300</t>
+          <t>TC2@300</t>
         </is>
       </c>
       <c r="M55" s="17" t="n"/>
       <c r="N55" s="17" t="inlineStr">
         <is>
-          <t>TC3@165</t>
+          <t>TC2@165</t>
         </is>
       </c>
       <c r="O55" s="17" t="n"/>
@@ -5901,13 +5987,13 @@
       <c r="U55" s="17" t="n"/>
       <c r="V55" s="17" t="inlineStr">
         <is>
-          <t>TC1@300</t>
+          <t>TP1@300</t>
         </is>
       </c>
       <c r="W55" s="17" t="n"/>
       <c r="X55" s="17" t="inlineStr">
         <is>
-          <t>TC3@195</t>
+          <t>TC1@195</t>
         </is>
       </c>
       <c r="Y55" s="17" t="n"/>
@@ -5919,67 +6005,67 @@
       <c r="AA55" s="17" t="n"/>
       <c r="AB55" s="17" t="inlineStr">
         <is>
-          <t>TD1@225</t>
+          <t>TT4@225</t>
         </is>
       </c>
       <c r="AC55" s="17" t="n"/>
       <c r="AD55" s="17" t="inlineStr">
         <is>
-          <t>TC5@45</t>
+          <t>TP1@45</t>
         </is>
       </c>
       <c r="AE55" s="17" t="n"/>
       <c r="AF55" s="17" t="inlineStr">
         <is>
-          <t>TT2@345</t>
+          <t>TC5@345</t>
         </is>
       </c>
       <c r="AG55" s="17" t="n"/>
       <c r="AH55" s="17" t="inlineStr">
         <is>
-          <t>TT2@345</t>
+          <t>TP5@345</t>
         </is>
       </c>
       <c r="AI55" s="17" t="n"/>
       <c r="AJ55" s="17" t="inlineStr">
         <is>
-          <t>TT2@135</t>
+          <t>TT5@135</t>
         </is>
       </c>
       <c r="AK55" s="17" t="n"/>
       <c r="AL55" s="17" t="inlineStr">
         <is>
-          <t>TC3@90</t>
+          <t>TC4@90</t>
         </is>
       </c>
       <c r="AM55" s="17" t="n"/>
       <c r="AN55" s="17" t="inlineStr">
         <is>
-          <t>TD1@270</t>
+          <t>TP1@270</t>
         </is>
       </c>
       <c r="AO55" s="17" t="n"/>
       <c r="AP55" s="17" t="inlineStr">
         <is>
-          <t>TD1@15</t>
+          <t>TC1@15</t>
         </is>
       </c>
       <c r="AQ55" s="17" t="n"/>
       <c r="AR55" s="17" t="inlineStr">
         <is>
-          <t>TC3@210</t>
+          <t>TC5@210</t>
         </is>
       </c>
       <c r="AS55" s="17" t="n"/>
       <c r="AT55" s="17" t="inlineStr">
         <is>
-          <t>TD1@285</t>
+          <t>TC3@285</t>
         </is>
       </c>
       <c r="AU55" s="17" t="n"/>
       <c r="AV55" s="17" t="inlineStr">
         <is>
-          <t>TT4@135</t>
+          <t>TC5@135</t>
         </is>
       </c>
       <c r="AW55" s="17" t="n"/>
@@ -5997,25 +6083,25 @@
       <c r="H56" s="17" t="n"/>
       <c r="I56" s="17" t="inlineStr">
         <is>
-          <t>TC1@120</t>
+          <t>TC2@120</t>
         </is>
       </c>
       <c r="J56" s="17" t="n"/>
       <c r="K56" s="17" t="inlineStr">
         <is>
-          <t>TT4@15</t>
+          <t>TC1@15</t>
         </is>
       </c>
       <c r="L56" s="17" t="n"/>
       <c r="M56" s="17" t="inlineStr">
         <is>
-          <t>TD1@300</t>
+          <t>TC5@300</t>
         </is>
       </c>
       <c r="N56" s="17" t="n"/>
       <c r="O56" s="17" t="inlineStr">
         <is>
-          <t>TD1@270</t>
+          <t>TC1@270</t>
         </is>
       </c>
       <c r="P56" s="17" t="n"/>
@@ -6031,19 +6117,19 @@
       <c r="V56" s="17" t="n"/>
       <c r="W56" s="17" t="inlineStr">
         <is>
-          <t>TT2@225</t>
+          <t>TC5@225</t>
         </is>
       </c>
       <c r="X56" s="17" t="n"/>
       <c r="Y56" s="17" t="inlineStr">
         <is>
-          <t>TC1@270</t>
+          <t>TC3@270</t>
         </is>
       </c>
       <c r="Z56" s="17" t="n"/>
       <c r="AA56" s="17" t="inlineStr">
         <is>
-          <t>TT2@150</t>
+          <t>TC5@150</t>
         </is>
       </c>
       <c r="AB56" s="17" t="n"/>
@@ -6075,25 +6161,25 @@
       </c>
       <c r="B57" s="17" t="inlineStr">
         <is>
-          <t>TC5@165</t>
+          <t>TC2@165</t>
         </is>
       </c>
       <c r="C57" s="17" t="n"/>
       <c r="D57" s="17" t="inlineStr">
         <is>
-          <t>TT4@90</t>
+          <t>TP5@90</t>
         </is>
       </c>
       <c r="E57" s="17" t="n"/>
       <c r="F57" s="17" t="inlineStr">
         <is>
-          <t>TD1@150</t>
+          <t>TP2@150</t>
         </is>
       </c>
       <c r="G57" s="17" t="n"/>
       <c r="H57" s="17" t="inlineStr">
         <is>
-          <t>TC5@195</t>
+          <t>TC3@195</t>
         </is>
       </c>
       <c r="I57" s="17" t="n"/>
@@ -6105,19 +6191,19 @@
       <c r="K57" s="17" t="n"/>
       <c r="L57" s="17" t="inlineStr">
         <is>
-          <t>TT2@300</t>
+          <t>TC1@300</t>
         </is>
       </c>
       <c r="M57" s="17" t="n"/>
       <c r="N57" s="17" t="inlineStr">
         <is>
-          <t>TT4@120</t>
+          <t>TP5@120</t>
         </is>
       </c>
       <c r="O57" s="17" t="n"/>
       <c r="P57" s="17" t="inlineStr">
         <is>
-          <t>TC5@315</t>
+          <t>TC2@315</t>
         </is>
       </c>
       <c r="Q57" s="17" t="n"/>
@@ -6135,19 +6221,19 @@
       <c r="U57" s="17" t="n"/>
       <c r="V57" s="17" t="inlineStr">
         <is>
-          <t>TD1@270</t>
+          <t>TC4@270</t>
         </is>
       </c>
       <c r="W57" s="17" t="n"/>
       <c r="X57" s="17" t="inlineStr">
         <is>
-          <t>TT4</t>
+          <t>TC2</t>
         </is>
       </c>
       <c r="Y57" s="17" t="n"/>
       <c r="Z57" s="17" t="inlineStr">
         <is>
-          <t>TD1</t>
+          <t>TC5</t>
         </is>
       </c>
       <c r="AA57" s="17" t="n"/>
@@ -6159,25 +6245,25 @@
       <c r="AC57" s="17" t="n"/>
       <c r="AD57" s="17" t="inlineStr">
         <is>
-          <t>TT4@15</t>
+          <t>TP1@15</t>
         </is>
       </c>
       <c r="AE57" s="17" t="n"/>
       <c r="AF57" s="17" t="inlineStr">
         <is>
-          <t>TD1@315</t>
+          <t>TP2@315</t>
         </is>
       </c>
       <c r="AG57" s="17" t="n"/>
       <c r="AH57" s="17" t="inlineStr">
         <is>
-          <t>TC5@315</t>
+          <t>TP1@315</t>
         </is>
       </c>
       <c r="AI57" s="17" t="n"/>
       <c r="AJ57" s="17" t="inlineStr">
         <is>
-          <t>TT4@255</t>
+          <t>TC5@255</t>
         </is>
       </c>
       <c r="AK57" s="17" t="n"/>
@@ -6189,31 +6275,31 @@
       <c r="AM57" s="17" t="n"/>
       <c r="AN57" s="17" t="inlineStr">
         <is>
-          <t>TC1@300</t>
+          <t>TC5@300</t>
         </is>
       </c>
       <c r="AO57" s="17" t="n"/>
       <c r="AP57" s="17" t="inlineStr">
         <is>
-          <t>TT2</t>
+          <t>TP1</t>
         </is>
       </c>
       <c r="AQ57" s="17" t="n"/>
       <c r="AR57" s="17" t="inlineStr">
         <is>
-          <t>TD1@180</t>
+          <t>TC1@180</t>
         </is>
       </c>
       <c r="AS57" s="17" t="n"/>
       <c r="AT57" s="17" t="inlineStr">
         <is>
-          <t>TD1@315</t>
+          <t>TT4@315</t>
         </is>
       </c>
       <c r="AU57" s="17" t="n"/>
       <c r="AV57" s="17" t="inlineStr">
         <is>
-          <t>TC5@120</t>
+          <t>TC1@120</t>
         </is>
       </c>
       <c r="AW57" s="17" t="n"/>
@@ -6231,25 +6317,25 @@
       <c r="H58" s="17" t="n"/>
       <c r="I58" s="17" t="inlineStr">
         <is>
-          <t>TT4@135</t>
+          <t>TC2@135</t>
         </is>
       </c>
       <c r="J58" s="17" t="n"/>
       <c r="K58" s="17" t="inlineStr">
         <is>
-          <t>TT2@240</t>
+          <t>TP2@240</t>
         </is>
       </c>
       <c r="L58" s="17" t="n"/>
       <c r="M58" s="17" t="inlineStr">
         <is>
-          <t>TC1@240</t>
+          <t>TC4@240</t>
         </is>
       </c>
       <c r="N58" s="17" t="n"/>
       <c r="O58" s="17" t="inlineStr">
         <is>
-          <t>TC3@240</t>
+          <t>TT5@240</t>
         </is>
       </c>
       <c r="P58" s="17" t="n"/>
@@ -6269,7 +6355,7 @@
       <c r="V58" s="17" t="n"/>
       <c r="W58" s="17" t="inlineStr">
         <is>
-          <t>TD1@315</t>
+          <t>TC1@315</t>
         </is>
       </c>
       <c r="X58" s="17" t="n"/>
@@ -6281,7 +6367,7 @@
       <c r="Z58" s="17" t="n"/>
       <c r="AA58" s="17" t="inlineStr">
         <is>
-          <t>TC5@165</t>
+          <t>TD1@165</t>
         </is>
       </c>
       <c r="AB58" s="17" t="n"/>
@@ -6313,7 +6399,7 @@
       </c>
       <c r="B59" s="17" t="inlineStr">
         <is>
-          <t>TC5</t>
+          <t>TP5</t>
         </is>
       </c>
       <c r="C59" s="17" t="n"/>
@@ -6325,37 +6411,37 @@
       <c r="E59" s="17" t="n"/>
       <c r="F59" s="17" t="inlineStr">
         <is>
-          <t>TT2@150</t>
+          <t>TC2@150</t>
         </is>
       </c>
       <c r="G59" s="17" t="n"/>
       <c r="H59" s="17" t="inlineStr">
         <is>
-          <t>TC5@120</t>
+          <t>TC2@120</t>
         </is>
       </c>
       <c r="I59" s="17" t="n"/>
       <c r="J59" s="17" t="inlineStr">
         <is>
-          <t>TC3@15</t>
+          <t>TD1@15</t>
         </is>
       </c>
       <c r="K59" s="17" t="n"/>
       <c r="L59" s="17" t="inlineStr">
         <is>
-          <t>TC1@225</t>
+          <t>TP2@225</t>
         </is>
       </c>
       <c r="M59" s="17" t="n"/>
       <c r="N59" s="17" t="inlineStr">
         <is>
-          <t>TD1@45</t>
+          <t>TC3@45</t>
         </is>
       </c>
       <c r="O59" s="17" t="n"/>
       <c r="P59" s="17" t="inlineStr">
         <is>
-          <t>TD1@225</t>
+          <t>TC3@225</t>
         </is>
       </c>
       <c r="Q59" s="17" t="n"/>
@@ -6377,61 +6463,61 @@
       <c r="Y59" s="17" t="n"/>
       <c r="Z59" s="17" t="inlineStr">
         <is>
-          <t>TC5@315</t>
+          <t>TT4@315</t>
         </is>
       </c>
       <c r="AA59" s="17" t="n"/>
       <c r="AB59" s="17" t="inlineStr">
         <is>
-          <t>TT2@195</t>
+          <t>TC1@195</t>
         </is>
       </c>
       <c r="AC59" s="17" t="n"/>
       <c r="AD59" s="17" t="inlineStr">
         <is>
-          <t>TC1@270</t>
+          <t>TP5@270</t>
         </is>
       </c>
       <c r="AE59" s="17" t="n"/>
       <c r="AF59" s="17" t="inlineStr">
         <is>
-          <t>TC1@120</t>
+          <t>TP2@120</t>
         </is>
       </c>
       <c r="AG59" s="17" t="n"/>
       <c r="AH59" s="17" t="inlineStr">
         <is>
-          <t>TD1@330</t>
+          <t>TT2@330</t>
         </is>
       </c>
       <c r="AI59" s="17" t="n"/>
       <c r="AJ59" s="17" t="inlineStr">
         <is>
-          <t>TC5@30</t>
+          <t>TP1@30</t>
         </is>
       </c>
       <c r="AK59" s="17" t="n"/>
       <c r="AL59" s="17" t="inlineStr">
         <is>
-          <t>TC1@255</t>
+          <t>TC5@255</t>
         </is>
       </c>
       <c r="AM59" s="17" t="n"/>
       <c r="AN59" s="17" t="inlineStr">
         <is>
-          <t>TT2@345</t>
+          <t>TP1@345</t>
         </is>
       </c>
       <c r="AO59" s="17" t="n"/>
       <c r="AP59" s="17" t="inlineStr">
         <is>
-          <t>TT4@300</t>
+          <t>TC4@300</t>
         </is>
       </c>
       <c r="AQ59" s="17" t="n"/>
       <c r="AR59" s="17" t="inlineStr">
         <is>
-          <t>TC1@225</t>
+          <t>TP2@225</t>
         </is>
       </c>
       <c r="AS59" s="17" t="n"/>
@@ -6443,7 +6529,7 @@
       <c r="AU59" s="17" t="n"/>
       <c r="AV59" s="17" t="inlineStr">
         <is>
-          <t>TC1@45</t>
+          <t>TT2@45</t>
         </is>
       </c>
       <c r="AW59" s="17" t="n"/>
@@ -6465,25 +6551,25 @@
       <c r="L60" s="17" t="n"/>
       <c r="M60" s="17" t="inlineStr">
         <is>
-          <t>TC1@345</t>
+          <t>TC2@345</t>
         </is>
       </c>
       <c r="N60" s="17" t="n"/>
       <c r="O60" s="17" t="inlineStr">
         <is>
-          <t>TD1@195</t>
+          <t>TC3@195</t>
         </is>
       </c>
       <c r="P60" s="17" t="n"/>
       <c r="Q60" s="17" t="inlineStr">
         <is>
-          <t>TC1@180</t>
+          <t>TC3@180</t>
         </is>
       </c>
       <c r="R60" s="17" t="n"/>
       <c r="S60" s="17" t="inlineStr">
         <is>
-          <t>TC5@195</t>
+          <t>TC2@195</t>
         </is>
       </c>
       <c r="T60" s="17" t="n"/>
@@ -6491,19 +6577,19 @@
       <c r="V60" s="17" t="n"/>
       <c r="W60" s="17" t="inlineStr">
         <is>
-          <t>TC3@75</t>
+          <t>TC5@75</t>
         </is>
       </c>
       <c r="X60" s="17" t="n"/>
       <c r="Y60" s="17" t="inlineStr">
         <is>
-          <t>TT4@105</t>
+          <t>TP5@105</t>
         </is>
       </c>
       <c r="Z60" s="17" t="n"/>
       <c r="AA60" s="17" t="inlineStr">
         <is>
-          <t>TD1@180</t>
+          <t>TC4@180</t>
         </is>
       </c>
       <c r="AB60" s="17" t="n"/>
@@ -6535,55 +6621,55 @@
       </c>
       <c r="B61" s="17" t="inlineStr">
         <is>
-          <t>TC3@135</t>
+          <t>TT5@135</t>
         </is>
       </c>
       <c r="C61" s="17" t="n"/>
       <c r="D61" s="17" t="inlineStr">
         <is>
-          <t>TC1@315</t>
+          <t>TC3@315</t>
         </is>
       </c>
       <c r="E61" s="17" t="n"/>
       <c r="F61" s="17" t="inlineStr">
         <is>
-          <t>TT4@240</t>
+          <t>TC5@240</t>
         </is>
       </c>
       <c r="G61" s="17" t="n"/>
       <c r="H61" s="17" t="inlineStr">
         <is>
-          <t>TC5@105</t>
+          <t>TC2@105</t>
         </is>
       </c>
       <c r="I61" s="17" t="n"/>
       <c r="J61" s="17" t="inlineStr">
         <is>
-          <t>TC1@180</t>
+          <t>TT4@180</t>
         </is>
       </c>
       <c r="K61" s="17" t="n"/>
       <c r="L61" s="17" t="inlineStr">
         <is>
-          <t>TT4@150</t>
+          <t>TC2@150</t>
         </is>
       </c>
       <c r="M61" s="17" t="n"/>
       <c r="N61" s="17" t="inlineStr">
         <is>
-          <t>TD1@30</t>
+          <t>TP5@30</t>
         </is>
       </c>
       <c r="O61" s="17" t="n"/>
       <c r="P61" s="17" t="inlineStr">
         <is>
-          <t>TT4@60</t>
+          <t>TC3@60</t>
         </is>
       </c>
       <c r="Q61" s="17" t="n"/>
       <c r="R61" s="17" t="inlineStr">
         <is>
-          <t>TC5@105</t>
+          <t>TP1@105</t>
         </is>
       </c>
       <c r="S61" s="17" t="n"/>
@@ -6597,37 +6683,37 @@
       <c r="W61" s="17" t="n"/>
       <c r="X61" s="17" t="inlineStr">
         <is>
-          <t>TC3@285</t>
+          <t>TC2@285</t>
         </is>
       </c>
       <c r="Y61" s="17" t="n"/>
       <c r="Z61" s="17" t="inlineStr">
         <is>
-          <t>TT4@60</t>
+          <t>TP2@60</t>
         </is>
       </c>
       <c r="AA61" s="17" t="n"/>
       <c r="AB61" s="17" t="inlineStr">
         <is>
-          <t>TT2@165</t>
+          <t>TP5@165</t>
         </is>
       </c>
       <c r="AC61" s="17" t="n"/>
       <c r="AD61" s="17" t="inlineStr">
         <is>
-          <t>TT4@60</t>
+          <t>TP2@60</t>
         </is>
       </c>
       <c r="AE61" s="17" t="n"/>
       <c r="AF61" s="17" t="inlineStr">
         <is>
-          <t>TD1@210</t>
+          <t>TP2@210</t>
         </is>
       </c>
       <c r="AG61" s="17" t="n"/>
       <c r="AH61" s="17" t="inlineStr">
         <is>
-          <t>TC3@105</t>
+          <t>TP2@105</t>
         </is>
       </c>
       <c r="AI61" s="17" t="n"/>
@@ -6639,37 +6725,37 @@
       <c r="AK61" s="17" t="n"/>
       <c r="AL61" s="17" t="inlineStr">
         <is>
-          <t>TD1@315</t>
+          <t>TC5@315</t>
         </is>
       </c>
       <c r="AM61" s="17" t="n"/>
       <c r="AN61" s="17" t="inlineStr">
         <is>
-          <t>TC3@105</t>
+          <t>TC2@105</t>
         </is>
       </c>
       <c r="AO61" s="17" t="n"/>
       <c r="AP61" s="17" t="inlineStr">
         <is>
-          <t>TC3@345</t>
+          <t>TC1@345</t>
         </is>
       </c>
       <c r="AQ61" s="17" t="n"/>
       <c r="AR61" s="17" t="inlineStr">
         <is>
-          <t>TT4@270</t>
+          <t>TP5@270</t>
         </is>
       </c>
       <c r="AS61" s="17" t="n"/>
       <c r="AT61" s="17" t="inlineStr">
         <is>
-          <t>TC1@270</t>
+          <t>TC4@270</t>
         </is>
       </c>
       <c r="AU61" s="17" t="n"/>
       <c r="AV61" s="17" t="inlineStr">
         <is>
-          <t>TD1@255</t>
+          <t>TP2@255</t>
         </is>
       </c>
       <c r="AW61" s="17" t="n"/>
@@ -6691,25 +6777,25 @@
       <c r="L62" s="17" t="n"/>
       <c r="M62" s="17" t="inlineStr">
         <is>
-          <t>TT4@195</t>
+          <t>TP5@195</t>
         </is>
       </c>
       <c r="N62" s="17" t="n"/>
       <c r="O62" s="17" t="inlineStr">
         <is>
-          <t>TT2@90</t>
+          <t>TC4@90</t>
         </is>
       </c>
       <c r="P62" s="17" t="n"/>
       <c r="Q62" s="17" t="inlineStr">
         <is>
-          <t>TT2@150</t>
+          <t>TC4@150</t>
         </is>
       </c>
       <c r="R62" s="17" t="n"/>
       <c r="S62" s="17" t="inlineStr">
         <is>
-          <t>TC3@210</t>
+          <t>TC5@210</t>
         </is>
       </c>
       <c r="T62" s="17" t="n"/>
@@ -6721,19 +6807,19 @@
       <c r="V62" s="17" t="n"/>
       <c r="W62" s="17" t="inlineStr">
         <is>
-          <t>TC1</t>
+          <t>TC4</t>
         </is>
       </c>
       <c r="X62" s="17" t="n"/>
       <c r="Y62" s="17" t="inlineStr">
         <is>
-          <t>TT4@240</t>
+          <t>TT2@240</t>
         </is>
       </c>
       <c r="Z62" s="17" t="n"/>
       <c r="AA62" s="17" t="inlineStr">
         <is>
-          <t>TC1@165</t>
+          <t>TC4@165</t>
         </is>
       </c>
       <c r="AB62" s="17" t="n"/>
@@ -6765,55 +6851,55 @@
       </c>
       <c r="B63" s="17" t="inlineStr">
         <is>
-          <t>TC3@240</t>
+          <t>TP2@240</t>
         </is>
       </c>
       <c r="C63" s="17" t="n"/>
       <c r="D63" s="17" t="inlineStr">
         <is>
-          <t>TC5@330</t>
+          <t>TC4@330</t>
         </is>
       </c>
       <c r="E63" s="17" t="n"/>
       <c r="F63" s="17" t="inlineStr">
         <is>
-          <t>TC3@315</t>
+          <t>TC2@315</t>
         </is>
       </c>
       <c r="G63" s="17" t="n"/>
       <c r="H63" s="17" t="inlineStr">
         <is>
-          <t>TT2@105</t>
+          <t>TC2@105</t>
         </is>
       </c>
       <c r="I63" s="17" t="n"/>
       <c r="J63" s="17" t="inlineStr">
         <is>
-          <t>TT4@240</t>
+          <t>TC3@240</t>
         </is>
       </c>
       <c r="K63" s="17" t="n"/>
       <c r="L63" s="17" t="inlineStr">
         <is>
-          <t>TT2@330</t>
+          <t>TP2@330</t>
         </is>
       </c>
       <c r="M63" s="17" t="n"/>
       <c r="N63" s="17" t="inlineStr">
         <is>
-          <t>TD1@30</t>
+          <t>TT2@30</t>
         </is>
       </c>
       <c r="O63" s="17" t="n"/>
       <c r="P63" s="17" t="inlineStr">
         <is>
-          <t>TC1@255</t>
+          <t>TT4@255</t>
         </is>
       </c>
       <c r="Q63" s="17" t="n"/>
       <c r="R63" s="17" t="inlineStr">
         <is>
-          <t>TD1</t>
+          <t>TC2</t>
         </is>
       </c>
       <c r="S63" s="17" t="n"/>
@@ -6823,79 +6909,79 @@
       <c r="W63" s="17" t="n"/>
       <c r="X63" s="17" t="inlineStr">
         <is>
-          <t>TC1@30</t>
+          <t>TC5@30</t>
         </is>
       </c>
       <c r="Y63" s="17" t="n"/>
       <c r="Z63" s="17" t="inlineStr">
         <is>
-          <t>TT2@180</t>
+          <t>TP5@180</t>
         </is>
       </c>
       <c r="AA63" s="17" t="n"/>
       <c r="AB63" s="17" t="inlineStr">
         <is>
-          <t>TC3@345</t>
+          <t>TC2@345</t>
         </is>
       </c>
       <c r="AC63" s="17" t="n"/>
       <c r="AD63" s="17" t="inlineStr">
         <is>
-          <t>TC5@105</t>
+          <t>TC3@105</t>
         </is>
       </c>
       <c r="AE63" s="17" t="n"/>
       <c r="AF63" s="17" t="inlineStr">
         <is>
-          <t>TT4@330</t>
+          <t>TP5@330</t>
         </is>
       </c>
       <c r="AG63" s="17" t="n"/>
       <c r="AH63" s="17" t="inlineStr">
         <is>
-          <t>TC1@150</t>
+          <t>TC4@150</t>
         </is>
       </c>
       <c r="AI63" s="17" t="n"/>
       <c r="AJ63" s="17" t="inlineStr">
         <is>
-          <t>TT2@120</t>
+          <t>TD1@120</t>
         </is>
       </c>
       <c r="AK63" s="17" t="n"/>
       <c r="AL63" s="17" t="inlineStr">
         <is>
-          <t>TC1@90</t>
+          <t>TC4@90</t>
         </is>
       </c>
       <c r="AM63" s="17" t="n"/>
       <c r="AN63" s="17" t="inlineStr">
         <is>
-          <t>TC3</t>
+          <t>TC1</t>
         </is>
       </c>
       <c r="AO63" s="17" t="n"/>
       <c r="AP63" s="17" t="inlineStr">
         <is>
-          <t>TC3@120</t>
+          <t>TC5@120</t>
         </is>
       </c>
       <c r="AQ63" s="17" t="n"/>
       <c r="AR63" s="17" t="inlineStr">
         <is>
-          <t>TT4@120</t>
+          <t>TC2@120</t>
         </is>
       </c>
       <c r="AS63" s="17" t="n"/>
       <c r="AT63" s="17" t="inlineStr">
         <is>
-          <t>TT4@90</t>
+          <t>TC1@90</t>
         </is>
       </c>
       <c r="AU63" s="17" t="n"/>
       <c r="AV63" s="17" t="inlineStr">
         <is>
-          <t>TT4@285</t>
+          <t>TC1@285</t>
         </is>
       </c>
       <c r="AW63" s="17" t="n"/>
@@ -6919,19 +7005,19 @@
       <c r="N64" s="17" t="n"/>
       <c r="O64" s="17" t="inlineStr">
         <is>
-          <t>TC5@30</t>
+          <t>TT5@30</t>
         </is>
       </c>
       <c r="P64" s="17" t="n"/>
       <c r="Q64" s="17" t="inlineStr">
         <is>
-          <t>TC5@240</t>
+          <t>TT2@240</t>
         </is>
       </c>
       <c r="R64" s="17" t="n"/>
       <c r="S64" s="17" t="inlineStr">
         <is>
-          <t>TC1@180</t>
+          <t>TC2@180</t>
         </is>
       </c>
       <c r="T64" s="17" t="n"/>
@@ -6943,19 +7029,19 @@
       <c r="V64" s="17" t="n"/>
       <c r="W64" s="17" t="inlineStr">
         <is>
-          <t>TC1@195</t>
+          <t>TC4@195</t>
         </is>
       </c>
       <c r="X64" s="17" t="n"/>
       <c r="Y64" s="17" t="inlineStr">
         <is>
-          <t>TT4@195</t>
+          <t>TC3@195</t>
         </is>
       </c>
       <c r="Z64" s="17" t="n"/>
       <c r="AA64" s="17" t="inlineStr">
         <is>
-          <t>TC1@45</t>
+          <t>TP5@45</t>
         </is>
       </c>
       <c r="AB64" s="17" t="n"/>
@@ -6963,13 +7049,13 @@
       <c r="AD64" s="17" t="n"/>
       <c r="AE64" s="17" t="inlineStr">
         <is>
-          <t>TC5@285</t>
+          <t>TC1@285</t>
         </is>
       </c>
       <c r="AF64" s="17" t="n"/>
       <c r="AG64" s="17" t="inlineStr">
         <is>
-          <t>TT2@60</t>
+          <t>TP5@60</t>
         </is>
       </c>
       <c r="AH64" s="17" t="n"/>
@@ -6995,19 +7081,19 @@
       </c>
       <c r="B65" s="17" t="inlineStr">
         <is>
-          <t>TC5</t>
+          <t>TD1</t>
         </is>
       </c>
       <c r="C65" s="17" t="n"/>
       <c r="D65" s="17" t="inlineStr">
         <is>
-          <t>TC1@90</t>
+          <t>TP1@90</t>
         </is>
       </c>
       <c r="E65" s="17" t="n"/>
       <c r="F65" s="17" t="inlineStr">
         <is>
-          <t>TT4@165</t>
+          <t>TT2@165</t>
         </is>
       </c>
       <c r="G65" s="17" t="n"/>
@@ -7019,31 +7105,31 @@
       <c r="I65" s="17" t="n"/>
       <c r="J65" s="17" t="inlineStr">
         <is>
-          <t>TT2@165</t>
+          <t>TC4@165</t>
         </is>
       </c>
       <c r="K65" s="17" t="n"/>
       <c r="L65" s="17" t="inlineStr">
         <is>
-          <t>TC1@105</t>
+          <t>TP1@105</t>
         </is>
       </c>
       <c r="M65" s="17" t="n"/>
       <c r="N65" s="17" t="inlineStr">
         <is>
-          <t>TT2@345</t>
+          <t>TC3@345</t>
         </is>
       </c>
       <c r="O65" s="17" t="n"/>
       <c r="P65" s="17" t="inlineStr">
         <is>
-          <t>TD1@30</t>
+          <t>TP2@30</t>
         </is>
       </c>
       <c r="Q65" s="17" t="n"/>
       <c r="R65" s="17" t="inlineStr">
         <is>
-          <t>TC1@60</t>
+          <t>TP2@60</t>
         </is>
       </c>
       <c r="S65" s="17" t="n"/>
@@ -7063,73 +7149,73 @@
       <c r="Y65" s="17" t="n"/>
       <c r="Z65" s="17" t="inlineStr">
         <is>
-          <t>TD1@105</t>
+          <t>TC3@105</t>
         </is>
       </c>
       <c r="AA65" s="17" t="n"/>
       <c r="AB65" s="17" t="inlineStr">
         <is>
-          <t>TC1</t>
+          <t>TP2</t>
         </is>
       </c>
       <c r="AC65" s="17" t="n"/>
       <c r="AD65" s="17" t="inlineStr">
         <is>
-          <t>TC1@30</t>
+          <t>TC5@30</t>
         </is>
       </c>
       <c r="AE65" s="17" t="n"/>
       <c r="AF65" s="17" t="inlineStr">
         <is>
-          <t>TT2@285</t>
+          <t>TC5@285</t>
         </is>
       </c>
       <c r="AG65" s="17" t="n"/>
       <c r="AH65" s="17" t="inlineStr">
         <is>
-          <t>TC3@285</t>
+          <t>TT4@285</t>
         </is>
       </c>
       <c r="AI65" s="17" t="n"/>
       <c r="AJ65" s="17" t="inlineStr">
         <is>
-          <t>TC1@300</t>
+          <t>TC5@300</t>
         </is>
       </c>
       <c r="AK65" s="17" t="n"/>
       <c r="AL65" s="17" t="inlineStr">
         <is>
-          <t>TC3@180</t>
+          <t>TP2@180</t>
         </is>
       </c>
       <c r="AM65" s="17" t="n"/>
       <c r="AN65" s="17" t="inlineStr">
         <is>
-          <t>TT4@195</t>
+          <t>TP1@195</t>
         </is>
       </c>
       <c r="AO65" s="17" t="n"/>
       <c r="AP65" s="17" t="inlineStr">
         <is>
-          <t>TT4@135</t>
+          <t>TP1@135</t>
         </is>
       </c>
       <c r="AQ65" s="17" t="n"/>
       <c r="AR65" s="17" t="inlineStr">
         <is>
-          <t>TC3@345</t>
+          <t>TC2@345</t>
         </is>
       </c>
       <c r="AS65" s="17" t="n"/>
       <c r="AT65" s="17" t="inlineStr">
         <is>
-          <t>TC3@60</t>
+          <t>TP1@60</t>
         </is>
       </c>
       <c r="AU65" s="17" t="n"/>
       <c r="AV65" s="17" t="inlineStr">
         <is>
-          <t>TC5@240</t>
+          <t>TP5@240</t>
         </is>
       </c>
       <c r="AW65" s="17" t="n"/>
@@ -7151,19 +7237,19 @@
       <c r="L66" s="17" t="n"/>
       <c r="M66" s="17" t="inlineStr">
         <is>
-          <t>TC1@90</t>
+          <t>TP2@90</t>
         </is>
       </c>
       <c r="N66" s="17" t="n"/>
       <c r="O66" s="17" t="inlineStr">
         <is>
-          <t>TT4@150</t>
+          <t>TC1@150</t>
         </is>
       </c>
       <c r="P66" s="17" t="n"/>
       <c r="Q66" s="17" t="inlineStr">
         <is>
-          <t>TC1@30</t>
+          <t>TP2@30</t>
         </is>
       </c>
       <c r="R66" s="17" t="n"/>
@@ -7183,43 +7269,43 @@
       <c r="X66" s="17" t="n"/>
       <c r="Y66" s="17" t="inlineStr">
         <is>
-          <t>TD1@120</t>
+          <t>TP5@120</t>
         </is>
       </c>
       <c r="Z66" s="17" t="n"/>
       <c r="AA66" s="17" t="inlineStr">
         <is>
-          <t>TC5@45</t>
+          <t>TT2@45</t>
         </is>
       </c>
       <c r="AB66" s="17" t="n"/>
       <c r="AC66" s="17" t="inlineStr">
         <is>
-          <t>TD1@30</t>
+          <t>TC4@30</t>
         </is>
       </c>
       <c r="AD66" s="17" t="n"/>
       <c r="AE66" s="17" t="inlineStr">
         <is>
-          <t>TC5@285</t>
+          <t>TP5@285</t>
         </is>
       </c>
       <c r="AF66" s="17" t="n"/>
       <c r="AG66" s="17" t="inlineStr">
         <is>
-          <t>TC5@225</t>
+          <t>TT5@225</t>
         </is>
       </c>
       <c r="AH66" s="17" t="n"/>
       <c r="AI66" s="17" t="inlineStr">
         <is>
-          <t>TC5@150</t>
+          <t>TP2@150</t>
         </is>
       </c>
       <c r="AJ66" s="17" t="n"/>
       <c r="AK66" s="17" t="inlineStr">
         <is>
-          <t>TD1@30</t>
+          <t>TC2@30</t>
         </is>
       </c>
       <c r="AL66" s="17" t="n"/>
@@ -7241,49 +7327,49 @@
       </c>
       <c r="B67" s="17" t="inlineStr">
         <is>
-          <t>TD1@300</t>
+          <t>TC2@300</t>
         </is>
       </c>
       <c r="C67" s="17" t="n"/>
       <c r="D67" s="17" t="inlineStr">
         <is>
-          <t>TC3@195</t>
+          <t>TP1@195</t>
         </is>
       </c>
       <c r="E67" s="17" t="n"/>
       <c r="F67" s="17" t="inlineStr">
         <is>
-          <t>TC3@90</t>
+          <t>TC1@90</t>
         </is>
       </c>
       <c r="G67" s="17" t="n"/>
       <c r="H67" s="17" t="inlineStr">
         <is>
-          <t>TT4@30</t>
+          <t>TC2@30</t>
         </is>
       </c>
       <c r="I67" s="17" t="n"/>
       <c r="J67" s="17" t="inlineStr">
         <is>
-          <t>TC5@300</t>
+          <t>TP5@300</t>
         </is>
       </c>
       <c r="K67" s="17" t="n"/>
       <c r="L67" s="17" t="inlineStr">
         <is>
-          <t>TD1@45</t>
+          <t>TP5@45</t>
         </is>
       </c>
       <c r="M67" s="17" t="n"/>
       <c r="N67" s="17" t="inlineStr">
         <is>
-          <t>TC5@225</t>
+          <t>TP2@225</t>
         </is>
       </c>
       <c r="O67" s="17" t="n"/>
       <c r="P67" s="17" t="inlineStr">
         <is>
-          <t>TC3@210</t>
+          <t>TC1@210</t>
         </is>
       </c>
       <c r="Q67" s="17" t="n"/>
@@ -7299,49 +7385,49 @@
       <c r="W67" s="17" t="n"/>
       <c r="X67" s="17" t="inlineStr">
         <is>
-          <t>TD1@105</t>
+          <t>TC4@105</t>
         </is>
       </c>
       <c r="Y67" s="17" t="n"/>
       <c r="Z67" s="17" t="inlineStr">
         <is>
-          <t>TC1@285</t>
+          <t>TP1@285</t>
         </is>
       </c>
       <c r="AA67" s="17" t="n"/>
       <c r="AB67" s="17" t="inlineStr">
         <is>
-          <t>TT4@270</t>
+          <t>TC1@270</t>
         </is>
       </c>
       <c r="AC67" s="17" t="n"/>
       <c r="AD67" s="17" t="inlineStr">
         <is>
-          <t>TT4@75</t>
+          <t>TC1@75</t>
         </is>
       </c>
       <c r="AE67" s="17" t="n"/>
       <c r="AF67" s="17" t="inlineStr">
         <is>
-          <t>TT2@345</t>
+          <t>TP2@345</t>
         </is>
       </c>
       <c r="AG67" s="17" t="n"/>
       <c r="AH67" s="17" t="inlineStr">
         <is>
-          <t>TT4@210</t>
+          <t>TC1@210</t>
         </is>
       </c>
       <c r="AI67" s="17" t="n"/>
       <c r="AJ67" s="17" t="inlineStr">
         <is>
-          <t>TT2@285</t>
+          <t>TC2@285</t>
         </is>
       </c>
       <c r="AK67" s="17" t="n"/>
       <c r="AL67" s="17" t="inlineStr">
         <is>
-          <t>TT4@75</t>
+          <t>TP2@75</t>
         </is>
       </c>
       <c r="AM67" s="17" t="n"/>
@@ -7353,25 +7439,25 @@
       <c r="AO67" s="17" t="n"/>
       <c r="AP67" s="17" t="inlineStr">
         <is>
-          <t>TT2@285</t>
+          <t>TT5@285</t>
         </is>
       </c>
       <c r="AQ67" s="17" t="n"/>
       <c r="AR67" s="17" t="inlineStr">
         <is>
-          <t>TC1@315</t>
+          <t>TP1@315</t>
         </is>
       </c>
       <c r="AS67" s="17" t="n"/>
       <c r="AT67" s="17" t="inlineStr">
         <is>
-          <t>TT4@45</t>
+          <t>TC1@45</t>
         </is>
       </c>
       <c r="AU67" s="17" t="n"/>
       <c r="AV67" s="17" t="inlineStr">
         <is>
-          <t>TD1@180</t>
+          <t>TC2@180</t>
         </is>
       </c>
       <c r="AW67" s="17" t="n"/>
@@ -7393,19 +7479,19 @@
       <c r="L68" s="17" t="n"/>
       <c r="M68" s="17" t="inlineStr">
         <is>
-          <t>TD1@90</t>
+          <t>TC1@90</t>
         </is>
       </c>
       <c r="N68" s="17" t="n"/>
       <c r="O68" s="17" t="inlineStr">
         <is>
-          <t>TC3@150</t>
+          <t>TT2@150</t>
         </is>
       </c>
       <c r="P68" s="17" t="n"/>
       <c r="Q68" s="17" t="inlineStr">
         <is>
-          <t>TC5@345</t>
+          <t>TC2@345</t>
         </is>
       </c>
       <c r="R68" s="17" t="n"/>
@@ -7419,55 +7505,55 @@
       <c r="V68" s="17" t="n"/>
       <c r="W68" s="17" t="inlineStr">
         <is>
-          <t>TC5@120</t>
+          <t>TC4@120</t>
         </is>
       </c>
       <c r="X68" s="17" t="n"/>
       <c r="Y68" s="17" t="inlineStr">
         <is>
-          <t>TC5@300</t>
+          <t>TT2@300</t>
         </is>
       </c>
       <c r="Z68" s="17" t="n"/>
       <c r="AA68" s="17" t="inlineStr">
         <is>
-          <t>TT2@165</t>
+          <t>TC5@165</t>
         </is>
       </c>
       <c r="AB68" s="17" t="n"/>
       <c r="AC68" s="17" t="inlineStr">
         <is>
-          <t>TC1@345</t>
+          <t>TP1@345</t>
         </is>
       </c>
       <c r="AD68" s="17" t="n"/>
       <c r="AE68" s="17" t="inlineStr">
         <is>
-          <t>TT2@90</t>
+          <t>TP1@90</t>
         </is>
       </c>
       <c r="AF68" s="17" t="n"/>
       <c r="AG68" s="17" t="inlineStr">
         <is>
-          <t>TC5@75</t>
+          <t>TC2@75</t>
         </is>
       </c>
       <c r="AH68" s="17" t="n"/>
       <c r="AI68" s="17" t="inlineStr">
         <is>
-          <t>TC1@60</t>
+          <t>TC3@60</t>
         </is>
       </c>
       <c r="AJ68" s="17" t="n"/>
       <c r="AK68" s="17" t="inlineStr">
         <is>
-          <t>TD1@315</t>
+          <t>TC3@315</t>
         </is>
       </c>
       <c r="AL68" s="17" t="n"/>
       <c r="AM68" s="17" t="inlineStr">
         <is>
-          <t>TT2@315</t>
+          <t>TP5@315</t>
         </is>
       </c>
       <c r="AN68" s="17" t="n"/>
@@ -7487,49 +7573,49 @@
       </c>
       <c r="B69" s="17" t="inlineStr">
         <is>
-          <t>TD1@165</t>
+          <t>TP5@165</t>
         </is>
       </c>
       <c r="C69" s="17" t="n"/>
       <c r="D69" s="17" t="inlineStr">
         <is>
-          <t>TC3@90</t>
+          <t>TC1@90</t>
         </is>
       </c>
       <c r="E69" s="17" t="n"/>
       <c r="F69" s="17" t="inlineStr">
         <is>
-          <t>TD1@75</t>
+          <t>TC5@75</t>
         </is>
       </c>
       <c r="G69" s="17" t="n"/>
       <c r="H69" s="17" t="inlineStr">
         <is>
-          <t>TC5@60</t>
+          <t>TT5@60</t>
         </is>
       </c>
       <c r="I69" s="17" t="n"/>
       <c r="J69" s="17" t="inlineStr">
         <is>
-          <t>TC1@330</t>
+          <t>TD1@330</t>
         </is>
       </c>
       <c r="K69" s="17" t="n"/>
       <c r="L69" s="17" t="inlineStr">
         <is>
-          <t>TT4@255</t>
+          <t>TC2@255</t>
         </is>
       </c>
       <c r="M69" s="17" t="n"/>
       <c r="N69" s="17" t="inlineStr">
         <is>
-          <t>TC3@120</t>
+          <t>TC4@120</t>
         </is>
       </c>
       <c r="O69" s="17" t="n"/>
       <c r="P69" s="17" t="inlineStr">
         <is>
-          <t>TT2@105</t>
+          <t>TC2@105</t>
         </is>
       </c>
       <c r="Q69" s="17" t="n"/>
@@ -7547,25 +7633,25 @@
       <c r="Y69" s="17" t="n"/>
       <c r="Z69" s="17" t="inlineStr">
         <is>
-          <t>TC1@345</t>
+          <t>TC2@345</t>
         </is>
       </c>
       <c r="AA69" s="17" t="n"/>
       <c r="AB69" s="17" t="inlineStr">
         <is>
-          <t>TC5@30</t>
+          <t>TC2@30</t>
         </is>
       </c>
       <c r="AC69" s="17" t="n"/>
       <c r="AD69" s="17" t="inlineStr">
         <is>
-          <t>TT2@75</t>
+          <t>TC5@75</t>
         </is>
       </c>
       <c r="AE69" s="17" t="n"/>
       <c r="AF69" s="17" t="inlineStr">
         <is>
-          <t>TC5@225</t>
+          <t>TC1@225</t>
         </is>
       </c>
       <c r="AG69" s="17" t="n"/>
@@ -7575,37 +7661,37 @@
       <c r="AK69" s="17" t="n"/>
       <c r="AL69" s="17" t="inlineStr">
         <is>
-          <t>TC1@225</t>
+          <t>TP2@225</t>
         </is>
       </c>
       <c r="AM69" s="17" t="n"/>
       <c r="AN69" s="17" t="inlineStr">
         <is>
-          <t>TT4@240</t>
+          <t>TC4@240</t>
         </is>
       </c>
       <c r="AO69" s="17" t="n"/>
       <c r="AP69" s="17" t="inlineStr">
         <is>
-          <t>TD1@180</t>
+          <t>TC4@180</t>
         </is>
       </c>
       <c r="AQ69" s="17" t="n"/>
       <c r="AR69" s="17" t="inlineStr">
         <is>
-          <t>TT4@75</t>
+          <t>TP5@75</t>
         </is>
       </c>
       <c r="AS69" s="17" t="n"/>
       <c r="AT69" s="17" t="inlineStr">
         <is>
-          <t>TT4@135</t>
+          <t>TT5@135</t>
         </is>
       </c>
       <c r="AU69" s="17" t="n"/>
       <c r="AV69" s="17" t="inlineStr">
         <is>
-          <t>TT4@120</t>
+          <t>TD1@120</t>
         </is>
       </c>
       <c r="AW69" s="17" t="n"/>
@@ -7627,19 +7713,19 @@
       <c r="L70" s="17" t="n"/>
       <c r="M70" s="17" t="inlineStr">
         <is>
-          <t>TC1@90</t>
+          <t>TP2@90</t>
         </is>
       </c>
       <c r="N70" s="17" t="n"/>
       <c r="O70" s="17" t="inlineStr">
         <is>
-          <t>TT2@315</t>
+          <t>TP2@315</t>
         </is>
       </c>
       <c r="P70" s="17" t="n"/>
       <c r="Q70" s="17" t="inlineStr">
         <is>
-          <t>TC1@285</t>
+          <t>TC4@285</t>
         </is>
       </c>
       <c r="R70" s="17" t="n"/>
@@ -7659,19 +7745,19 @@
       <c r="X70" s="17" t="n"/>
       <c r="Y70" s="17" t="inlineStr">
         <is>
-          <t>TC5@45</t>
+          <t>TC2@45</t>
         </is>
       </c>
       <c r="Z70" s="17" t="n"/>
       <c r="AA70" s="17" t="inlineStr">
         <is>
-          <t>TC5@180</t>
+          <t>TC3@180</t>
         </is>
       </c>
       <c r="AB70" s="17" t="n"/>
       <c r="AC70" s="17" t="inlineStr">
         <is>
-          <t>TC3@300</t>
+          <t>TC1@300</t>
         </is>
       </c>
       <c r="AD70" s="17" t="n"/>
@@ -7687,19 +7773,19 @@
       <c r="AJ70" s="17" t="n"/>
       <c r="AK70" s="17" t="inlineStr">
         <is>
-          <t>TC3@165</t>
+          <t>TC1@165</t>
         </is>
       </c>
       <c r="AL70" s="17" t="n"/>
       <c r="AM70" s="17" t="inlineStr">
         <is>
-          <t>TT2@135</t>
+          <t>TC2@135</t>
         </is>
       </c>
       <c r="AN70" s="17" t="n"/>
       <c r="AO70" s="17" t="inlineStr">
         <is>
-          <t>TT2@15</t>
+          <t>TP2@15</t>
         </is>
       </c>
       <c r="AP70" s="17" t="n"/>
@@ -7717,49 +7803,49 @@
       </c>
       <c r="B71" s="17" t="inlineStr">
         <is>
-          <t>TT4@300</t>
+          <t>TP1@300</t>
         </is>
       </c>
       <c r="C71" s="17" t="n"/>
       <c r="D71" s="17" t="inlineStr">
         <is>
-          <t>TC3@255</t>
+          <t>TC2@255</t>
         </is>
       </c>
       <c r="E71" s="17" t="n"/>
       <c r="F71" s="17" t="inlineStr">
         <is>
-          <t>TT4@120</t>
+          <t>TP5@120</t>
         </is>
       </c>
       <c r="G71" s="17" t="n"/>
       <c r="H71" s="17" t="inlineStr">
         <is>
-          <t>TD1@315</t>
+          <t>TT2@315</t>
         </is>
       </c>
       <c r="I71" s="17" t="n"/>
       <c r="J71" s="17" t="inlineStr">
         <is>
-          <t>TC5@180</t>
+          <t>TC3@180</t>
         </is>
       </c>
       <c r="K71" s="17" t="n"/>
       <c r="L71" s="17" t="inlineStr">
         <is>
-          <t>TC5@120</t>
+          <t>TT5@120</t>
         </is>
       </c>
       <c r="M71" s="17" t="n"/>
       <c r="N71" s="17" t="inlineStr">
         <is>
-          <t>TC5@315</t>
+          <t>TP1@315</t>
         </is>
       </c>
       <c r="O71" s="17" t="n"/>
       <c r="P71" s="17" t="inlineStr">
         <is>
-          <t>TD1@30</t>
+          <t>TP2@30</t>
         </is>
       </c>
       <c r="Q71" s="17" t="n"/>
@@ -7793,37 +7879,37 @@
       <c r="AK71" s="17" t="n"/>
       <c r="AL71" s="17" t="inlineStr">
         <is>
-          <t>TT2@300</t>
+          <t>TP2@300</t>
         </is>
       </c>
       <c r="AM71" s="17" t="n"/>
       <c r="AN71" s="17" t="inlineStr">
         <is>
-          <t>TT2@90</t>
+          <t>TC4@90</t>
         </is>
       </c>
       <c r="AO71" s="17" t="n"/>
       <c r="AP71" s="17" t="inlineStr">
         <is>
-          <t>TC1@150</t>
+          <t>TP1@150</t>
         </is>
       </c>
       <c r="AQ71" s="17" t="n"/>
       <c r="AR71" s="17" t="inlineStr">
         <is>
-          <t>TC1@135</t>
+          <t>TC5@135</t>
         </is>
       </c>
       <c r="AS71" s="17" t="n"/>
       <c r="AT71" s="17" t="inlineStr">
         <is>
-          <t>TD1@60</t>
+          <t>TC1@60</t>
         </is>
       </c>
       <c r="AU71" s="17" t="n"/>
       <c r="AV71" s="17" t="inlineStr">
         <is>
-          <t>TC1@240</t>
+          <t>TP2@240</t>
         </is>
       </c>
       <c r="AW71" s="17" t="n"/>
@@ -7843,25 +7929,25 @@
       <c r="J72" s="17" t="n"/>
       <c r="K72" s="17" t="inlineStr">
         <is>
-          <t>TT2@255</t>
+          <t>TC5@255</t>
         </is>
       </c>
       <c r="L72" s="17" t="n"/>
       <c r="M72" s="17" t="inlineStr">
         <is>
-          <t>TT2@255</t>
+          <t>TC5@255</t>
         </is>
       </c>
       <c r="N72" s="17" t="n"/>
       <c r="O72" s="17" t="inlineStr">
         <is>
-          <t>TC5@255</t>
+          <t>TT5@255</t>
         </is>
       </c>
       <c r="P72" s="17" t="n"/>
       <c r="Q72" s="17" t="inlineStr">
         <is>
-          <t>TC5@285</t>
+          <t>TD1@285</t>
         </is>
       </c>
       <c r="R72" s="17" t="n"/>
@@ -7905,19 +7991,19 @@
       <c r="AJ72" s="17" t="n"/>
       <c r="AK72" s="17" t="inlineStr">
         <is>
-          <t>TT4@285</t>
+          <t>TD1@285</t>
         </is>
       </c>
       <c r="AL72" s="17" t="n"/>
       <c r="AM72" s="17" t="inlineStr">
         <is>
-          <t>TC1@210</t>
+          <t>TP2@210</t>
         </is>
       </c>
       <c r="AN72" s="17" t="n"/>
       <c r="AO72" s="17" t="inlineStr">
         <is>
-          <t>TT4@330</t>
+          <t>TP1@330</t>
         </is>
       </c>
       <c r="AP72" s="17" t="n"/>
@@ -7935,49 +8021,49 @@
       </c>
       <c r="B73" s="17" t="inlineStr">
         <is>
-          <t>TD1@165</t>
+          <t>TC2@165</t>
         </is>
       </c>
       <c r="C73" s="17" t="n"/>
       <c r="D73" s="17" t="inlineStr">
         <is>
-          <t>TC1@120</t>
+          <t>TC3@120</t>
         </is>
       </c>
       <c r="E73" s="17" t="n"/>
       <c r="F73" s="17" t="inlineStr">
         <is>
-          <t>TC5@105</t>
+          <t>TC3@105</t>
         </is>
       </c>
       <c r="G73" s="17" t="n"/>
       <c r="H73" s="17" t="inlineStr">
         <is>
-          <t>TC1@315</t>
+          <t>TC3@315</t>
         </is>
       </c>
       <c r="I73" s="17" t="n"/>
       <c r="J73" s="17" t="inlineStr">
         <is>
-          <t>TT4@105</t>
+          <t>TC5@105</t>
         </is>
       </c>
       <c r="K73" s="17" t="n"/>
       <c r="L73" s="17" t="inlineStr">
         <is>
-          <t>TD1@330</t>
+          <t>TC3@330</t>
         </is>
       </c>
       <c r="M73" s="17" t="n"/>
       <c r="N73" s="17" t="inlineStr">
         <is>
-          <t>TT2@255</t>
+          <t>TP1@255</t>
         </is>
       </c>
       <c r="O73" s="17" t="n"/>
       <c r="P73" s="17" t="inlineStr">
         <is>
-          <t>TD1@105</t>
+          <t>TC3@105</t>
         </is>
       </c>
       <c r="Q73" s="17" t="n"/>
@@ -8011,25 +8097,25 @@
       <c r="AK73" s="17" t="n"/>
       <c r="AL73" s="17" t="inlineStr">
         <is>
-          <t>TC1@75</t>
+          <t>TT5@75</t>
         </is>
       </c>
       <c r="AM73" s="17" t="n"/>
       <c r="AN73" s="17" t="inlineStr">
         <is>
-          <t>TC5@30</t>
+          <t>TP1@30</t>
         </is>
       </c>
       <c r="AO73" s="17" t="n"/>
       <c r="AP73" s="17" t="inlineStr">
         <is>
-          <t>TC5@345</t>
+          <t>TP1@345</t>
         </is>
       </c>
       <c r="AQ73" s="17" t="n"/>
       <c r="AR73" s="17" t="inlineStr">
         <is>
-          <t>TT2@180</t>
+          <t>TT4@180</t>
         </is>
       </c>
       <c r="AS73" s="17" t="n"/>
@@ -8041,7 +8127,7 @@
       <c r="AU73" s="17" t="n"/>
       <c r="AV73" s="17" t="inlineStr">
         <is>
-          <t>TC3@210</t>
+          <t>TC1@210</t>
         </is>
       </c>
       <c r="AW73" s="17" t="n"/>
@@ -8061,19 +8147,19 @@
       <c r="J74" s="17" t="n"/>
       <c r="K74" s="17" t="inlineStr">
         <is>
-          <t>TT2@30</t>
+          <t>TC4@30</t>
         </is>
       </c>
       <c r="L74" s="17" t="n"/>
       <c r="M74" s="17" t="inlineStr">
         <is>
-          <t>TT2@120</t>
+          <t>TC3@120</t>
         </is>
       </c>
       <c r="N74" s="17" t="n"/>
       <c r="O74" s="17" t="inlineStr">
         <is>
-          <t>TD1@30</t>
+          <t>TC5@30</t>
         </is>
       </c>
       <c r="P74" s="17" t="n"/>
@@ -8089,7 +8175,7 @@
       <c r="V74" s="17" t="n"/>
       <c r="W74" s="17" t="inlineStr">
         <is>
-          <t>TC3@75</t>
+          <t>TC2@75</t>
         </is>
       </c>
       <c r="X74" s="17" t="n"/>
@@ -8109,7 +8195,7 @@
       <c r="AD74" s="17" t="n"/>
       <c r="AE74" s="17" t="inlineStr">
         <is>
-          <t>TC3@105</t>
+          <t>TC4@105</t>
         </is>
       </c>
       <c r="AF74" s="17" t="n"/>
@@ -8123,19 +8209,19 @@
       <c r="AJ74" s="17" t="n"/>
       <c r="AK74" s="17" t="inlineStr">
         <is>
-          <t>TC3@270</t>
+          <t>TC2@270</t>
         </is>
       </c>
       <c r="AL74" s="17" t="n"/>
       <c r="AM74" s="17" t="inlineStr">
         <is>
-          <t>TC5@285</t>
+          <t>TC1@285</t>
         </is>
       </c>
       <c r="AN74" s="17" t="n"/>
       <c r="AO74" s="17" t="inlineStr">
         <is>
-          <t>TC5@75</t>
+          <t>TC2@75</t>
         </is>
       </c>
       <c r="AP74" s="17" t="n"/>
@@ -8153,43 +8239,43 @@
       </c>
       <c r="B75" s="17" t="inlineStr">
         <is>
-          <t>TT2</t>
+          <t>TP2</t>
         </is>
       </c>
       <c r="C75" s="17" t="n"/>
       <c r="D75" s="17" t="inlineStr">
         <is>
-          <t>TT4@345</t>
+          <t>TC1@345</t>
         </is>
       </c>
       <c r="E75" s="17" t="n"/>
       <c r="F75" s="17" t="inlineStr">
         <is>
-          <t>TT4@180</t>
+          <t>TP5@180</t>
         </is>
       </c>
       <c r="G75" s="17" t="n"/>
       <c r="H75" s="17" t="inlineStr">
         <is>
-          <t>TC1@135</t>
+          <t>TC3@135</t>
         </is>
       </c>
       <c r="I75" s="17" t="n"/>
       <c r="J75" s="17" t="inlineStr">
         <is>
-          <t>TT4@60</t>
+          <t>TC2@60</t>
         </is>
       </c>
       <c r="K75" s="17" t="n"/>
       <c r="L75" s="17" t="inlineStr">
         <is>
-          <t>TC3@270</t>
+          <t>TP2@270</t>
         </is>
       </c>
       <c r="M75" s="17" t="n"/>
       <c r="N75" s="17" t="inlineStr">
         <is>
-          <t>TD1@90</t>
+          <t>TC1@90</t>
         </is>
       </c>
       <c r="O75" s="17" t="n"/>
@@ -8215,7 +8301,7 @@
       <c r="W75" s="17" t="n"/>
       <c r="X75" s="17" t="inlineStr">
         <is>
-          <t>TT2@60</t>
+          <t>TC1@60</t>
         </is>
       </c>
       <c r="Y75" s="17" t="n"/>
@@ -8237,37 +8323,37 @@
       <c r="AK75" s="17" t="n"/>
       <c r="AL75" s="17" t="inlineStr">
         <is>
-          <t>TC5@210</t>
+          <t>TP5@210</t>
         </is>
       </c>
       <c r="AM75" s="17" t="n"/>
       <c r="AN75" s="17" t="inlineStr">
         <is>
-          <t>TC5@60</t>
+          <t>TC4@60</t>
         </is>
       </c>
       <c r="AO75" s="17" t="n"/>
       <c r="AP75" s="17" t="inlineStr">
         <is>
-          <t>TD1@75</t>
+          <t>TC3@75</t>
         </is>
       </c>
       <c r="AQ75" s="17" t="n"/>
       <c r="AR75" s="17" t="inlineStr">
         <is>
-          <t>TT4@195</t>
+          <t>TC5@195</t>
         </is>
       </c>
       <c r="AS75" s="17" t="n"/>
       <c r="AT75" s="17" t="inlineStr">
         <is>
-          <t>TT2@315</t>
+          <t>TC4@315</t>
         </is>
       </c>
       <c r="AU75" s="17" t="n"/>
       <c r="AV75" s="17" t="inlineStr">
         <is>
-          <t>TT4@30</t>
+          <t>TP1@30</t>
         </is>
       </c>
       <c r="AW75" s="17" t="n"/>
@@ -8285,19 +8371,19 @@
       <c r="H76" s="17" t="n"/>
       <c r="I76" s="17" t="inlineStr">
         <is>
-          <t>TC1@285</t>
+          <t>TP2@285</t>
         </is>
       </c>
       <c r="J76" s="17" t="n"/>
       <c r="K76" s="17" t="inlineStr">
         <is>
-          <t>TD1@300</t>
+          <t>TC1@300</t>
         </is>
       </c>
       <c r="L76" s="17" t="n"/>
       <c r="M76" s="17" t="inlineStr">
         <is>
-          <t>TC3@180</t>
+          <t>TP5@180</t>
         </is>
       </c>
       <c r="N76" s="17" t="n"/>
@@ -8313,19 +8399,19 @@
       <c r="T76" s="17" t="n"/>
       <c r="U76" s="17" t="inlineStr">
         <is>
-          <t>TC5@105</t>
+          <t>TC2@105</t>
         </is>
       </c>
       <c r="V76" s="17" t="n"/>
       <c r="W76" s="17" t="inlineStr">
         <is>
-          <t>TC1@210</t>
+          <t>TT5@210</t>
         </is>
       </c>
       <c r="X76" s="17" t="n"/>
       <c r="Y76" s="17" t="inlineStr">
         <is>
-          <t>TC1@240</t>
+          <t>TC3@240</t>
         </is>
       </c>
       <c r="Z76" s="17" t="n"/>
@@ -8339,7 +8425,7 @@
       <c r="AD76" s="17" t="n"/>
       <c r="AE76" s="17" t="inlineStr">
         <is>
-          <t>TC1@15</t>
+          <t>TC4@15</t>
         </is>
       </c>
       <c r="AF76" s="17" t="n"/>
@@ -8349,19 +8435,19 @@
       <c r="AJ76" s="17" t="n"/>
       <c r="AK76" s="17" t="inlineStr">
         <is>
-          <t>TT2@60</t>
+          <t>TP1@60</t>
         </is>
       </c>
       <c r="AL76" s="17" t="n"/>
       <c r="AM76" s="17" t="inlineStr">
         <is>
-          <t>TT2@45</t>
+          <t>TP2@45</t>
         </is>
       </c>
       <c r="AN76" s="17" t="n"/>
       <c r="AO76" s="17" t="inlineStr">
         <is>
-          <t>TT4@45</t>
+          <t>TC4@45</t>
         </is>
       </c>
       <c r="AP76" s="17" t="n"/>
@@ -8379,31 +8465,31 @@
       </c>
       <c r="B77" s="17" t="inlineStr">
         <is>
-          <t>TT2@225</t>
+          <t>TT4@225</t>
         </is>
       </c>
       <c r="C77" s="17" t="n"/>
       <c r="D77" s="17" t="inlineStr">
         <is>
-          <t>TD1@345</t>
+          <t>TP1@345</t>
         </is>
       </c>
       <c r="E77" s="17" t="n"/>
       <c r="F77" s="17" t="inlineStr">
         <is>
-          <t>TD1@30</t>
+          <t>TT4@30</t>
         </is>
       </c>
       <c r="G77" s="17" t="n"/>
       <c r="H77" s="17" t="inlineStr">
         <is>
-          <t>TT4@330</t>
+          <t>TC1@330</t>
         </is>
       </c>
       <c r="I77" s="17" t="n"/>
       <c r="J77" s="17" t="inlineStr">
         <is>
-          <t>TC3</t>
+          <t>TC1</t>
         </is>
       </c>
       <c r="K77" s="17" t="n"/>
@@ -8415,7 +8501,7 @@
       <c r="M77" s="17" t="n"/>
       <c r="N77" s="17" t="inlineStr">
         <is>
-          <t>TC3@195</t>
+          <t>TP2@195</t>
         </is>
       </c>
       <c r="O77" s="17" t="n"/>
@@ -8425,13 +8511,13 @@
       <c r="S77" s="17" t="n"/>
       <c r="T77" s="17" t="inlineStr">
         <is>
-          <t>TC3@75</t>
+          <t>TC4@75</t>
         </is>
       </c>
       <c r="U77" s="17" t="n"/>
       <c r="V77" s="17" t="inlineStr">
         <is>
-          <t>TC5@135</t>
+          <t>TC4@135</t>
         </is>
       </c>
       <c r="W77" s="17" t="n"/>
@@ -8449,7 +8535,7 @@
       <c r="AE77" s="17" t="n"/>
       <c r="AF77" s="17" t="inlineStr">
         <is>
-          <t>TC1@225</t>
+          <t>TC3@225</t>
         </is>
       </c>
       <c r="AG77" s="17" t="n"/>
@@ -8461,19 +8547,19 @@
       <c r="AI77" s="17" t="n"/>
       <c r="AJ77" s="17" t="inlineStr">
         <is>
-          <t>TD1@180</t>
+          <t>TC1@180</t>
         </is>
       </c>
       <c r="AK77" s="17" t="n"/>
       <c r="AL77" s="17" t="inlineStr">
         <is>
-          <t>TD1@30</t>
+          <t>TC2@30</t>
         </is>
       </c>
       <c r="AM77" s="17" t="n"/>
       <c r="AN77" s="17" t="inlineStr">
         <is>
-          <t>TT2@135</t>
+          <t>TC3@135</t>
         </is>
       </c>
       <c r="AO77" s="17" t="n"/>
@@ -8485,19 +8571,19 @@
       <c r="AQ77" s="17" t="n"/>
       <c r="AR77" s="17" t="inlineStr">
         <is>
-          <t>TT2@285</t>
+          <t>TC3@285</t>
         </is>
       </c>
       <c r="AS77" s="17" t="n"/>
       <c r="AT77" s="17" t="inlineStr">
         <is>
-          <t>TC5@120</t>
+          <t>TC2@120</t>
         </is>
       </c>
       <c r="AU77" s="17" t="n"/>
       <c r="AV77" s="17" t="inlineStr">
         <is>
-          <t>TT2@225</t>
+          <t>TT4@225</t>
         </is>
       </c>
       <c r="AW77" s="17" t="n"/>
@@ -8517,19 +8603,19 @@
       <c r="J78" s="17" t="n"/>
       <c r="K78" s="17" t="inlineStr">
         <is>
-          <t>TC3@270</t>
+          <t>TP2@270</t>
         </is>
       </c>
       <c r="L78" s="17" t="n"/>
       <c r="M78" s="17" t="inlineStr">
         <is>
-          <t>TT4@240</t>
+          <t>TC5@240</t>
         </is>
       </c>
       <c r="N78" s="17" t="n"/>
       <c r="O78" s="17" t="inlineStr">
         <is>
-          <t>TC3@60</t>
+          <t>TC1@60</t>
         </is>
       </c>
       <c r="P78" s="17" t="n"/>
@@ -8537,19 +8623,19 @@
       <c r="R78" s="17" t="n"/>
       <c r="S78" s="17" t="inlineStr">
         <is>
-          <t>TC5@135</t>
+          <t>TC3@135</t>
         </is>
       </c>
       <c r="T78" s="17" t="n"/>
       <c r="U78" s="17" t="inlineStr">
         <is>
-          <t>TT2@285</t>
+          <t>TC2@285</t>
         </is>
       </c>
       <c r="V78" s="17" t="n"/>
       <c r="W78" s="17" t="inlineStr">
         <is>
-          <t>TC3</t>
+          <t>TC4</t>
         </is>
       </c>
       <c r="X78" s="17" t="n"/>
@@ -8569,7 +8655,7 @@
       <c r="AD78" s="17" t="n"/>
       <c r="AE78" s="17" t="inlineStr">
         <is>
-          <t>TC3</t>
+          <t>TD1</t>
         </is>
       </c>
       <c r="AF78" s="17" t="n"/>
@@ -8585,13 +8671,13 @@
       <c r="AL78" s="17" t="n"/>
       <c r="AM78" s="17" t="inlineStr">
         <is>
-          <t>TD1@45</t>
+          <t>TC5@45</t>
         </is>
       </c>
       <c r="AN78" s="17" t="n"/>
       <c r="AO78" s="17" t="inlineStr">
         <is>
-          <t>TC1@315</t>
+          <t>TP2@315</t>
         </is>
       </c>
       <c r="AP78" s="17" t="n"/>
@@ -8609,19 +8695,19 @@
       </c>
       <c r="B79" s="17" t="inlineStr">
         <is>
-          <t>TC1</t>
+          <t>TP2</t>
         </is>
       </c>
       <c r="C79" s="17" t="n"/>
       <c r="D79" s="17" t="inlineStr">
         <is>
-          <t>TC3@165</t>
+          <t>TT4@165</t>
         </is>
       </c>
       <c r="E79" s="17" t="n"/>
       <c r="F79" s="17" t="inlineStr">
         <is>
-          <t>TC1@240</t>
+          <t>TC2@240</t>
         </is>
       </c>
       <c r="G79" s="17" t="n"/>
@@ -8633,43 +8719,43 @@
       <c r="I79" s="17" t="n"/>
       <c r="J79" s="17" t="inlineStr">
         <is>
-          <t>TC1@345</t>
+          <t>TP2@345</t>
         </is>
       </c>
       <c r="K79" s="17" t="n"/>
       <c r="L79" s="17" t="inlineStr">
         <is>
-          <t>TC3@90</t>
+          <t>TC1@90</t>
         </is>
       </c>
       <c r="M79" s="17" t="n"/>
       <c r="N79" s="17" t="inlineStr">
         <is>
-          <t>TT4@330</t>
+          <t>TC1@330</t>
         </is>
       </c>
       <c r="O79" s="17" t="n"/>
       <c r="P79" s="17" t="inlineStr">
         <is>
-          <t>TC3@150</t>
+          <t>TC1@150</t>
         </is>
       </c>
       <c r="Q79" s="17" t="n"/>
       <c r="R79" s="17" t="inlineStr">
         <is>
-          <t>TC3@45</t>
+          <t>TC5@45</t>
         </is>
       </c>
       <c r="S79" s="17" t="n"/>
       <c r="T79" s="17" t="inlineStr">
         <is>
-          <t>TT4@15</t>
+          <t>TC5@15</t>
         </is>
       </c>
       <c r="U79" s="17" t="n"/>
       <c r="V79" s="17" t="inlineStr">
         <is>
-          <t>TC3@120</t>
+          <t>TC2@120</t>
         </is>
       </c>
       <c r="W79" s="17" t="n"/>
@@ -8687,25 +8773,25 @@
       <c r="AE79" s="17" t="n"/>
       <c r="AF79" s="17" t="inlineStr">
         <is>
-          <t>TC5@75</t>
+          <t>TT5@75</t>
         </is>
       </c>
       <c r="AG79" s="17" t="n"/>
       <c r="AH79" s="17" t="inlineStr">
         <is>
-          <t>TD1@285</t>
+          <t>TC4@285</t>
         </is>
       </c>
       <c r="AI79" s="17" t="n"/>
       <c r="AJ79" s="17" t="inlineStr">
         <is>
-          <t>TC5@90</t>
+          <t>TC2@90</t>
         </is>
       </c>
       <c r="AK79" s="17" t="n"/>
       <c r="AL79" s="17" t="inlineStr">
         <is>
-          <t>TT4@45</t>
+          <t>TC2@45</t>
         </is>
       </c>
       <c r="AM79" s="17" t="n"/>
@@ -8717,7 +8803,7 @@
       <c r="AO79" s="17" t="n"/>
       <c r="AP79" s="17" t="inlineStr">
         <is>
-          <t>TT4@135</t>
+          <t>TP1@135</t>
         </is>
       </c>
       <c r="AQ79" s="17" t="n"/>
@@ -8729,13 +8815,13 @@
       <c r="AS79" s="17" t="n"/>
       <c r="AT79" s="17" t="inlineStr">
         <is>
-          <t>TD1@45</t>
+          <t>TC5@45</t>
         </is>
       </c>
       <c r="AU79" s="17" t="n"/>
       <c r="AV79" s="17" t="inlineStr">
         <is>
-          <t>TT4@15</t>
+          <t>TC5@15</t>
         </is>
       </c>
       <c r="AW79" s="17" t="n"/>
@@ -8755,37 +8841,37 @@
       <c r="J80" s="17" t="n"/>
       <c r="K80" s="17" t="inlineStr">
         <is>
-          <t>TC1@240</t>
+          <t>TP2@240</t>
         </is>
       </c>
       <c r="L80" s="17" t="n"/>
       <c r="M80" s="17" t="inlineStr">
         <is>
-          <t>TC3@165</t>
+          <t>TC2@165</t>
         </is>
       </c>
       <c r="N80" s="17" t="n"/>
       <c r="O80" s="17" t="inlineStr">
         <is>
-          <t>TC3@270</t>
+          <t>TP5@270</t>
         </is>
       </c>
       <c r="P80" s="17" t="n"/>
       <c r="Q80" s="17" t="inlineStr">
         <is>
-          <t>TC5@330</t>
+          <t>TC1@330</t>
         </is>
       </c>
       <c r="R80" s="17" t="n"/>
       <c r="S80" s="17" t="inlineStr">
         <is>
-          <t>TT2@150</t>
+          <t>TP2@150</t>
         </is>
       </c>
       <c r="T80" s="17" t="n"/>
       <c r="U80" s="17" t="inlineStr">
         <is>
-          <t>TC1@210</t>
+          <t>TC2@210</t>
         </is>
       </c>
       <c r="V80" s="17" t="n"/>
@@ -8795,43 +8881,43 @@
       <c r="Z80" s="17" t="n"/>
       <c r="AA80" s="17" t="inlineStr">
         <is>
-          <t>TC3@225</t>
+          <t>TT2@225</t>
         </is>
       </c>
       <c r="AB80" s="17" t="n"/>
       <c r="AC80" s="17" t="inlineStr">
         <is>
-          <t>TC5@120</t>
+          <t>TC3@120</t>
         </is>
       </c>
       <c r="AD80" s="17" t="n"/>
       <c r="AE80" s="17" t="inlineStr">
         <is>
-          <t>TD1@255</t>
+          <t>TP1@255</t>
         </is>
       </c>
       <c r="AF80" s="17" t="n"/>
       <c r="AG80" s="17" t="inlineStr">
         <is>
-          <t>TC3@15</t>
+          <t>TC5@15</t>
         </is>
       </c>
       <c r="AH80" s="17" t="n"/>
       <c r="AI80" s="17" t="inlineStr">
         <is>
-          <t>TC3@195</t>
+          <t>TC4@195</t>
         </is>
       </c>
       <c r="AJ80" s="17" t="n"/>
       <c r="AK80" s="17" t="inlineStr">
         <is>
-          <t>TC5@30</t>
+          <t>TT4@30</t>
         </is>
       </c>
       <c r="AL80" s="17" t="n"/>
       <c r="AM80" s="17" t="inlineStr">
         <is>
-          <t>TC1@120</t>
+          <t>TC4@120</t>
         </is>
       </c>
       <c r="AN80" s="17" t="n"/>
@@ -8851,55 +8937,55 @@
       </c>
       <c r="B81" s="17" t="inlineStr">
         <is>
-          <t>TT4@210</t>
+          <t>TP5@210</t>
         </is>
       </c>
       <c r="C81" s="17" t="n"/>
       <c r="D81" s="17" t="inlineStr">
         <is>
-          <t>TT4@105</t>
+          <t>TC4@105</t>
         </is>
       </c>
       <c r="E81" s="17" t="n"/>
       <c r="F81" s="17" t="inlineStr">
         <is>
-          <t>TC3@165</t>
+          <t>TP5@165</t>
         </is>
       </c>
       <c r="G81" s="17" t="n"/>
       <c r="H81" s="17" t="inlineStr">
         <is>
-          <t>TC1@105</t>
+          <t>TC5@105</t>
         </is>
       </c>
       <c r="I81" s="17" t="n"/>
       <c r="J81" s="17" t="inlineStr">
         <is>
-          <t>TT2@150</t>
+          <t>TC2@150</t>
         </is>
       </c>
       <c r="K81" s="17" t="n"/>
       <c r="L81" s="17" t="inlineStr">
         <is>
-          <t>TT2@150</t>
+          <t>TD1@150</t>
         </is>
       </c>
       <c r="M81" s="17" t="n"/>
       <c r="N81" s="17" t="inlineStr">
         <is>
-          <t>TT2@195</t>
+          <t>TC5@195</t>
         </is>
       </c>
       <c r="O81" s="17" t="n"/>
       <c r="P81" s="17" t="inlineStr">
         <is>
-          <t>TC1@255</t>
+          <t>TT2@255</t>
         </is>
       </c>
       <c r="Q81" s="17" t="n"/>
       <c r="R81" s="17" t="inlineStr">
         <is>
-          <t>TD1@135</t>
+          <t>TC5@135</t>
         </is>
       </c>
       <c r="S81" s="17" t="n"/>
@@ -8925,67 +9011,67 @@
       <c r="AA81" s="17" t="n"/>
       <c r="AB81" s="17" t="inlineStr">
         <is>
-          <t>TD1@150</t>
+          <t>TC3@150</t>
         </is>
       </c>
       <c r="AC81" s="17" t="n"/>
       <c r="AD81" s="17" t="inlineStr">
         <is>
-          <t>TC3@45</t>
+          <t>TD1@45</t>
         </is>
       </c>
       <c r="AE81" s="17" t="n"/>
       <c r="AF81" s="17" t="inlineStr">
         <is>
-          <t>TD1@15</t>
+          <t>TP1@15</t>
         </is>
       </c>
       <c r="AG81" s="17" t="n"/>
       <c r="AH81" s="17" t="inlineStr">
         <is>
-          <t>TD1@315</t>
+          <t>TP5@315</t>
         </is>
       </c>
       <c r="AI81" s="17" t="n"/>
       <c r="AJ81" s="17" t="inlineStr">
         <is>
-          <t>TD1@75</t>
+          <t>TC2@75</t>
         </is>
       </c>
       <c r="AK81" s="17" t="n"/>
       <c r="AL81" s="17" t="inlineStr">
         <is>
-          <t>TT2@15</t>
+          <t>TP2@15</t>
         </is>
       </c>
       <c r="AM81" s="17" t="n"/>
       <c r="AN81" s="17" t="inlineStr">
         <is>
-          <t>TT4@210</t>
+          <t>TC4@210</t>
         </is>
       </c>
       <c r="AO81" s="17" t="n"/>
       <c r="AP81" s="17" t="inlineStr">
         <is>
-          <t>TT4@330</t>
+          <t>TC2@330</t>
         </is>
       </c>
       <c r="AQ81" s="17" t="n"/>
       <c r="AR81" s="17" t="inlineStr">
         <is>
-          <t>TD1@75</t>
+          <t>TT5@75</t>
         </is>
       </c>
       <c r="AS81" s="17" t="n"/>
       <c r="AT81" s="17" t="inlineStr">
         <is>
-          <t>TC5@75</t>
+          <t>TC3@75</t>
         </is>
       </c>
       <c r="AU81" s="17" t="n"/>
       <c r="AV81" s="17" t="inlineStr">
         <is>
-          <t>TC5@345</t>
+          <t>TC1@345</t>
         </is>
       </c>
       <c r="AW81" s="17" t="n"/>
@@ -9007,13 +9093,13 @@
       <c r="L82" s="17" t="n"/>
       <c r="M82" s="17" t="inlineStr">
         <is>
-          <t>TD1@240</t>
+          <t>TC3@240</t>
         </is>
       </c>
       <c r="N82" s="17" t="n"/>
       <c r="O82" s="17" t="inlineStr">
         <is>
-          <t>TT4</t>
+          <t>TC4</t>
         </is>
       </c>
       <c r="P82" s="17" t="n"/>
@@ -9025,13 +9111,13 @@
       <c r="R82" s="17" t="n"/>
       <c r="S82" s="17" t="inlineStr">
         <is>
-          <t>TT2</t>
+          <t>TC4</t>
         </is>
       </c>
       <c r="T82" s="17" t="n"/>
       <c r="U82" s="17" t="inlineStr">
         <is>
-          <t>TT2@270</t>
+          <t>TC5@270</t>
         </is>
       </c>
       <c r="V82" s="17" t="n"/>
@@ -9051,25 +9137,25 @@
       <c r="AB82" s="17" t="n"/>
       <c r="AC82" s="17" t="inlineStr">
         <is>
-          <t>TC3@15</t>
+          <t>TC4@15</t>
         </is>
       </c>
       <c r="AD82" s="17" t="n"/>
       <c r="AE82" s="17" t="inlineStr">
         <is>
-          <t>TT4@255</t>
+          <t>TC5@255</t>
         </is>
       </c>
       <c r="AF82" s="17" t="n"/>
       <c r="AG82" s="17" t="inlineStr">
         <is>
-          <t>TC3@285</t>
+          <t>TP5@285</t>
         </is>
       </c>
       <c r="AH82" s="17" t="n"/>
       <c r="AI82" s="17" t="inlineStr">
         <is>
-          <t>TC1@120</t>
+          <t>TC5@120</t>
         </is>
       </c>
       <c r="AJ82" s="17" t="n"/>
@@ -9093,61 +9179,61 @@
       </c>
       <c r="B83" s="17" t="inlineStr">
         <is>
-          <t>TT4@105</t>
+          <t>TP2@105</t>
         </is>
       </c>
       <c r="C83" s="17" t="n"/>
       <c r="D83" s="17" t="inlineStr">
         <is>
-          <t>TD1@30</t>
+          <t>TP5@30</t>
         </is>
       </c>
       <c r="E83" s="17" t="n"/>
       <c r="F83" s="17" t="inlineStr">
         <is>
-          <t>TC3@30</t>
+          <t>TC5@30</t>
         </is>
       </c>
       <c r="G83" s="17" t="n"/>
       <c r="H83" s="17" t="inlineStr">
         <is>
-          <t>TC1@120</t>
+          <t>TP1@120</t>
         </is>
       </c>
       <c r="I83" s="17" t="n"/>
       <c r="J83" s="17" t="inlineStr">
         <is>
-          <t>TC3</t>
+          <t>TD1</t>
         </is>
       </c>
       <c r="K83" s="17" t="n"/>
       <c r="L83" s="17" t="inlineStr">
         <is>
-          <t>TC1@120</t>
+          <t>TD1@120</t>
         </is>
       </c>
       <c r="M83" s="17" t="n"/>
       <c r="N83" s="17" t="inlineStr">
         <is>
-          <t>TT4@45</t>
+          <t>TP2@45</t>
         </is>
       </c>
       <c r="O83" s="17" t="n"/>
       <c r="P83" s="17" t="inlineStr">
         <is>
-          <t>TT2@240</t>
+          <t>TC1@240</t>
         </is>
       </c>
       <c r="Q83" s="17" t="n"/>
       <c r="R83" s="17" t="inlineStr">
         <is>
-          <t>TT2@60</t>
+          <t>TC2@60</t>
         </is>
       </c>
       <c r="S83" s="17" t="n"/>
       <c r="T83" s="17" t="inlineStr">
         <is>
-          <t>TC3@165</t>
+          <t>TP5@165</t>
         </is>
       </c>
       <c r="U83" s="17" t="n"/>
@@ -9163,67 +9249,67 @@
       <c r="AA83" s="17" t="n"/>
       <c r="AB83" s="17" t="inlineStr">
         <is>
-          <t>TT2@210</t>
+          <t>TC3@210</t>
         </is>
       </c>
       <c r="AC83" s="17" t="n"/>
       <c r="AD83" s="17" t="inlineStr">
         <is>
-          <t>TD1@195</t>
+          <t>TC5@195</t>
         </is>
       </c>
       <c r="AE83" s="17" t="n"/>
       <c r="AF83" s="17" t="inlineStr">
         <is>
-          <t>TC1@285</t>
+          <t>TT5@285</t>
         </is>
       </c>
       <c r="AG83" s="17" t="n"/>
       <c r="AH83" s="17" t="inlineStr">
         <is>
-          <t>TC1@75</t>
+          <t>TC5@75</t>
         </is>
       </c>
       <c r="AI83" s="17" t="n"/>
       <c r="AJ83" s="17" t="inlineStr">
         <is>
-          <t>TC1@120</t>
+          <t>TP2@120</t>
         </is>
       </c>
       <c r="AK83" s="17" t="n"/>
       <c r="AL83" s="17" t="inlineStr">
         <is>
-          <t>TC5@120</t>
+          <t>TC2@120</t>
         </is>
       </c>
       <c r="AM83" s="17" t="n"/>
       <c r="AN83" s="17" t="inlineStr">
         <is>
-          <t>TD1@210</t>
+          <t>TC4@210</t>
         </is>
       </c>
       <c r="AO83" s="17" t="n"/>
       <c r="AP83" s="17" t="inlineStr">
         <is>
-          <t>TD1@45</t>
+          <t>TP2@45</t>
         </is>
       </c>
       <c r="AQ83" s="17" t="n"/>
       <c r="AR83" s="17" t="inlineStr">
         <is>
-          <t>TT2@90</t>
+          <t>TC4@90</t>
         </is>
       </c>
       <c r="AS83" s="17" t="n"/>
       <c r="AT83" s="17" t="inlineStr">
         <is>
-          <t>TC3@90</t>
+          <t>TP5@90</t>
         </is>
       </c>
       <c r="AU83" s="17" t="n"/>
       <c r="AV83" s="17" t="inlineStr">
         <is>
-          <t>TT4@105</t>
+          <t>TT2@105</t>
         </is>
       </c>
       <c r="AW83" s="17" t="n"/>
@@ -9249,13 +9335,13 @@
       <c r="P84" s="17" t="n"/>
       <c r="Q84" s="17" t="inlineStr">
         <is>
-          <t>TD1@225</t>
+          <t>TC5@225</t>
         </is>
       </c>
       <c r="R84" s="17" t="n"/>
       <c r="S84" s="17" t="inlineStr">
         <is>
-          <t>TC5@315</t>
+          <t>TC1@315</t>
         </is>
       </c>
       <c r="T84" s="17" t="n"/>
@@ -9277,19 +9363,19 @@
       <c r="AB84" s="17" t="n"/>
       <c r="AC84" s="17" t="inlineStr">
         <is>
-          <t>TT2@60</t>
+          <t>TP1@60</t>
         </is>
       </c>
       <c r="AD84" s="17" t="n"/>
       <c r="AE84" s="17" t="inlineStr">
         <is>
-          <t>TC1@15</t>
+          <t>TP1@15</t>
         </is>
       </c>
       <c r="AF84" s="17" t="n"/>
       <c r="AG84" s="17" t="inlineStr">
         <is>
-          <t>TD1@30</t>
+          <t>TC4@30</t>
         </is>
       </c>
       <c r="AH84" s="17" t="n"/>
@@ -9315,61 +9401,61 @@
       </c>
       <c r="B85" s="17" t="inlineStr">
         <is>
-          <t>TC5@90</t>
+          <t>TC2@90</t>
         </is>
       </c>
       <c r="C85" s="17" t="n"/>
       <c r="D85" s="17" t="inlineStr">
         <is>
-          <t>TD1</t>
+          <t>TC1</t>
         </is>
       </c>
       <c r="E85" s="17" t="n"/>
       <c r="F85" s="17" t="inlineStr">
         <is>
-          <t>TT2@195</t>
+          <t>TP5@195</t>
         </is>
       </c>
       <c r="G85" s="17" t="n"/>
       <c r="H85" s="17" t="inlineStr">
         <is>
-          <t>TC1</t>
+          <t>TC5</t>
         </is>
       </c>
       <c r="I85" s="17" t="n"/>
       <c r="J85" s="17" t="inlineStr">
         <is>
-          <t>TC3@60</t>
+          <t>TC2@60</t>
         </is>
       </c>
       <c r="K85" s="17" t="n"/>
       <c r="L85" s="17" t="inlineStr">
         <is>
-          <t>TT2@240</t>
+          <t>TD1@240</t>
         </is>
       </c>
       <c r="M85" s="17" t="n"/>
       <c r="N85" s="17" t="inlineStr">
         <is>
-          <t>TC1@345</t>
+          <t>TC2@345</t>
         </is>
       </c>
       <c r="O85" s="17" t="n"/>
       <c r="P85" s="17" t="inlineStr">
         <is>
-          <t>TD1@255</t>
+          <t>TC1@255</t>
         </is>
       </c>
       <c r="Q85" s="17" t="n"/>
       <c r="R85" s="17" t="inlineStr">
         <is>
-          <t>TT2@75</t>
+          <t>TP5@75</t>
         </is>
       </c>
       <c r="S85" s="17" t="n"/>
       <c r="T85" s="17" t="inlineStr">
         <is>
-          <t>TT2@285</t>
+          <t>TP1@285</t>
         </is>
       </c>
       <c r="U85" s="17" t="n"/>
@@ -9387,19 +9473,19 @@
       <c r="AC85" s="17" t="n"/>
       <c r="AD85" s="17" t="inlineStr">
         <is>
-          <t>TC5@165</t>
+          <t>TP5@165</t>
         </is>
       </c>
       <c r="AE85" s="17" t="n"/>
       <c r="AF85" s="17" t="inlineStr">
         <is>
-          <t>TC5@90</t>
+          <t>TP1@90</t>
         </is>
       </c>
       <c r="AG85" s="17" t="n"/>
       <c r="AH85" s="17" t="inlineStr">
         <is>
-          <t>TC5@225</t>
+          <t>TP2@225</t>
         </is>
       </c>
       <c r="AI85" s="17" t="n"/>
@@ -9411,37 +9497,37 @@
       <c r="AK85" s="17" t="n"/>
       <c r="AL85" s="17" t="inlineStr">
         <is>
-          <t>TC5@120</t>
+          <t>TC4@120</t>
         </is>
       </c>
       <c r="AM85" s="17" t="n"/>
       <c r="AN85" s="17" t="inlineStr">
         <is>
-          <t>TC1@135</t>
+          <t>TP2@135</t>
         </is>
       </c>
       <c r="AO85" s="17" t="n"/>
       <c r="AP85" s="17" t="inlineStr">
         <is>
-          <t>TD1@15</t>
+          <t>TP5@15</t>
         </is>
       </c>
       <c r="AQ85" s="17" t="n"/>
       <c r="AR85" s="17" t="inlineStr">
         <is>
-          <t>TC3@240</t>
+          <t>TP1@240</t>
         </is>
       </c>
       <c r="AS85" s="17" t="n"/>
       <c r="AT85" s="17" t="inlineStr">
         <is>
-          <t>TC3@15</t>
+          <t>TP5@15</t>
         </is>
       </c>
       <c r="AU85" s="17" t="n"/>
       <c r="AV85" s="17" t="inlineStr">
         <is>
-          <t>TC5@105</t>
+          <t>TP1@105</t>
         </is>
       </c>
       <c r="AW85" s="17" t="n"/>
@@ -9467,19 +9553,19 @@
       <c r="P86" s="17" t="n"/>
       <c r="Q86" s="17" t="inlineStr">
         <is>
-          <t>TD1@225</t>
+          <t>TP1@225</t>
         </is>
       </c>
       <c r="R86" s="17" t="n"/>
       <c r="S86" s="17" t="inlineStr">
         <is>
-          <t>TC5@120</t>
+          <t>TP2@120</t>
         </is>
       </c>
       <c r="T86" s="17" t="n"/>
       <c r="U86" s="17" t="inlineStr">
         <is>
-          <t>TC3@240</t>
+          <t>TC1@240</t>
         </is>
       </c>
       <c r="V86" s="17" t="n"/>
@@ -9499,25 +9585,25 @@
       <c r="AB86" s="17" t="n"/>
       <c r="AC86" s="17" t="inlineStr">
         <is>
-          <t>TC3@345</t>
+          <t>TP1@345</t>
         </is>
       </c>
       <c r="AD86" s="17" t="n"/>
       <c r="AE86" s="17" t="inlineStr">
         <is>
-          <t>TC5@105</t>
+          <t>TC3@105</t>
         </is>
       </c>
       <c r="AF86" s="17" t="n"/>
       <c r="AG86" s="17" t="inlineStr">
         <is>
-          <t>TC3</t>
+          <t>TC4</t>
         </is>
       </c>
       <c r="AH86" s="17" t="n"/>
       <c r="AI86" s="17" t="inlineStr">
         <is>
-          <t>TT4@120</t>
+          <t>TC4@120</t>
         </is>
       </c>
       <c r="AJ86" s="17" t="n"/>
@@ -9541,61 +9627,61 @@
       </c>
       <c r="B87" s="17" t="inlineStr">
         <is>
-          <t>TT4@165</t>
+          <t>TC5@165</t>
         </is>
       </c>
       <c r="C87" s="17" t="n"/>
       <c r="D87" s="17" t="inlineStr">
         <is>
-          <t>TC5@210</t>
+          <t>TC1@210</t>
         </is>
       </c>
       <c r="E87" s="17" t="n"/>
       <c r="F87" s="17" t="inlineStr">
         <is>
-          <t>TD1@180</t>
+          <t>TP1@180</t>
         </is>
       </c>
       <c r="G87" s="17" t="n"/>
       <c r="H87" s="17" t="inlineStr">
         <is>
-          <t>TC3@210</t>
+          <t>TP2@210</t>
         </is>
       </c>
       <c r="I87" s="17" t="n"/>
       <c r="J87" s="17" t="inlineStr">
         <is>
-          <t>TC3@255</t>
+          <t>TT4@255</t>
         </is>
       </c>
       <c r="K87" s="17" t="n"/>
       <c r="L87" s="17" t="inlineStr">
         <is>
-          <t>TC5@135</t>
+          <t>TP2@135</t>
         </is>
       </c>
       <c r="M87" s="17" t="n"/>
       <c r="N87" s="17" t="inlineStr">
         <is>
-          <t>TC5@240</t>
+          <t>TP1@240</t>
         </is>
       </c>
       <c r="O87" s="17" t="n"/>
       <c r="P87" s="17" t="inlineStr">
         <is>
-          <t>TT4@135</t>
+          <t>TT5@135</t>
         </is>
       </c>
       <c r="Q87" s="17" t="n"/>
       <c r="R87" s="17" t="inlineStr">
         <is>
-          <t>TD1@300</t>
+          <t>TC4@300</t>
         </is>
       </c>
       <c r="S87" s="17" t="n"/>
       <c r="T87" s="17" t="inlineStr">
         <is>
-          <t>TC1@270</t>
+          <t>TC4@270</t>
         </is>
       </c>
       <c r="U87" s="17" t="n"/>
@@ -9617,37 +9703,37 @@
       <c r="AC87" s="17" t="n"/>
       <c r="AD87" s="17" t="inlineStr">
         <is>
-          <t>TT2@210</t>
+          <t>TC5@210</t>
         </is>
       </c>
       <c r="AE87" s="17" t="n"/>
       <c r="AF87" s="17" t="inlineStr">
         <is>
-          <t>TC5@60</t>
+          <t>TP1@60</t>
         </is>
       </c>
       <c r="AG87" s="17" t="n"/>
       <c r="AH87" s="17" t="inlineStr">
         <is>
-          <t>TC3@60</t>
+          <t>TC2@60</t>
         </is>
       </c>
       <c r="AI87" s="17" t="n"/>
       <c r="AJ87" s="17" t="inlineStr">
         <is>
-          <t>TD1@165</t>
+          <t>TC3@165</t>
         </is>
       </c>
       <c r="AK87" s="17" t="n"/>
       <c r="AL87" s="17" t="inlineStr">
         <is>
-          <t>TC3@255</t>
+          <t>TP5@255</t>
         </is>
       </c>
       <c r="AM87" s="17" t="n"/>
       <c r="AN87" s="17" t="inlineStr">
         <is>
-          <t>TC5@195</t>
+          <t>TC2@195</t>
         </is>
       </c>
       <c r="AO87" s="17" t="n"/>
@@ -9659,19 +9745,19 @@
       <c r="AQ87" s="17" t="n"/>
       <c r="AR87" s="17" t="inlineStr">
         <is>
-          <t>TC5</t>
+          <t>TC3</t>
         </is>
       </c>
       <c r="AS87" s="17" t="n"/>
       <c r="AT87" s="17" t="inlineStr">
         <is>
-          <t>TC3</t>
+          <t>TC5</t>
         </is>
       </c>
       <c r="AU87" s="17" t="n"/>
       <c r="AV87" s="17" t="inlineStr">
         <is>
-          <t>TT2@45</t>
+          <t>TC3@45</t>
         </is>
       </c>
       <c r="AW87" s="17" t="n"/>
@@ -9697,19 +9783,19 @@
       <c r="P88" s="17" t="n"/>
       <c r="Q88" s="17" t="inlineStr">
         <is>
-          <t>TC1@210</t>
+          <t>TT5@210</t>
         </is>
       </c>
       <c r="R88" s="17" t="n"/>
       <c r="S88" s="17" t="inlineStr">
         <is>
-          <t>TC3@30</t>
+          <t>TC5@30</t>
         </is>
       </c>
       <c r="T88" s="17" t="n"/>
       <c r="U88" s="17" t="inlineStr">
         <is>
-          <t>TC3@240</t>
+          <t>TC5@240</t>
         </is>
       </c>
       <c r="V88" s="17" t="n"/>
@@ -9737,13 +9823,13 @@
       <c r="AF88" s="17" t="n"/>
       <c r="AG88" s="17" t="inlineStr">
         <is>
-          <t>TD1@135</t>
+          <t>TT5@135</t>
         </is>
       </c>
       <c r="AH88" s="17" t="n"/>
       <c r="AI88" s="17" t="inlineStr">
         <is>
-          <t>TC3@75</t>
+          <t>TC2@75</t>
         </is>
       </c>
       <c r="AJ88" s="17" t="n"/>
@@ -9767,37 +9853,37 @@
       </c>
       <c r="B89" s="17" t="inlineStr">
         <is>
-          <t>TT2@120</t>
+          <t>TP5@120</t>
         </is>
       </c>
       <c r="C89" s="17" t="n"/>
       <c r="D89" s="17" t="inlineStr">
         <is>
-          <t>TD1@165</t>
+          <t>TC4@165</t>
         </is>
       </c>
       <c r="E89" s="17" t="n"/>
       <c r="F89" s="17" t="inlineStr">
         <is>
-          <t>TD1@180</t>
+          <t>TT2@180</t>
         </is>
       </c>
       <c r="G89" s="17" t="n"/>
       <c r="H89" s="17" t="inlineStr">
         <is>
-          <t>TD1@165</t>
+          <t>TC3@165</t>
         </is>
       </c>
       <c r="I89" s="17" t="n"/>
       <c r="J89" s="17" t="inlineStr">
         <is>
-          <t>TT2@30</t>
+          <t>TP2@30</t>
         </is>
       </c>
       <c r="K89" s="17" t="n"/>
       <c r="L89" s="17" t="inlineStr">
         <is>
-          <t>TC3@270</t>
+          <t>TT2@270</t>
         </is>
       </c>
       <c r="M89" s="17" t="n"/>
@@ -9809,19 +9895,19 @@
       <c r="O89" s="17" t="n"/>
       <c r="P89" s="17" t="inlineStr">
         <is>
-          <t>TT2@120</t>
+          <t>TC4@120</t>
         </is>
       </c>
       <c r="Q89" s="17" t="n"/>
       <c r="R89" s="17" t="inlineStr">
         <is>
-          <t>TD1@150</t>
+          <t>TP2@150</t>
         </is>
       </c>
       <c r="S89" s="17" t="n"/>
       <c r="T89" s="17" t="inlineStr">
         <is>
-          <t>TC5@255</t>
+          <t>TC3@255</t>
         </is>
       </c>
       <c r="U89" s="17" t="n"/>
@@ -9845,37 +9931,37 @@
       <c r="AE89" s="17" t="n"/>
       <c r="AF89" s="17" t="inlineStr">
         <is>
-          <t>TC1@240</t>
+          <t>TC4@240</t>
         </is>
       </c>
       <c r="AG89" s="17" t="n"/>
       <c r="AH89" s="17" t="inlineStr">
         <is>
-          <t>TD1@90</t>
+          <t>TP5@90</t>
         </is>
       </c>
       <c r="AI89" s="17" t="n"/>
       <c r="AJ89" s="17" t="inlineStr">
         <is>
-          <t>TC3@225</t>
+          <t>TP2@225</t>
         </is>
       </c>
       <c r="AK89" s="17" t="n"/>
       <c r="AL89" s="17" t="inlineStr">
         <is>
-          <t>TC1@120</t>
+          <t>TP1@120</t>
         </is>
       </c>
       <c r="AM89" s="17" t="n"/>
       <c r="AN89" s="17" t="inlineStr">
         <is>
-          <t>TC3@345</t>
+          <t>TC2@345</t>
         </is>
       </c>
       <c r="AO89" s="17" t="n"/>
       <c r="AP89" s="17" t="inlineStr">
         <is>
-          <t>TC3@135</t>
+          <t>TC1@135</t>
         </is>
       </c>
       <c r="AQ89" s="17" t="n"/>
@@ -9887,13 +9973,13 @@
       <c r="AS89" s="17" t="n"/>
       <c r="AT89" s="17" t="inlineStr">
         <is>
-          <t>TT2@45</t>
+          <t>TC5@45</t>
         </is>
       </c>
       <c r="AU89" s="17" t="n"/>
       <c r="AV89" s="17" t="inlineStr">
         <is>
-          <t>TT2@180</t>
+          <t>TC2@180</t>
         </is>
       </c>
       <c r="AW89" s="17" t="n"/>
@@ -9919,7 +10005,7 @@
       <c r="P90" s="17" t="n"/>
       <c r="Q90" s="17" t="inlineStr">
         <is>
-          <t>TD1@150</t>
+          <t>TT2@150</t>
         </is>
       </c>
       <c r="R90" s="17" t="n"/>
@@ -9929,7 +10015,11 @@
         </is>
       </c>
       <c r="T90" s="17" t="n"/>
-      <c r="U90" s="17" t="n"/>
+      <c r="U90" s="17" t="inlineStr">
+        <is>
+          <t>TC4@180</t>
+        </is>
+      </c>
       <c r="V90" s="17" t="n"/>
       <c r="W90" s="17" t="n"/>
       <c r="X90" s="17" t="inlineStr">
@@ -9959,17 +10049,21 @@
       </c>
       <c r="AC90" s="17" t="n"/>
       <c r="AD90" s="17" t="n"/>
-      <c r="AE90" s="17" t="n"/>
+      <c r="AE90" s="17" t="inlineStr">
+        <is>
+          <t>TC4@45</t>
+        </is>
+      </c>
       <c r="AF90" s="17" t="n"/>
       <c r="AG90" s="17" t="inlineStr">
         <is>
-          <t>TC3@90</t>
+          <t>TC1@90</t>
         </is>
       </c>
       <c r="AH90" s="17" t="n"/>
       <c r="AI90" s="17" t="inlineStr">
         <is>
-          <t>TC1@270</t>
+          <t>TC3@270</t>
         </is>
       </c>
       <c r="AJ90" s="17" t="n"/>
@@ -9993,61 +10087,61 @@
       </c>
       <c r="B91" s="17" t="inlineStr">
         <is>
-          <t>TD1@15</t>
+          <t>TC1@15</t>
         </is>
       </c>
       <c r="C91" s="17" t="n"/>
       <c r="D91" s="17" t="inlineStr">
         <is>
-          <t>TC5@300</t>
+          <t>TC3@300</t>
         </is>
       </c>
       <c r="E91" s="17" t="n"/>
       <c r="F91" s="17" t="inlineStr">
         <is>
-          <t>TC3@330</t>
+          <t>TT5@330</t>
         </is>
       </c>
       <c r="G91" s="17" t="n"/>
       <c r="H91" s="17" t="inlineStr">
         <is>
-          <t>TT4@300</t>
+          <t>TP2@300</t>
         </is>
       </c>
       <c r="I91" s="17" t="n"/>
       <c r="J91" s="17" t="inlineStr">
         <is>
-          <t>TT4@315</t>
+          <t>TP2@315</t>
         </is>
       </c>
       <c r="K91" s="17" t="n"/>
       <c r="L91" s="17" t="inlineStr">
         <is>
-          <t>TC1@270</t>
+          <t>TC5@270</t>
         </is>
       </c>
       <c r="M91" s="17" t="n"/>
       <c r="N91" s="17" t="inlineStr">
         <is>
-          <t>TD1@240</t>
+          <t>TT2@240</t>
         </is>
       </c>
       <c r="O91" s="17" t="n"/>
       <c r="P91" s="17" t="inlineStr">
         <is>
-          <t>TC1@285</t>
+          <t>TC2@285</t>
         </is>
       </c>
       <c r="Q91" s="17" t="n"/>
       <c r="R91" s="17" t="inlineStr">
         <is>
-          <t>TD1@330</t>
+          <t>TC3@330</t>
         </is>
       </c>
       <c r="S91" s="17" t="n"/>
       <c r="T91" s="17" t="inlineStr">
         <is>
-          <t>TT2@60</t>
+          <t>TP1@60</t>
         </is>
       </c>
       <c r="U91" s="17" t="n"/>
@@ -10095,43 +10189,43 @@
       <c r="AI91" s="17" t="n"/>
       <c r="AJ91" s="17" t="inlineStr">
         <is>
-          <t>TC3@90</t>
+          <t>TT4@90</t>
         </is>
       </c>
       <c r="AK91" s="17" t="n"/>
       <c r="AL91" s="17" t="inlineStr">
         <is>
-          <t>TT2@60</t>
+          <t>TC1@60</t>
         </is>
       </c>
       <c r="AM91" s="17" t="n"/>
       <c r="AN91" s="17" t="inlineStr">
         <is>
-          <t>TC3@75</t>
+          <t>TC4@75</t>
         </is>
       </c>
       <c r="AO91" s="17" t="n"/>
       <c r="AP91" s="17" t="inlineStr">
         <is>
-          <t>TD1@120</t>
+          <t>TP2@120</t>
         </is>
       </c>
       <c r="AQ91" s="17" t="n"/>
       <c r="AR91" s="17" t="inlineStr">
         <is>
-          <t>TC3@30</t>
+          <t>TT2@30</t>
         </is>
       </c>
       <c r="AS91" s="17" t="n"/>
       <c r="AT91" s="17" t="inlineStr">
         <is>
-          <t>TC3@45</t>
+          <t>TP2@45</t>
         </is>
       </c>
       <c r="AU91" s="17" t="n"/>
       <c r="AV91" s="17" t="inlineStr">
         <is>
-          <t>TD1@315</t>
+          <t>TP5@315</t>
         </is>
       </c>
       <c r="AW91" s="17" t="n"/>
@@ -10157,17 +10251,21 @@
       <c r="P92" s="17" t="n"/>
       <c r="Q92" s="17" t="inlineStr">
         <is>
-          <t>TC1@270</t>
+          <t>TP1@270</t>
         </is>
       </c>
       <c r="R92" s="17" t="n"/>
       <c r="S92" s="17" t="inlineStr">
         <is>
-          <t>TD1@120</t>
+          <t>TP5@120</t>
         </is>
       </c>
       <c r="T92" s="17" t="n"/>
-      <c r="U92" s="17" t="n"/>
+      <c r="U92" s="17" t="inlineStr">
+        <is>
+          <t>TC4@210</t>
+        </is>
+      </c>
       <c r="V92" s="17" t="n"/>
       <c r="W92" s="17" t="n"/>
       <c r="X92" s="17" t="inlineStr">
@@ -10197,17 +10295,21 @@
       </c>
       <c r="AC92" s="17" t="n"/>
       <c r="AD92" s="17" t="n"/>
-      <c r="AE92" s="17" t="n"/>
+      <c r="AE92" s="17" t="inlineStr">
+        <is>
+          <t>TC4@330</t>
+        </is>
+      </c>
       <c r="AF92" s="17" t="n"/>
       <c r="AG92" s="17" t="inlineStr">
         <is>
-          <t>TC5@225</t>
+          <t>TP5@225</t>
         </is>
       </c>
       <c r="AH92" s="17" t="n"/>
       <c r="AI92" s="17" t="inlineStr">
         <is>
-          <t>TT4@135</t>
+          <t>TC2@135</t>
         </is>
       </c>
       <c r="AJ92" s="17" t="n"/>
@@ -10231,61 +10333,61 @@
       </c>
       <c r="B93" s="17" t="inlineStr">
         <is>
-          <t>TT2@150</t>
+          <t>TT5@150</t>
         </is>
       </c>
       <c r="C93" s="17" t="n"/>
       <c r="D93" s="17" t="inlineStr">
         <is>
-          <t>TT4@270</t>
+          <t>TC3@270</t>
         </is>
       </c>
       <c r="E93" s="17" t="n"/>
       <c r="F93" s="17" t="inlineStr">
         <is>
-          <t>TD1@255</t>
+          <t>TC2@255</t>
         </is>
       </c>
       <c r="G93" s="17" t="n"/>
       <c r="H93" s="17" t="inlineStr">
         <is>
-          <t>TC3@105</t>
+          <t>TD1@105</t>
         </is>
       </c>
       <c r="I93" s="17" t="n"/>
       <c r="J93" s="17" t="inlineStr">
         <is>
-          <t>TC5@180</t>
+          <t>TC4@180</t>
         </is>
       </c>
       <c r="K93" s="17" t="n"/>
       <c r="L93" s="17" t="inlineStr">
         <is>
-          <t>TC5@300</t>
+          <t>TC1@300</t>
         </is>
       </c>
       <c r="M93" s="17" t="n"/>
       <c r="N93" s="17" t="inlineStr">
         <is>
-          <t>TT2@285</t>
+          <t>TP1@285</t>
         </is>
       </c>
       <c r="O93" s="17" t="n"/>
       <c r="P93" s="17" t="inlineStr">
         <is>
-          <t>TC3@300</t>
+          <t>TC5@300</t>
         </is>
       </c>
       <c r="Q93" s="17" t="n"/>
       <c r="R93" s="17" t="inlineStr">
         <is>
-          <t>TC3@165</t>
+          <t>TC4@165</t>
         </is>
       </c>
       <c r="S93" s="17" t="n"/>
       <c r="T93" s="17" t="inlineStr">
         <is>
-          <t>TT2</t>
+          <t>TP1</t>
         </is>
       </c>
       <c r="U93" s="17" t="n"/>
@@ -10321,7 +10423,7 @@
       <c r="AE93" s="17" t="n"/>
       <c r="AF93" s="17" t="inlineStr">
         <is>
-          <t>TC5@15</t>
+          <t>TP1@15</t>
         </is>
       </c>
       <c r="AG93" s="17" t="n"/>
@@ -10339,37 +10441,37 @@
       <c r="AK93" s="17" t="n"/>
       <c r="AL93" s="17" t="inlineStr">
         <is>
-          <t>TC3@300</t>
+          <t>TC4@300</t>
         </is>
       </c>
       <c r="AM93" s="17" t="n"/>
       <c r="AN93" s="17" t="inlineStr">
         <is>
-          <t>TC1@60</t>
+          <t>TT4@60</t>
         </is>
       </c>
       <c r="AO93" s="17" t="n"/>
       <c r="AP93" s="17" t="inlineStr">
         <is>
-          <t>TC3@240</t>
+          <t>TC5@240</t>
         </is>
       </c>
       <c r="AQ93" s="17" t="n"/>
       <c r="AR93" s="17" t="inlineStr">
         <is>
-          <t>TT2@30</t>
+          <t>TC2@30</t>
         </is>
       </c>
       <c r="AS93" s="17" t="n"/>
       <c r="AT93" s="17" t="inlineStr">
         <is>
-          <t>TT4@195</t>
+          <t>TD1@195</t>
         </is>
       </c>
       <c r="AU93" s="17" t="n"/>
       <c r="AV93" s="17" t="inlineStr">
         <is>
-          <t>TT2@60</t>
+          <t>TP5@60</t>
         </is>
       </c>
       <c r="AW93" s="17" t="n"/>
@@ -10395,17 +10497,21 @@
       <c r="P94" s="17" t="n"/>
       <c r="Q94" s="17" t="inlineStr">
         <is>
-          <t>TC1@225</t>
+          <t>TC3@225</t>
         </is>
       </c>
       <c r="R94" s="17" t="n"/>
       <c r="S94" s="17" t="inlineStr">
         <is>
-          <t>TC1@330</t>
+          <t>TC2@330</t>
         </is>
       </c>
       <c r="T94" s="17" t="n"/>
-      <c r="U94" s="17" t="n"/>
+      <c r="U94" s="17" t="inlineStr">
+        <is>
+          <t>TC4@270</t>
+        </is>
+      </c>
       <c r="V94" s="17" t="n"/>
       <c r="W94" s="17" t="n"/>
       <c r="X94" s="17" t="inlineStr">
@@ -10435,17 +10541,21 @@
       </c>
       <c r="AC94" s="17" t="n"/>
       <c r="AD94" s="17" t="n"/>
-      <c r="AE94" s="17" t="n"/>
+      <c r="AE94" s="17" t="inlineStr">
+        <is>
+          <t>TC4@270</t>
+        </is>
+      </c>
       <c r="AF94" s="17" t="n"/>
       <c r="AG94" s="17" t="inlineStr">
         <is>
-          <t>TC3@255</t>
+          <t>TD1@255</t>
         </is>
       </c>
       <c r="AH94" s="17" t="n"/>
       <c r="AI94" s="17" t="inlineStr">
         <is>
-          <t>TC5@255</t>
+          <t>TC2@255</t>
         </is>
       </c>
       <c r="AJ94" s="17" t="n"/>
@@ -10469,55 +10579,55 @@
       </c>
       <c r="B95" s="17" t="inlineStr">
         <is>
-          <t>TC3@105</t>
+          <t>TC4@105</t>
         </is>
       </c>
       <c r="C95" s="17" t="n"/>
       <c r="D95" s="17" t="inlineStr">
         <is>
-          <t>TT4@75</t>
+          <t>TC2@75</t>
         </is>
       </c>
       <c r="E95" s="17" t="n"/>
       <c r="F95" s="17" t="inlineStr">
         <is>
-          <t>TD1@330</t>
+          <t>TC5@330</t>
         </is>
       </c>
       <c r="G95" s="17" t="n"/>
       <c r="H95" s="17" t="inlineStr">
         <is>
-          <t>TD1@75</t>
+          <t>TC4@75</t>
         </is>
       </c>
       <c r="I95" s="17" t="n"/>
       <c r="J95" s="17" t="inlineStr">
         <is>
-          <t>TC3@255</t>
+          <t>TP2@255</t>
         </is>
       </c>
       <c r="K95" s="17" t="n"/>
       <c r="L95" s="17" t="inlineStr">
         <is>
-          <t>TT2@150</t>
+          <t>TD1@150</t>
         </is>
       </c>
       <c r="M95" s="17" t="n"/>
       <c r="N95" s="17" t="inlineStr">
         <is>
-          <t>TT4@240</t>
+          <t>TC2@240</t>
         </is>
       </c>
       <c r="O95" s="17" t="n"/>
       <c r="P95" s="17" t="inlineStr">
         <is>
-          <t>TT2@150</t>
+          <t>TC5@150</t>
         </is>
       </c>
       <c r="Q95" s="17" t="n"/>
       <c r="R95" s="17" t="inlineStr">
         <is>
-          <t>TC5@45</t>
+          <t>TT5@45</t>
         </is>
       </c>
       <c r="S95" s="17" t="n"/>
@@ -10539,55 +10649,55 @@
       <c r="AE95" s="17" t="n"/>
       <c r="AF95" s="17" t="inlineStr">
         <is>
-          <t>TT2@225</t>
+          <t>TC3@225</t>
         </is>
       </c>
       <c r="AG95" s="17" t="n"/>
       <c r="AH95" s="17" t="inlineStr">
         <is>
-          <t>TT2@285</t>
+          <t>TC1@285</t>
         </is>
       </c>
       <c r="AI95" s="17" t="n"/>
       <c r="AJ95" s="17" t="inlineStr">
         <is>
-          <t>TT4@330</t>
+          <t>TC5@330</t>
         </is>
       </c>
       <c r="AK95" s="17" t="n"/>
       <c r="AL95" s="17" t="inlineStr">
         <is>
-          <t>TC5@240</t>
+          <t>TC1@240</t>
         </is>
       </c>
       <c r="AM95" s="17" t="n"/>
       <c r="AN95" s="17" t="inlineStr">
         <is>
-          <t>TT4@180</t>
+          <t>TC2@180</t>
         </is>
       </c>
       <c r="AO95" s="17" t="n"/>
       <c r="AP95" s="17" t="inlineStr">
         <is>
-          <t>TC3@120</t>
+          <t>TP5@120</t>
         </is>
       </c>
       <c r="AQ95" s="17" t="n"/>
       <c r="AR95" s="17" t="inlineStr">
         <is>
-          <t>TC1@135</t>
+          <t>TC3@135</t>
         </is>
       </c>
       <c r="AS95" s="17" t="n"/>
       <c r="AT95" s="17" t="inlineStr">
         <is>
-          <t>TD1@195</t>
+          <t>TP1@195</t>
         </is>
       </c>
       <c r="AU95" s="17" t="n"/>
       <c r="AV95" s="17" t="inlineStr">
         <is>
-          <t>TC5@300</t>
+          <t>TC3@300</t>
         </is>
       </c>
       <c r="AW95" s="17" t="n"/>
@@ -10613,19 +10723,19 @@
       <c r="P96" s="17" t="n"/>
       <c r="Q96" s="17" t="inlineStr">
         <is>
-          <t>TC1@210</t>
+          <t>TC4@210</t>
         </is>
       </c>
       <c r="R96" s="17" t="n"/>
       <c r="S96" s="17" t="inlineStr">
         <is>
-          <t>TC3@255</t>
+          <t>TP5@255</t>
         </is>
       </c>
       <c r="T96" s="17" t="n"/>
       <c r="U96" s="17" t="inlineStr">
         <is>
-          <t>TC5@345</t>
+          <t>TC3@345</t>
         </is>
       </c>
       <c r="V96" s="17" t="n"/>
@@ -10675,37 +10785,37 @@
       </c>
       <c r="B97" s="17" t="inlineStr">
         <is>
-          <t>TC1@345</t>
+          <t>TP1@345</t>
         </is>
       </c>
       <c r="C97" s="17" t="n"/>
       <c r="D97" s="17" t="inlineStr">
         <is>
-          <t>TC1@285</t>
+          <t>TP2@285</t>
         </is>
       </c>
       <c r="E97" s="17" t="n"/>
       <c r="F97" s="17" t="inlineStr">
         <is>
-          <t>TC1@210</t>
+          <t>TC3@210</t>
         </is>
       </c>
       <c r="G97" s="17" t="n"/>
       <c r="H97" s="17" t="inlineStr">
         <is>
-          <t>TD1</t>
+          <t>TP1</t>
         </is>
       </c>
       <c r="I97" s="17" t="n"/>
       <c r="J97" s="17" t="inlineStr">
         <is>
-          <t>TC3@45</t>
+          <t>TC2@45</t>
         </is>
       </c>
       <c r="K97" s="17" t="n"/>
       <c r="L97" s="17" t="inlineStr">
         <is>
-          <t>TT2@165</t>
+          <t>TC1@165</t>
         </is>
       </c>
       <c r="M97" s="17" t="n"/>
@@ -10717,91 +10827,103 @@
       <c r="O97" s="17" t="n"/>
       <c r="P97" s="17" t="inlineStr">
         <is>
-          <t>TC3@210</t>
+          <t>TP1@210</t>
         </is>
       </c>
       <c r="Q97" s="17" t="n"/>
       <c r="R97" s="17" t="inlineStr">
         <is>
-          <t>TC5@285</t>
+          <t>TP1@285</t>
         </is>
       </c>
       <c r="S97" s="17" t="n"/>
       <c r="T97" s="17" t="inlineStr">
         <is>
-          <t>TC1@60</t>
+          <t>TC4@60</t>
         </is>
       </c>
       <c r="U97" s="17" t="n"/>
       <c r="V97" s="17" t="inlineStr">
         <is>
-          <t>TT2@285</t>
+          <t>TC3@285</t>
         </is>
       </c>
       <c r="W97" s="17" t="n"/>
-      <c r="X97" s="17" t="n"/>
+      <c r="X97" s="17" t="inlineStr">
+        <is>
+          <t>TC4@45</t>
+        </is>
+      </c>
       <c r="Y97" s="17" t="n"/>
-      <c r="Z97" s="17" t="n"/>
+      <c r="Z97" s="17" t="inlineStr">
+        <is>
+          <t>TC4@120</t>
+        </is>
+      </c>
       <c r="AA97" s="17" t="n"/>
-      <c r="AB97" s="17" t="n"/>
+      <c r="AB97" s="17" t="inlineStr">
+        <is>
+          <t>TC4@285</t>
+        </is>
+      </c>
       <c r="AC97" s="17" t="n"/>
       <c r="AD97" s="17" t="inlineStr">
         <is>
-          <t>TT2</t>
+          <t>TC3</t>
         </is>
       </c>
       <c r="AE97" s="17" t="n"/>
       <c r="AF97" s="17" t="inlineStr">
         <is>
-          <t>TD1@195</t>
+          <t>TC4@195</t>
         </is>
       </c>
       <c r="AG97" s="17" t="n"/>
       <c r="AH97" s="17" t="inlineStr">
         <is>
-          <t>TC5@60</t>
+          <t>TP5@60</t>
         </is>
       </c>
       <c r="AI97" s="17" t="n"/>
       <c r="AJ97" s="17" t="inlineStr">
         <is>
-          <t>TT4@120</t>
+          <t>TC5@120</t>
         </is>
       </c>
       <c r="AK97" s="17" t="n"/>
       <c r="AL97" s="17" t="inlineStr">
         <is>
-          <t>TC3@15</t>
+          <t>TP2@15</t>
         </is>
       </c>
       <c r="AM97" s="17" t="n"/>
       <c r="AN97" s="17" t="inlineStr">
         <is>
-          <t>TC3@15</t>
+          <t>TC2@15</t>
         </is>
       </c>
       <c r="AO97" s="17" t="n"/>
       <c r="AP97" s="17" t="inlineStr">
         <is>
-          <t>TT4@15</t>
+          <t>TC1@15</t>
         </is>
       </c>
       <c r="AQ97" s="17" t="n"/>
       <c r="AR97" s="17" t="inlineStr">
         <is>
-          <t>TC5@120</t>
+          <t>TP2@120</t>
         </is>
       </c>
       <c r="AS97" s="17" t="n"/>
       <c r="AT97" s="17" t="inlineStr">
         <is>
-          <t>TC3@135</t>
+          <t>TC1@135</t>
         </is>
       </c>
       <c r="AU97" s="17" t="n"/>
       <c r="AV97" s="17" t="inlineStr">
         <is>
-          <t>TT4@165</t>
+          <t>TC2@165</t>
         </is>
       </c>
       <c r="AW97" s="17" t="n"/>
@@ -10839,49 +10961,49 @@
       <c r="T98" s="17" t="n"/>
       <c r="U98" s="17" t="inlineStr">
         <is>
-          <t>TD1</t>
+          <t>TC3</t>
         </is>
       </c>
       <c r="V98" s="17" t="n"/>
       <c r="W98" s="17" t="inlineStr">
         <is>
-          <t>TT2@195</t>
+          <t>TP1@195</t>
         </is>
       </c>
       <c r="X98" s="17" t="n"/>
       <c r="Y98" s="17" t="inlineStr">
         <is>
-          <t>TC1@30</t>
+          <t>TC4@30</t>
         </is>
       </c>
       <c r="Z98" s="17" t="n"/>
       <c r="AA98" s="17" t="inlineStr">
         <is>
-          <t>TC5@30</t>
+          <t>TP1@30</t>
         </is>
       </c>
       <c r="AB98" s="17" t="n"/>
       <c r="AC98" s="17" t="inlineStr">
         <is>
-          <t>TC3@210</t>
+          <t>TC4@210</t>
         </is>
       </c>
       <c r="AD98" s="17" t="n"/>
       <c r="AE98" s="17" t="inlineStr">
         <is>
-          <t>TD1@345</t>
+          <t>TC2@345</t>
         </is>
       </c>
       <c r="AF98" s="17" t="n"/>
       <c r="AG98" s="17" t="inlineStr">
         <is>
-          <t>TC3@255</t>
+          <t>TP5@255</t>
         </is>
       </c>
       <c r="AH98" s="17" t="n"/>
       <c r="AI98" s="17" t="inlineStr">
         <is>
-          <t>TC1@210</t>
+          <t>TC4@210</t>
         </is>
       </c>
       <c r="AJ98" s="17" t="n"/>
@@ -10905,85 +11027,85 @@
       </c>
       <c r="B99" s="17" t="inlineStr">
         <is>
-          <t>TD1@345</t>
+          <t>TC5@345</t>
         </is>
       </c>
       <c r="C99" s="17" t="n"/>
       <c r="D99" s="17" t="inlineStr">
         <is>
-          <t>TC5@300</t>
+          <t>TC3@300</t>
         </is>
       </c>
       <c r="E99" s="17" t="n"/>
       <c r="F99" s="17" t="inlineStr">
         <is>
-          <t>TT4@240</t>
+          <t>TP1@240</t>
         </is>
       </c>
       <c r="G99" s="17" t="n"/>
       <c r="H99" s="17" t="inlineStr">
         <is>
-          <t>TC1@135</t>
+          <t>TC3@135</t>
         </is>
       </c>
       <c r="I99" s="17" t="n"/>
       <c r="J99" s="17" t="inlineStr">
         <is>
-          <t>TC1@120</t>
+          <t>TP5@120</t>
         </is>
       </c>
       <c r="K99" s="17" t="n"/>
       <c r="L99" s="17" t="inlineStr">
         <is>
-          <t>TT4@180</t>
+          <t>TC2@180</t>
         </is>
       </c>
       <c r="M99" s="17" t="n"/>
       <c r="N99" s="17" t="inlineStr">
         <is>
-          <t>TT2@330</t>
+          <t>TC3@330</t>
         </is>
       </c>
       <c r="O99" s="17" t="n"/>
       <c r="P99" s="17" t="inlineStr">
         <is>
-          <t>TT4@330</t>
+          <t>TC5@330</t>
         </is>
       </c>
       <c r="Q99" s="17" t="n"/>
       <c r="R99" s="17" t="inlineStr">
         <is>
-          <t>TT2@255</t>
+          <t>TC1@255</t>
         </is>
       </c>
       <c r="S99" s="17" t="n"/>
       <c r="T99" s="17" t="inlineStr">
         <is>
-          <t>TT2@225</t>
+          <t>TD1@225</t>
         </is>
       </c>
       <c r="U99" s="17" t="n"/>
       <c r="V99" s="17" t="inlineStr">
         <is>
-          <t>TC5@30</t>
+          <t>TT2@30</t>
         </is>
       </c>
       <c r="W99" s="17" t="n"/>
       <c r="X99" s="17" t="inlineStr">
         <is>
-          <t>TC3@270</t>
+          <t>TP1@270</t>
         </is>
       </c>
       <c r="Y99" s="17" t="n"/>
       <c r="Z99" s="17" t="inlineStr">
         <is>
-          <t>TC5@270</t>
+          <t>TP5@270</t>
         </is>
       </c>
       <c r="AA99" s="17" t="n"/>
       <c r="AB99" s="17" t="inlineStr">
         <is>
-          <t>TT2@225</t>
+          <t>TC5@225</t>
         </is>
       </c>
       <c r="AC99" s="17" t="n"/>
@@ -10995,7 +11117,7 @@
       <c r="AE99" s="17" t="n"/>
       <c r="AF99" s="17" t="inlineStr">
         <is>
-          <t>TC3@345</t>
+          <t>TP2@345</t>
         </is>
       </c>
       <c r="AG99" s="17" t="n"/>
@@ -11007,43 +11129,43 @@
       <c r="AI99" s="17" t="n"/>
       <c r="AJ99" s="17" t="inlineStr">
         <is>
-          <t>TT2@150</t>
+          <t>TC5@150</t>
         </is>
       </c>
       <c r="AK99" s="17" t="n"/>
       <c r="AL99" s="17" t="inlineStr">
         <is>
-          <t>TC1@210</t>
+          <t>TC5@210</t>
         </is>
       </c>
       <c r="AM99" s="17" t="n"/>
       <c r="AN99" s="17" t="inlineStr">
         <is>
-          <t>TT2@150</t>
+          <t>TD1@150</t>
         </is>
       </c>
       <c r="AO99" s="17" t="n"/>
       <c r="AP99" s="17" t="inlineStr">
         <is>
-          <t>TC3@135</t>
+          <t>TC1@135</t>
         </is>
       </c>
       <c r="AQ99" s="17" t="n"/>
       <c r="AR99" s="17" t="inlineStr">
         <is>
-          <t>TD1@75</t>
+          <t>TC4@75</t>
         </is>
       </c>
       <c r="AS99" s="17" t="n"/>
       <c r="AT99" s="17" t="inlineStr">
         <is>
-          <t>TT2@135</t>
+          <t>TD1@135</t>
         </is>
       </c>
       <c r="AU99" s="17" t="n"/>
       <c r="AV99" s="17" t="inlineStr">
         <is>
-          <t>TT4@75</t>
+          <t>TC2@75</t>
         </is>
       </c>
       <c r="AW99" s="17" t="n"/>
@@ -11071,49 +11193,49 @@
       <c r="R100" s="17" t="n"/>
       <c r="S100" s="17" t="inlineStr">
         <is>
-          <t>TC3@255</t>
+          <t>TD1@255</t>
         </is>
       </c>
       <c r="T100" s="17" t="n"/>
       <c r="U100" s="17" t="inlineStr">
         <is>
-          <t>TC5@270</t>
+          <t>TC1@270</t>
         </is>
       </c>
       <c r="V100" s="17" t="n"/>
       <c r="W100" s="17" t="inlineStr">
         <is>
-          <t>TD1@300</t>
+          <t>TP2@300</t>
         </is>
       </c>
       <c r="X100" s="17" t="n"/>
       <c r="Y100" s="17" t="inlineStr">
         <is>
-          <t>TT2@135</t>
+          <t>TC2@135</t>
         </is>
       </c>
       <c r="Z100" s="17" t="n"/>
       <c r="AA100" s="17" t="inlineStr">
         <is>
-          <t>TC5@210</t>
+          <t>TP2@210</t>
         </is>
       </c>
       <c r="AB100" s="17" t="n"/>
       <c r="AC100" s="17" t="inlineStr">
         <is>
-          <t>TC5@285</t>
+          <t>TP1@285</t>
         </is>
       </c>
       <c r="AD100" s="17" t="n"/>
       <c r="AE100" s="17" t="inlineStr">
         <is>
-          <t>TC5@270</t>
+          <t>TC1@270</t>
         </is>
       </c>
       <c r="AF100" s="17" t="n"/>
       <c r="AG100" s="17" t="inlineStr">
         <is>
-          <t>TC1@330</t>
+          <t>TC2@330</t>
         </is>
       </c>
       <c r="AH100" s="17" t="n"/>
@@ -11139,79 +11261,79 @@
       </c>
       <c r="B101" s="17" t="inlineStr">
         <is>
-          <t>TC1@315</t>
+          <t>TC4@315</t>
         </is>
       </c>
       <c r="C101" s="17" t="n"/>
       <c r="D101" s="17" t="inlineStr">
         <is>
-          <t>TD1@345</t>
+          <t>TP2@345</t>
         </is>
       </c>
       <c r="E101" s="17" t="n"/>
       <c r="F101" s="17" t="inlineStr">
         <is>
-          <t>TT4@195</t>
+          <t>TD1@195</t>
         </is>
       </c>
       <c r="G101" s="17" t="n"/>
       <c r="H101" s="17" t="inlineStr">
         <is>
-          <t>TC5@255</t>
+          <t>TP2@255</t>
         </is>
       </c>
       <c r="I101" s="17" t="n"/>
       <c r="J101" s="17" t="inlineStr">
         <is>
-          <t>TC3@195</t>
+          <t>TP2@195</t>
         </is>
       </c>
       <c r="K101" s="17" t="n"/>
       <c r="L101" s="17" t="inlineStr">
         <is>
-          <t>TT2@285</t>
+          <t>TP5@285</t>
         </is>
       </c>
       <c r="M101" s="17" t="n"/>
       <c r="N101" s="17" t="inlineStr">
         <is>
-          <t>TC3@300</t>
+          <t>TC4@300</t>
         </is>
       </c>
       <c r="O101" s="17" t="n"/>
       <c r="P101" s="17" t="inlineStr">
         <is>
-          <t>TC3@75</t>
+          <t>TD1@75</t>
         </is>
       </c>
       <c r="Q101" s="17" t="n"/>
       <c r="R101" s="17" t="inlineStr">
         <is>
-          <t>TT4@90</t>
+          <t>TC4@90</t>
         </is>
       </c>
       <c r="S101" s="17" t="n"/>
       <c r="T101" s="17" t="inlineStr">
         <is>
-          <t>TT2@345</t>
+          <t>TC1@345</t>
         </is>
       </c>
       <c r="U101" s="17" t="n"/>
       <c r="V101" s="17" t="inlineStr">
         <is>
-          <t>TC1@90</t>
+          <t>TP1@90</t>
         </is>
       </c>
       <c r="W101" s="17" t="n"/>
       <c r="X101" s="17" t="inlineStr">
         <is>
-          <t>TT2@15</t>
+          <t>TC5@15</t>
         </is>
       </c>
       <c r="Y101" s="17" t="n"/>
       <c r="Z101" s="17" t="inlineStr">
         <is>
-          <t>TT2@90</t>
+          <t>TP5@90</t>
         </is>
       </c>
       <c r="AA101" s="17" t="n"/>
@@ -11223,61 +11345,61 @@
       <c r="AC101" s="17" t="n"/>
       <c r="AD101" s="17" t="inlineStr">
         <is>
-          <t>TT2@165</t>
+          <t>TC4@165</t>
         </is>
       </c>
       <c r="AE101" s="17" t="n"/>
       <c r="AF101" s="17" t="inlineStr">
         <is>
-          <t>TC5@315</t>
+          <t>TC3@315</t>
         </is>
       </c>
       <c r="AG101" s="17" t="n"/>
       <c r="AH101" s="17" t="inlineStr">
         <is>
-          <t>TC1@90</t>
+          <t>TT4@90</t>
         </is>
       </c>
       <c r="AI101" s="17" t="n"/>
       <c r="AJ101" s="17" t="inlineStr">
         <is>
-          <t>TC5@135</t>
+          <t>TT5@135</t>
         </is>
       </c>
       <c r="AK101" s="17" t="n"/>
       <c r="AL101" s="17" t="inlineStr">
         <is>
-          <t>TT2@285</t>
+          <t>TP1@285</t>
         </is>
       </c>
       <c r="AM101" s="17" t="n"/>
       <c r="AN101" s="17" t="inlineStr">
         <is>
-          <t>TT4@90</t>
+          <t>TP1@90</t>
         </is>
       </c>
       <c r="AO101" s="17" t="n"/>
       <c r="AP101" s="17" t="inlineStr">
         <is>
-          <t>TT2@135</t>
+          <t>TP1@135</t>
         </is>
       </c>
       <c r="AQ101" s="17" t="n"/>
       <c r="AR101" s="17" t="inlineStr">
         <is>
-          <t>TT4</t>
+          <t>TC3</t>
         </is>
       </c>
       <c r="AS101" s="17" t="n"/>
       <c r="AT101" s="17" t="inlineStr">
         <is>
-          <t>TD1@255</t>
+          <t>TC2@255</t>
         </is>
       </c>
       <c r="AU101" s="17" t="n"/>
       <c r="AV101" s="17" t="inlineStr">
         <is>
-          <t>TT2@345</t>
+          <t>TP1@345</t>
         </is>
       </c>
       <c r="AW101" s="17" t="n"/>
@@ -11341,85 +11463,85 @@
       </c>
       <c r="B103" s="17" t="inlineStr">
         <is>
-          <t>TC1@75</t>
+          <t>TC4@75</t>
         </is>
       </c>
       <c r="C103" s="17" t="n"/>
       <c r="D103" s="17" t="inlineStr">
         <is>
-          <t>TD1@315</t>
+          <t>TP5@315</t>
         </is>
       </c>
       <c r="E103" s="17" t="n"/>
       <c r="F103" s="17" t="inlineStr">
         <is>
-          <t>TD1@255</t>
+          <t>TC4@255</t>
         </is>
       </c>
       <c r="G103" s="17" t="n"/>
       <c r="H103" s="17" t="inlineStr">
         <is>
-          <t>TC3@30</t>
+          <t>TT2@30</t>
         </is>
       </c>
       <c r="I103" s="17" t="n"/>
       <c r="J103" s="17" t="inlineStr">
         <is>
-          <t>TC1@300</t>
+          <t>TC2@300</t>
         </is>
       </c>
       <c r="K103" s="17" t="n"/>
       <c r="L103" s="17" t="inlineStr">
         <is>
-          <t>TC3@75</t>
+          <t>TC4@75</t>
         </is>
       </c>
       <c r="M103" s="17" t="n"/>
       <c r="N103" s="17" t="inlineStr">
         <is>
-          <t>TC3@345</t>
+          <t>TD1@345</t>
         </is>
       </c>
       <c r="O103" s="17" t="n"/>
       <c r="P103" s="17" t="inlineStr">
         <is>
-          <t>TC3@90</t>
+          <t>TT4@90</t>
         </is>
       </c>
       <c r="Q103" s="17" t="n"/>
       <c r="R103" s="17" t="inlineStr">
         <is>
-          <t>TT4@45</t>
+          <t>TP5@45</t>
         </is>
       </c>
       <c r="S103" s="17" t="n"/>
       <c r="T103" s="17" t="inlineStr">
         <is>
-          <t>TC5@30</t>
+          <t>TP2@30</t>
         </is>
       </c>
       <c r="U103" s="17" t="n"/>
       <c r="V103" s="17" t="inlineStr">
         <is>
-          <t>TT2@165</t>
+          <t>TC5@165</t>
         </is>
       </c>
       <c r="W103" s="17" t="n"/>
       <c r="X103" s="17" t="inlineStr">
         <is>
-          <t>TC5@330</t>
+          <t>TC1@330</t>
         </is>
       </c>
       <c r="Y103" s="17" t="n"/>
       <c r="Z103" s="17" t="inlineStr">
         <is>
-          <t>TD1@135</t>
+          <t>TP5@135</t>
         </is>
       </c>
       <c r="AA103" s="17" t="n"/>
       <c r="AB103" s="17" t="inlineStr">
         <is>
-          <t>TC1@30</t>
+          <t>TP2@30</t>
         </is>
       </c>
       <c r="AC103" s="17" t="n"/>
@@ -11431,55 +11553,55 @@
       <c r="AE103" s="17" t="n"/>
       <c r="AF103" s="17" t="inlineStr">
         <is>
-          <t>TD1@60</t>
+          <t>TP1@60</t>
         </is>
       </c>
       <c r="AG103" s="17" t="n"/>
       <c r="AH103" s="17" t="inlineStr">
         <is>
-          <t>TC3@285</t>
+          <t>TP1@285</t>
         </is>
       </c>
       <c r="AI103" s="17" t="n"/>
       <c r="AJ103" s="17" t="inlineStr">
         <is>
-          <t>TC1@285</t>
+          <t>TC2@285</t>
         </is>
       </c>
       <c r="AK103" s="17" t="n"/>
       <c r="AL103" s="17" t="inlineStr">
         <is>
-          <t>TC5@30</t>
+          <t>TC3@30</t>
         </is>
       </c>
       <c r="AM103" s="17" t="n"/>
       <c r="AN103" s="17" t="inlineStr">
         <is>
-          <t>TC1@270</t>
+          <t>TC5@270</t>
         </is>
       </c>
       <c r="AO103" s="17" t="n"/>
       <c r="AP103" s="17" t="inlineStr">
         <is>
-          <t>TC5@120</t>
+          <t>TC1@120</t>
         </is>
       </c>
       <c r="AQ103" s="17" t="n"/>
       <c r="AR103" s="17" t="inlineStr">
         <is>
-          <t>TT4@300</t>
+          <t>TP2@300</t>
         </is>
       </c>
       <c r="AS103" s="17" t="n"/>
       <c r="AT103" s="17" t="inlineStr">
         <is>
-          <t>TT4@45</t>
+          <t>TC4@45</t>
         </is>
       </c>
       <c r="AU103" s="17" t="n"/>
       <c r="AV103" s="17" t="inlineStr">
         <is>
-          <t>TC5@300</t>
+          <t>TC3@300</t>
         </is>
       </c>
       <c r="AW103" s="17" t="n"/>
@@ -11543,145 +11665,145 @@
       </c>
       <c r="B105" s="17" t="inlineStr">
         <is>
-          <t>TD1@255</t>
+          <t>TP5@255</t>
         </is>
       </c>
       <c r="C105" s="17" t="n"/>
       <c r="D105" s="17" t="inlineStr">
         <is>
-          <t>TC3@330</t>
+          <t>TC2@330</t>
         </is>
       </c>
       <c r="E105" s="17" t="n"/>
       <c r="F105" s="17" t="inlineStr">
         <is>
-          <t>TC5@90</t>
+          <t>TC1@90</t>
         </is>
       </c>
       <c r="G105" s="17" t="n"/>
       <c r="H105" s="17" t="inlineStr">
         <is>
-          <t>TT4@210</t>
+          <t>TC1@210</t>
         </is>
       </c>
       <c r="I105" s="17" t="n"/>
       <c r="J105" s="17" t="inlineStr">
         <is>
-          <t>TD1@345</t>
+          <t>TC3@345</t>
         </is>
       </c>
       <c r="K105" s="17" t="n"/>
       <c r="L105" s="17" t="inlineStr">
         <is>
-          <t>TC3@345</t>
+          <t>TC4@345</t>
         </is>
       </c>
       <c r="M105" s="17" t="n"/>
       <c r="N105" s="17" t="inlineStr">
         <is>
-          <t>TC3@345</t>
+          <t>TP1@345</t>
         </is>
       </c>
       <c r="O105" s="17" t="n"/>
       <c r="P105" s="17" t="inlineStr">
         <is>
-          <t>TT4@345</t>
+          <t>TC5@345</t>
         </is>
       </c>
       <c r="Q105" s="17" t="n"/>
       <c r="R105" s="17" t="inlineStr">
         <is>
-          <t>TD1@90</t>
+          <t>TP5@90</t>
         </is>
       </c>
       <c r="S105" s="17" t="n"/>
       <c r="T105" s="17" t="inlineStr">
         <is>
-          <t>TT4@255</t>
+          <t>TC4@255</t>
         </is>
       </c>
       <c r="U105" s="17" t="n"/>
       <c r="V105" s="17" t="inlineStr">
         <is>
-          <t>TC1@315</t>
+          <t>TC4@315</t>
         </is>
       </c>
       <c r="W105" s="17" t="n"/>
       <c r="X105" s="17" t="inlineStr">
         <is>
-          <t>TC5@150</t>
+          <t>TC2@150</t>
         </is>
       </c>
       <c r="Y105" s="17" t="n"/>
       <c r="Z105" s="17" t="inlineStr">
         <is>
-          <t>TT4@330</t>
+          <t>TC5@330</t>
         </is>
       </c>
       <c r="AA105" s="17" t="n"/>
       <c r="AB105" s="17" t="inlineStr">
         <is>
-          <t>TT2@180</t>
+          <t>TP1@180</t>
         </is>
       </c>
       <c r="AC105" s="17" t="n"/>
       <c r="AD105" s="17" t="inlineStr">
         <is>
-          <t>TD1@90</t>
+          <t>TC3@90</t>
         </is>
       </c>
       <c r="AE105" s="17" t="n"/>
       <c r="AF105" s="17" t="inlineStr">
         <is>
-          <t>TC1@120</t>
+          <t>TP5@120</t>
         </is>
       </c>
       <c r="AG105" s="17" t="n"/>
       <c r="AH105" s="17" t="inlineStr">
         <is>
-          <t>TT4@150</t>
+          <t>TP2@150</t>
         </is>
       </c>
       <c r="AI105" s="17" t="n"/>
       <c r="AJ105" s="17" t="inlineStr">
         <is>
-          <t>TC5@345</t>
+          <t>TC3@345</t>
         </is>
       </c>
       <c r="AK105" s="17" t="n"/>
       <c r="AL105" s="17" t="inlineStr">
         <is>
-          <t>TC1@225</t>
+          <t>TC5@225</t>
         </is>
       </c>
       <c r="AM105" s="17" t="n"/>
       <c r="AN105" s="17" t="inlineStr">
         <is>
-          <t>TT2@315</t>
+          <t>TP5@315</t>
         </is>
       </c>
       <c r="AO105" s="17" t="n"/>
       <c r="AP105" s="17" t="inlineStr">
         <is>
-          <t>TT2@240</t>
+          <t>TP1@240</t>
         </is>
       </c>
       <c r="AQ105" s="17" t="n"/>
       <c r="AR105" s="17" t="inlineStr">
         <is>
-          <t>TT4@150</t>
+          <t>TP1@150</t>
         </is>
       </c>
       <c r="AS105" s="17" t="n"/>
       <c r="AT105" s="17" t="inlineStr">
         <is>
-          <t>TD1@135</t>
+          <t>TC1@135</t>
         </is>
       </c>
       <c r="AU105" s="17" t="n"/>
       <c r="AV105" s="17" t="inlineStr">
         <is>
-          <t>TC5</t>
+          <t>TP5</t>
         </is>
       </c>
       <c r="AW105" s="17" t="n"/>
@@ -11745,73 +11867,73 @@
       </c>
       <c r="B107" s="17" t="inlineStr">
         <is>
-          <t>TD1@165</t>
+          <t>TC5@165</t>
         </is>
       </c>
       <c r="C107" s="17" t="n"/>
       <c r="D107" s="17" t="inlineStr">
         <is>
-          <t>TT2@45</t>
+          <t>TC3@45</t>
         </is>
       </c>
       <c r="E107" s="17" t="n"/>
       <c r="F107" s="17" t="inlineStr">
         <is>
-          <t>TD1@150</t>
+          <t>TP5@150</t>
         </is>
       </c>
       <c r="G107" s="17" t="n"/>
       <c r="H107" s="17" t="inlineStr">
         <is>
-          <t>TC5</t>
+          <t>TC3</t>
         </is>
       </c>
       <c r="I107" s="17" t="n"/>
       <c r="J107" s="17" t="inlineStr">
         <is>
-          <t>TT2</t>
+          <t>TP1</t>
         </is>
       </c>
       <c r="K107" s="17" t="n"/>
       <c r="L107" s="17" t="inlineStr">
         <is>
-          <t>TC5@195</t>
+          <t>TC2@195</t>
         </is>
       </c>
       <c r="M107" s="17" t="n"/>
       <c r="N107" s="17" t="inlineStr">
         <is>
-          <t>TT2@90</t>
+          <t>TC1@90</t>
         </is>
       </c>
       <c r="O107" s="17" t="n"/>
       <c r="P107" s="17" t="inlineStr">
         <is>
-          <t>TD1@165</t>
+          <t>TC3@165</t>
         </is>
       </c>
       <c r="Q107" s="17" t="n"/>
       <c r="R107" s="17" t="inlineStr">
         <is>
-          <t>TC5@315</t>
+          <t>TC2@315</t>
         </is>
       </c>
       <c r="S107" s="17" t="n"/>
       <c r="T107" s="17" t="inlineStr">
         <is>
-          <t>TC5@60</t>
+          <t>TT4@60</t>
         </is>
       </c>
       <c r="U107" s="17" t="n"/>
       <c r="V107" s="17" t="inlineStr">
         <is>
-          <t>TC1@165</t>
+          <t>TC2@165</t>
         </is>
       </c>
       <c r="W107" s="17" t="n"/>
       <c r="X107" s="17" t="inlineStr">
         <is>
-          <t>TD1@255</t>
+          <t>TC3@255</t>
         </is>
       </c>
       <c r="Y107" s="17" t="n"/>
@@ -11823,67 +11945,67 @@
       <c r="AA107" s="17" t="n"/>
       <c r="AB107" s="17" t="inlineStr">
         <is>
-          <t>TC3@120</t>
+          <t>TT2@120</t>
         </is>
       </c>
       <c r="AC107" s="17" t="n"/>
       <c r="AD107" s="17" t="inlineStr">
         <is>
-          <t>TT4@165</t>
+          <t>TC3@165</t>
         </is>
       </c>
       <c r="AE107" s="17" t="n"/>
       <c r="AF107" s="17" t="inlineStr">
         <is>
-          <t>TC1@270</t>
+          <t>TC4@270</t>
         </is>
       </c>
       <c r="AG107" s="17" t="n"/>
       <c r="AH107" s="17" t="inlineStr">
         <is>
-          <t>TC5@180</t>
+          <t>TC4@180</t>
         </is>
       </c>
       <c r="AI107" s="17" t="n"/>
       <c r="AJ107" s="17" t="inlineStr">
         <is>
-          <t>TT4@135</t>
+          <t>TT5@135</t>
         </is>
       </c>
       <c r="AK107" s="17" t="n"/>
       <c r="AL107" s="17" t="inlineStr">
         <is>
-          <t>TC1@75</t>
+          <t>TD1@75</t>
         </is>
       </c>
       <c r="AM107" s="17" t="n"/>
       <c r="AN107" s="17" t="inlineStr">
         <is>
-          <t>TC5@135</t>
+          <t>TP2@135</t>
         </is>
       </c>
       <c r="AO107" s="17" t="n"/>
       <c r="AP107" s="17" t="inlineStr">
         <is>
-          <t>TD1@105</t>
+          <t>TC4@105</t>
         </is>
       </c>
       <c r="AQ107" s="17" t="n"/>
       <c r="AR107" s="17" t="inlineStr">
         <is>
-          <t>TC3@210</t>
+          <t>TP2@210</t>
         </is>
       </c>
       <c r="AS107" s="17" t="n"/>
       <c r="AT107" s="17" t="inlineStr">
         <is>
-          <t>TC1@90</t>
+          <t>TT5@90</t>
         </is>
       </c>
       <c r="AU107" s="17" t="n"/>
       <c r="AV107" s="17" t="inlineStr">
         <is>
-          <t>TC5@210</t>
+          <t>TC1@210</t>
         </is>
       </c>
       <c r="AW107" s="17" t="n"/>
@@ -11947,67 +12069,67 @@
       </c>
       <c r="B109" s="17" t="inlineStr">
         <is>
-          <t>TC1@135</t>
+          <t>TP5@135</t>
         </is>
       </c>
       <c r="C109" s="17" t="n"/>
       <c r="D109" s="17" t="inlineStr">
         <is>
-          <t>TC1@255</t>
+          <t>TP1@255</t>
         </is>
       </c>
       <c r="E109" s="17" t="n"/>
       <c r="F109" s="17" t="inlineStr">
         <is>
-          <t>TC3@15</t>
+          <t>TP5@15</t>
         </is>
       </c>
       <c r="G109" s="17" t="n"/>
       <c r="H109" s="17" t="inlineStr">
         <is>
-          <t>TD1@105</t>
+          <t>TP1@105</t>
         </is>
       </c>
       <c r="I109" s="17" t="n"/>
       <c r="J109" s="17" t="inlineStr">
         <is>
-          <t>TT4@60</t>
+          <t>TP1@60</t>
         </is>
       </c>
       <c r="K109" s="17" t="n"/>
       <c r="L109" s="17" t="inlineStr">
         <is>
-          <t>TT2@225</t>
+          <t>TC1@225</t>
         </is>
       </c>
       <c r="M109" s="17" t="n"/>
       <c r="N109" s="17" t="inlineStr">
         <is>
-          <t>TC5@120</t>
+          <t>TC4@120</t>
         </is>
       </c>
       <c r="O109" s="17" t="n"/>
       <c r="P109" s="17" t="inlineStr">
         <is>
-          <t>TT4@120</t>
+          <t>TP2@120</t>
         </is>
       </c>
       <c r="Q109" s="17" t="n"/>
       <c r="R109" s="17" t="inlineStr">
         <is>
-          <t>TT4@60</t>
+          <t>TP2@60</t>
         </is>
       </c>
       <c r="S109" s="17" t="n"/>
       <c r="T109" s="17" t="inlineStr">
         <is>
-          <t>TC1@60</t>
+          <t>TC5@60</t>
         </is>
       </c>
       <c r="U109" s="17" t="n"/>
       <c r="V109" s="17" t="inlineStr">
         <is>
-          <t>TC5@165</t>
+          <t>TP5@165</t>
         </is>
       </c>
       <c r="W109" s="17" t="n"/>
@@ -12019,73 +12141,73 @@
       <c r="Y109" s="17" t="n"/>
       <c r="Z109" s="17" t="inlineStr">
         <is>
-          <t>TD1@240</t>
+          <t>TT2@240</t>
         </is>
       </c>
       <c r="AA109" s="17" t="n"/>
       <c r="AB109" s="17" t="inlineStr">
         <is>
-          <t>TD1@255</t>
+          <t>TC1@255</t>
         </is>
       </c>
       <c r="AC109" s="17" t="n"/>
       <c r="AD109" s="17" t="inlineStr">
         <is>
-          <t>TT2@90</t>
+          <t>TC2@90</t>
         </is>
       </c>
       <c r="AE109" s="17" t="n"/>
       <c r="AF109" s="17" t="inlineStr">
         <is>
-          <t>TD1@75</t>
+          <t>TT5@75</t>
         </is>
       </c>
       <c r="AG109" s="17" t="n"/>
       <c r="AH109" s="17" t="inlineStr">
         <is>
-          <t>TT4@150</t>
+          <t>TC2@150</t>
         </is>
       </c>
       <c r="AI109" s="17" t="n"/>
       <c r="AJ109" s="17" t="inlineStr">
         <is>
-          <t>TC5@90</t>
+          <t>TP5@90</t>
         </is>
       </c>
       <c r="AK109" s="17" t="n"/>
       <c r="AL109" s="17" t="inlineStr">
         <is>
-          <t>TC1@345</t>
+          <t>TC2@345</t>
         </is>
       </c>
       <c r="AM109" s="17" t="n"/>
       <c r="AN109" s="17" t="inlineStr">
         <is>
-          <t>TT4@75</t>
+          <t>TC2@75</t>
         </is>
       </c>
       <c r="AO109" s="17" t="n"/>
       <c r="AP109" s="17" t="inlineStr">
         <is>
-          <t>TC1@225</t>
+          <t>TC4@225</t>
         </is>
       </c>
       <c r="AQ109" s="17" t="n"/>
       <c r="AR109" s="17" t="inlineStr">
         <is>
-          <t>TC3@150</t>
+          <t>TC5@150</t>
         </is>
       </c>
       <c r="AS109" s="17" t="n"/>
       <c r="AT109" s="17" t="inlineStr">
         <is>
-          <t>TT2@195</t>
+          <t>TP5@195</t>
         </is>
       </c>
       <c r="AU109" s="17" t="n"/>
       <c r="AV109" s="17" t="inlineStr">
         <is>
-          <t>TC5@315</t>
+          <t>TP5@315</t>
         </is>
       </c>
       <c r="AW109" s="17" t="n"/>
